--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Quien no es Nunca_ha_cotizado tiene reg_cotiz_ppal_agrupado informada</t>
+          <t>Quien no es Nunca_ha_cotizado tiene causa_ult_baja informada</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND reg_cotiz_ppal_agrupado IS NULL</t>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND causa_ult_baja IS NULL</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado</t>
+          <t>edad_ultimo_empleo</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Quien no es Nunca_ha_cotizado tiene tipo_contr_ppal_agrupado informada</t>
+          <t>Quien no es Nunca_ha_cotizado tiene edad_ultimo_empleo informada</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND tipo_contr_ppal_agrupado IS NULL</t>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND edad_ultimo_empleo IS NULL</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja</t>
+          <t>reg_cotiz_ppal_agrupado</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Quien no es Nunca_ha_cotizado tiene causa_ult_baja informada</t>
+          <t>Con empleo real, quien no es Nunca_ha_cotizado tiene reg_cotiz_ppal_agrupado informada</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND causa_ult_baja IS NULL</t>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND COALESCE(t_total_empleo, 0) &gt; 0 AND reg_cotiz_ppal_agrupado IS NULL</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>edad_ultimo_empleo</t>
+          <t>tipo_contr_ppal_agrupado</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Quien no es Nunca_ha_cotizado tiene edad_ultimo_empleo informada</t>
+          <t>Con empleo real, quien no es Nunca_ha_cotizado tiene tipo_contr_ppal_agrupado informada</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND edad_ultimo_empleo IS NULL</t>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND COALESCE(t_total_empleo, 0) &gt; 0 AND tipo_contr_ppal_agrupado IS NULL</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>Sin régimen de cotización ⇒ Nunca_ha_cotizado</t>
+          <t>Sin régimen de cotización, con empleo real ⇒ Nunca_ha_cotizado</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr">
@@ -27104,10 +27104,14 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado IS NULL AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
-        </is>
-      </c>
-      <c r="J506" s="2" t="inlineStr"/>
+          <t>reg_cotiz_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="inlineStr">
+        <is>
+          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene régimen principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
+        </is>
+      </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27142,7 +27146,7 @@
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>Sin tipo de contrato principal (nulo) ⇒ Nunca_ha_cotizado</t>
+          <t>Sin tipo de contrato principal (nulo), con empleo real ⇒ Nunca_ha_cotizado</t>
         </is>
       </c>
       <c r="G507" s="2" t="inlineStr">
@@ -27157,10 +27161,14 @@
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado IS NULL AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
-        </is>
-      </c>
-      <c r="J507" s="2" t="inlineStr"/>
+          <t>tipo_contr_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="inlineStr">
+        <is>
+          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene tipo de contrato principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
+        </is>
+      </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
           <t>OK</t>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dudas para el usuario" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reglas'!$A$1:$K$563</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reglas'!$A$1:$K$562</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K563"/>
+  <dimension ref="A1:K562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19543,12 +19543,12 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio</t>
+          <t>t_total_desempleo</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl vacío ⇒ cotizado_anual_promedio vacío</t>
+          <t>tiempo_total_desde_inicio_vl vacío ⇒ t_total_desempleo vacío</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl IS NULL AND cotizado_anual_promedio IS NOT NULL</t>
+          <t>tiempo_total_desde_inicio_vl IS NULL AND t_total_desempleo IS NOT NULL</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr"/>
@@ -19596,12 +19596,12 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio</t>
+          <t>t_total_desempleo</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio vacío ⇒ tiempo_total_desde_inicio_vl vacío (hay historia)</t>
+          <t>t_total_desempleo vacío ⇒ tiempo_total_desde_inicio_vl vacío (hay historia)</t>
         </is>
       </c>
       <c r="G362" s="2" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
+          <t>t_total_desempleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
         </is>
       </c>
       <c r="J362" s="2" t="inlineStr"/>
@@ -19649,12 +19649,12 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo</t>
+          <t>causas_baja_distintas</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl vacío ⇒ t_total_desempleo vacío</t>
+          <t>tiempo_total_desde_inicio_vl vacío ⇒ causas_baja_distintas vacío</t>
         </is>
       </c>
       <c r="G363" s="2" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl IS NULL AND t_total_desempleo IS NOT NULL</t>
+          <t>tiempo_total_desde_inicio_vl IS NULL AND causas_baja_distintas IS NOT NULL</t>
         </is>
       </c>
       <c r="J363" s="2" t="inlineStr"/>
@@ -19702,12 +19702,12 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo</t>
+          <t>causas_baja_distintas</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo vacío ⇒ tiempo_total_desde_inicio_vl vacío (hay historia)</t>
+          <t>causas_baja_distintas vacío ⇒ tiempo_total_desde_inicio_vl vacío (hay historia)</t>
         </is>
       </c>
       <c r="G364" s="2" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
+          <t>causas_baja_distintas IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr"/>
@@ -19755,12 +19755,12 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas</t>
+          <t>cotizado_anual_promedio</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl vacío ⇒ causas_baja_distintas vacío</t>
+          <t>tiempo_total_desde_inicio_vl vacío ⇒ cotizado_anual_promedio vacío</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
@@ -19775,7 +19775,7 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl IS NULL AND causas_baja_distintas IS NOT NULL</t>
+          <t>tiempo_total_desde_inicio_vl IS NULL AND cotizado_anual_promedio IS NOT NULL</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr"/>
@@ -19803,17 +19803,17 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl</t>
+          <t>edad_primer_empleo_signif</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas</t>
+          <t>duracion_1er_empleo_signif</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas vacío ⇒ tiempo_total_desde_inicio_vl vacío (hay historia)</t>
+          <t>edad primer empleo significativo vacía ⇒ su duración vacía</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
+          <t>edad_primer_empleo_signif IS NULL AND duracion_1er_empleo_signif IS NOT NULL</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr"/>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>edad primer empleo significativo vacía ⇒ su duración vacía</t>
+          <t>duración del primer empleo significativo vacía ⇒ su edad vacía</t>
         </is>
       </c>
       <c r="G367" s="2" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>edad_primer_empleo_signif IS NULL AND duracion_1er_empleo_signif IS NOT NULL</t>
+          <t>duracion_1er_empleo_signif IS NULL AND edad_primer_empleo_signif IS NOT NULL</t>
         </is>
       </c>
       <c r="J367" s="2" t="inlineStr"/>
@@ -19909,17 +19909,17 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>edad_primer_empleo_signif</t>
+          <t>causas_baja_distintas</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>duracion_1er_empleo_signif</t>
+          <t>causa_baja_mas_comun</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>duración del primer empleo significativo vacía ⇒ su edad vacía</t>
+          <t>causas_baja_distintas vacío ⇒ causa_baja_mas_comun sin valor</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>duracion_1er_empleo_signif IS NULL AND edad_primer_empleo_signif IS NOT NULL</t>
+          <t>causas_baja_distintas IS NULL AND (causa_baja_mas_comun IS NOT NULL AND causa_baja_mas_comun NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta'))</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas vacío ⇒ causa_baja_mas_comun sin valor</t>
+          <t>causa_baja_mas_comun con valor real ⇒ causas_baja_distintas informado</t>
         </is>
       </c>
       <c r="G369" s="2" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas IS NULL AND (causa_baja_mas_comun IS NOT NULL AND causa_baja_mas_comun NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta'))</t>
+          <t>(causa_baja_mas_comun IS NOT NULL AND causa_baja_mas_comun NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND causas_baja_distintas IS NULL</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr"/>
@@ -20010,22 +20010,22 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Acoplamiento de nulos</t>
+          <t>Pensiones</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_mas_comun</t>
+          <t>pension_actual</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_mas_comun con valor real ⇒ causas_baja_distintas informado</t>
+          <t>cobra pensión = SI ⇒ pension_actual informada</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>(causa_baja_mas_comun IS NOT NULL AND causa_baja_mas_comun NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND causas_baja_distintas IS NULL</t>
+          <t>cobra_pension_2024_5 = 'SI' AND pension_actual IS NULL</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr"/>
@@ -20078,7 +20078,7 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>cobra pensión = SI ⇒ pension_actual informada</t>
+          <t>cobra pensión = NO ⇒ pension_actual vacía</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 = 'SI' AND pension_actual IS NULL</t>
+          <t>cobra_pension_2024_5 = 'NO' AND pension_actual IS NOT NULL</t>
         </is>
       </c>
       <c r="J371" s="2" t="inlineStr"/>
@@ -20121,17 +20121,17 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>pension_actual</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>pension_actual</t>
+          <t>pension_todas_cobradas</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>cobra pensión = NO ⇒ pension_actual vacía</t>
+          <t>Las pensiones actuales están incluidas en todas las cobradas</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 = 'NO' AND pension_actual IS NOT NULL</t>
+          <t>pension_actual IS NOT NULL AND (pension_todas_cobradas IS NULL OR NOT list_has_all(pension_todas_cobradas, pension_actual))</t>
         </is>
       </c>
       <c r="J372" s="2" t="inlineStr"/>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>pension_actual</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>Las pensiones actuales están incluidas en todas las cobradas</t>
+          <t>cobra pensión = SI ⇒ ha cobrado alguna pensión</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>pension_actual IS NOT NULL AND (pension_todas_cobradas IS NULL OR NOT list_has_all(pension_todas_cobradas, pension_actual))</t>
+          <t>cobra_pension_2024_5 = 'SI' AND pension_todas_cobradas IS NULL</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr"/>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>discap_pension</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -20237,7 +20237,7 @@
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>cobra pensión = SI ⇒ ha cobrado alguna pensión</t>
+          <t>Discapacidad por pensión ⇒ ha cobrado una pensión de incapacidad</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
@@ -20247,15 +20247,19 @@
       </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 = 'SI' AND pension_todas_cobradas IS NULL</t>
-        </is>
-      </c>
-      <c r="J374" s="2" t="inlineStr"/>
+          <t>discap_pension AND (pension_todas_cobradas IS NULL OR array_to_string(pension_todas_cobradas, ',') NOT LIKE '%Incapacidad%')</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>A confirmar la definición de discap_pension</t>
+        </is>
+      </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -20290,7 +20294,7 @@
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>Discapacidad por pensión ⇒ ha cobrado una pensión de incapacidad</t>
+          <t>Discapacidad por pensión ⇒ ha cobrado alguna pensión</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
@@ -20300,19 +20304,15 @@
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>discap_pension AND (pension_todas_cobradas IS NULL OR array_to_string(pension_todas_cobradas, ',') NOT LIKE '%Incapacidad%')</t>
-        </is>
-      </c>
-      <c r="J375" s="2" t="inlineStr">
-        <is>
-          <t>A confirmar la definición de discap_pension</t>
-        </is>
-      </c>
+          <t>discap_pension AND pension_todas_cobradas IS NULL</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr"/>
       <c r="K375" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -20337,35 +20337,39 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>discap_pension</t>
+          <t>pension_actual</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>pension_todas_cobradas</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>Discapacidad por pensión ⇒ ha cobrado alguna pensión</t>
+          <t>Jubilación ⇒ edad ≥ 50</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>discap_pension AND pension_todas_cobradas IS NULL</t>
-        </is>
-      </c>
-      <c r="J376" s="2" t="inlineStr"/>
+          <t>array_to_string(pension_actual, ',') LIKE '%Jubilaci%' AND edad_actual_fecha_corte &lt; 50</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>Jubilaciones anticipadas por actividad penosa desde ~52</t>
+        </is>
+      </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -20400,7 +20404,7 @@
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>Jubilación ⇒ edad ≥ 50</t>
+          <t>Orfandad ⇒ edad ≤ 60</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
@@ -20410,17 +20414,17 @@
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Jubilaci%' AND edad_actual_fecha_corte &lt; 50</t>
+          <t>array_to_string(pension_actual, ',') LIKE '%Orfandad%' AND edad_actual_fecha_corte &gt; 60</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>Jubilaciones anticipadas por actividad penosa desde ~52</t>
+          <t>Puede haber orfandad de discapacitados</t>
         </is>
       </c>
       <c r="K377" s="2" t="inlineStr">
@@ -20457,7 +20461,7 @@
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>Orfandad ⇒ edad ≤ 60</t>
+          <t>Viudedad ⇒ edad ≥ 18</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
@@ -20472,14 +20476,10 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Orfandad%' AND edad_actual_fecha_corte &gt; 60</t>
-        </is>
-      </c>
-      <c r="J378" s="2" t="inlineStr">
-        <is>
-          <t>Puede haber orfandad de discapacitados</t>
-        </is>
-      </c>
+          <t>array_to_string(pension_actual, ',') LIKE '%Viudedad%' AND edad_actual_fecha_corte &lt; 18</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
       <c r="K378" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>Viudedad ⇒ edad ≥ 18</t>
+          <t>Incapacidad ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G379" s="2" t="inlineStr">
@@ -20524,12 +20524,12 @@
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Viudedad%' AND edad_actual_fecha_corte &lt; 18</t>
+          <t>array_to_string(pension_actual, ',') LIKE '%Incapacidad%' AND edad_actual_fecha_corte &lt; 16</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr"/>
@@ -20567,12 +20567,12 @@
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>Incapacidad ⇒ edad ≥ 16</t>
+          <t>Incapacidad&gt;65 ⇒ edad ≥ 65</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Incapacidad%' AND edad_actual_fecha_corte &lt; 16</t>
+          <t>array_to_string(pension_actual, ',') LIKE '%Incapacidad&gt;65%' AND edad_actual_fecha_corte &lt; 65</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr"/>
@@ -20615,27 +20615,27 @@
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>pension_actual</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>Incapacidad&gt;65 ⇒ edad ≥ 65</t>
+          <t>No se cobra jubilación e incapacidad a la vez (la incapacidad se convierte en jubilación)</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Incapacidad&gt;65%' AND edad_actual_fecha_corte &lt; 65</t>
+          <t>array_to_string(pension_actual, ',') LIKE '%Jubilaci%' AND array_to_string(pension_actual, ',') LIKE '%Incapacidad%'</t>
         </is>
       </c>
       <c r="J381" s="2" t="inlineStr"/>
@@ -20668,12 +20668,12 @@
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>pension_actual</t>
+          <t>t_total_empleo</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>No se cobra jubilación e incapacidad a la vez (la incapacidad se convierte en jubilación)</t>
+          <t>Jubilación ⇒ ≥ 10 años de empleo (se exigen 15 cotizados)</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
@@ -20683,15 +20683,19 @@
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Jubilaci%' AND array_to_string(pension_actual, ',') LIKE '%Incapacidad%'</t>
-        </is>
-      </c>
-      <c r="J382" s="2" t="inlineStr"/>
+          <t>array_to_string(pension_actual, ',') LIKE '%Jubilaci%' AND COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) &lt; 10</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>Faltan datos anteriores a 1967</t>
+        </is>
+      </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -20721,12 +20725,12 @@
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo</t>
+          <t>edad_ultimo_empleo</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>Jubilación ⇒ ≥ 10 años de empleo (se exigen 15 cotizados)</t>
+          <t>Jubilación ⇒ edad del último empleo ≥ 30</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
@@ -20741,14 +20745,10 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Jubilaci%' AND COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) &lt; 10</t>
-        </is>
-      </c>
-      <c r="J383" s="2" t="inlineStr">
-        <is>
-          <t>Faltan datos anteriores a 1967</t>
-        </is>
-      </c>
+          <t>array_to_string(pension_actual, ',') LIKE '%Jubilaci%' AND edad_ultimo_empleo &lt; 30</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr"/>
       <c r="K383" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -20776,29 +20776,25 @@
           <t>pension_actual</t>
         </is>
       </c>
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>edad_ultimo_empleo</t>
-        </is>
-      </c>
+      <c r="E384" s="2" t="inlineStr"/>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>Jubilación ⇒ edad del último empleo ≥ 30</t>
+          <t>pension_actual solo contiene los 6 tipos conocidos</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Jubilaci%' AND edad_ultimo_empleo &lt; 30</t>
+          <t>pension_actual IS NOT NULL AND len(list_filter(pension_actual, x -&gt; x NOT IN ('Incapacidad','Jubilación','Viudedad','Orfandad','Pension_a_favor_familiares','Incapacidad&gt;65'))) &gt; 0</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr"/>
@@ -20826,13 +20822,13 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>pension_actual</t>
+          <t>pension_todas_cobradas</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr"/>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>pension_actual solo contiene los 6 tipos conocidos</t>
+          <t>pension_todas_cobradas solo contiene los 6 tipos conocidos</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr">
@@ -20847,7 +20843,7 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>pension_actual IS NOT NULL AND len(list_filter(pension_actual, x -&gt; x NOT IN ('Incapacidad','Jubilación','Viudedad','Orfandad','Pension_a_favor_familiares','Incapacidad&gt;65'))) &gt; 0</t>
+          <t>pension_todas_cobradas IS NOT NULL AND len(list_filter(pension_todas_cobradas, x -&gt; x NOT IN ('Incapacidad','Jubilación','Viudedad','Orfandad','Pension_a_favor_familiares','Incapacidad&gt;65'))) &gt; 0</t>
         </is>
       </c>
       <c r="J385" s="2" t="inlineStr"/>
@@ -20881,7 +20877,7 @@
       <c r="E386" s="2" t="inlineStr"/>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>pension_todas_cobradas solo contiene los 6 tipos conocidos</t>
+          <t>pension_todas_cobradas no repite tipos (es 'tipos distintos')</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr">
@@ -20891,12 +20887,12 @@
       </c>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>pension_todas_cobradas IS NOT NULL AND len(list_filter(pension_todas_cobradas, x -&gt; x NOT IN ('Incapacidad','Jubilación','Viudedad','Orfandad','Pension_a_favor_familiares','Incapacidad&gt;65'))) &gt; 0</t>
+          <t>len(pension_todas_cobradas) &lt;&gt; len(list_distinct(pension_todas_cobradas))</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr"/>
@@ -20924,13 +20920,13 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>pension_todas_cobradas</t>
+          <t>pension_actual</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr"/>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>pension_todas_cobradas no repite tipos (es 'tipos distintos')</t>
+          <t>pension_actual no repite tipos (es 'tipos distintos')</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
@@ -20945,10 +20941,14 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>len(pension_todas_cobradas) &lt;&gt; len(list_distinct(pension_todas_cobradas))</t>
-        </is>
-      </c>
-      <c r="J387" s="2" t="inlineStr"/>
+          <t>pension_actual IS NOT NULL AND len(pension_actual) &lt;&gt; len(list_distinct(pension_actual))</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>Regla nueva 2026-09-22: bug real corregido en el ETL (faltaba el .unique() que ya tenía pension_todas_cobradas, 3.823 personas afectadas); esta regla vigila que no vuelva a pasar</t>
+        </is>
+      </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -20979,7 +20979,7 @@
       <c r="E388" s="2" t="inlineStr"/>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>pension_actual no repite tipos (es 'tipos distintos')</t>
+          <t>Sin pensión ⇒ NULL, no lista vacía</t>
         </is>
       </c>
       <c r="G388" s="2" t="inlineStr">
@@ -20994,14 +20994,10 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>pension_actual IS NOT NULL AND len(pension_actual) &lt;&gt; len(list_distinct(pension_actual))</t>
-        </is>
-      </c>
-      <c r="J388" s="2" t="inlineStr">
-        <is>
-          <t>Regla nueva 2026-09-22: bug real corregido en el ETL (faltaba el .unique() que ya tenía pension_todas_cobradas, 3.823 personas afectadas); esta regla vigila que no vuelva a pasar</t>
-        </is>
-      </c>
+          <t>pension_actual IS NOT NULL AND len(pension_actual) = 0</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr"/>
       <c r="K388" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21026,13 +21022,13 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>pension_actual</t>
+          <t>pension_todas_cobradas</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr"/>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>Sin pensión ⇒ NULL, no lista vacía</t>
+          <t>Sin pensiones ⇒ NULL, no lista vacía</t>
         </is>
       </c>
       <c r="G389" s="2" t="inlineStr">
@@ -21047,7 +21043,7 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>pension_actual IS NOT NULL AND len(pension_actual) = 0</t>
+          <t>pension_todas_cobradas IS NOT NULL AND len(pension_todas_cobradas) = 0</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr"/>
@@ -21070,18 +21066,22 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Pensiones</t>
+          <t>Datos fiscales y discapacidad</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>pension_todas_cobradas</t>
-        </is>
-      </c>
-      <c r="E390" s="2" t="inlineStr"/>
+          <t>ingresos_bruto_total_2024</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>prov_fiscal_actual</t>
+        </is>
+      </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>Sin pensiones ⇒ NULL, no lista vacía</t>
+          <t>Con ingresos ⇒ provincia fiscal conocida</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>pension_todas_cobradas IS NOT NULL AND len(pension_todas_cobradas) = 0</t>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND NOT (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta'))</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr"/>
@@ -21124,17 +21124,17 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
+          <t>prov_fiscal_actual</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
           <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
-      <c r="E391" s="2" t="inlineStr">
-        <is>
-          <t>prov_fiscal_actual</t>
-        </is>
-      </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos ⇒ provincia fiscal conocida</t>
+          <t>Provincia fiscal conocida ⇒ con ingresos</t>
         </is>
       </c>
       <c r="G391" s="2" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND NOT (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta'))</t>
+          <t>(prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND ingresos_bruto_total_2024 IS NULL</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr"/>
@@ -21177,22 +21177,22 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual</t>
+          <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>Provincia fiscal conocida ⇒ con ingresos</t>
+          <t>Con ingresos ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
@@ -21202,10 +21202,14 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>(prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND ingresos_bruto_total_2024 IS NULL</t>
-        </is>
-      </c>
-      <c r="J392" s="2" t="inlineStr"/>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>Las pensiones de orfandad también constan como ingresos</t>
+        </is>
+      </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21233,14 +21237,10 @@
           <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
-      <c r="E393" s="2" t="inlineStr">
-        <is>
-          <t>edad_actual_fecha_corte</t>
-        </is>
-      </c>
+      <c r="E393" s="2" t="inlineStr"/>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos ⇒ edad ≥ 16</t>
+          <t>Ingresos brutos anuales ≤ 1.000.000 €</t>
         </is>
       </c>
       <c r="G393" s="2" t="inlineStr">
@@ -21250,17 +21250,17 @@
       </c>
       <c r="H393" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+          <t>ingresos_bruto_total_2024 &gt; 1000000</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>Las pensiones de orfandad también constan como ingresos</t>
+          <t>Outliers (directivos)</t>
         </is>
       </c>
       <c r="K393" s="2" t="inlineStr">
@@ -21290,10 +21290,14 @@
           <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
-      <c r="E394" s="2" t="inlineStr"/>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>situacion_actual_afiliacion</t>
+        </is>
+      </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>Ingresos brutos anuales ≤ 1.000.000 €</t>
+          <t>Con ingresos, sin afiliación ni pensión ⇒ raro</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr">
@@ -21308,14 +21312,10 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 1000000</t>
-        </is>
-      </c>
-      <c r="J394" s="2" t="inlineStr">
-        <is>
-          <t>Outliers (directivos)</t>
-        </is>
-      </c>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND situacion_actual_afiliacion = 'Nunca_ha_cotizado' AND cobra_pension_2024_5 = 'NO'</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr"/>
       <c r="K394" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21345,27 +21345,27 @@
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos, sin afiliación ni pensión ⇒ raro</t>
+          <t>Con ingresos 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND situacion_actual_afiliacion = 'Nunca_ha_cotizado' AND cobra_pension_2024_5 = 'NO'</t>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr"/>
@@ -21393,32 +21393,32 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
+          <t>discap_fiscal</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
           <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
-      <c r="E396" s="2" t="inlineStr">
-        <is>
-          <t>fecha_fallecimiento</t>
-        </is>
-      </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Discapacidad fiscal ⇒ tiene registro de ingresos</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+          <t>discap_fiscal AND ingresos_bruto_total_2024 IS NULL</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr"/>
@@ -21446,17 +21446,17 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal</t>
+          <t>discap_afiliacion</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>fecha_ini_primer_empleo</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>Discapacidad fiscal ⇒ tiene registro de ingresos</t>
+          <t>Discapacidad en afiliación ⇒ tiene primer empleo</t>
         </is>
       </c>
       <c r="G397" s="2" t="inlineStr">
@@ -21466,12 +21466,12 @@
       </c>
       <c r="H397" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal AND ingresos_bruto_total_2024 IS NULL</t>
+          <t>discap_afiliacion AND fecha_ini_primer_empleo IS NULL</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr"/>
@@ -21494,22 +21494,22 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Datos fiscales y discapacidad</t>
+          <t>Nacionalidad y geografía</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion</t>
+          <t>nacionalidad</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>nacionalidad_agrupado</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>Discapacidad en afiliación ⇒ tiene primer empleo</t>
+          <t>Nacionalidad España ⇒ agrupado 'espana'</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion AND fecha_ini_primer_empleo IS NULL</t>
+          <t>nacionalidad LIKE 'N00%' AND nacionalidad_agrupado IS DISTINCT FROM 'espana'</t>
         </is>
       </c>
       <c r="J398" s="2" t="inlineStr"/>
@@ -21552,17 +21552,17 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
+          <t>nacionalidad_agrupado</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
           <t>nacionalidad</t>
         </is>
       </c>
-      <c r="E399" s="2" t="inlineStr">
-        <is>
-          <t>nacionalidad_agrupado</t>
-        </is>
-      </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>Nacionalidad España ⇒ agrupado 'espana'</t>
+          <t>Agrupado 'espana' ⇒ nacionalidad España</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad LIKE 'N00%' AND nacionalidad_agrupado IS DISTINCT FROM 'espana'</t>
+          <t>nacionalidad_agrupado = 'espana' AND nacionalidad NOT LIKE 'N00%'</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr"/>
@@ -21605,17 +21605,17 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado</t>
+          <t>pais_nacimiento</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad</t>
+          <t>pais_nacim_agrupado</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>Agrupado 'espana' ⇒ nacionalidad España</t>
+          <t>País de nacimiento España ⇒ agrupado 'espana'</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
@@ -21630,7 +21630,7 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado = 'espana' AND nacionalidad NOT LIKE 'N00%'</t>
+          <t>pais_nacimiento LIKE 'N00%' AND pais_nacim_agrupado IS DISTINCT FROM 'espana'</t>
         </is>
       </c>
       <c r="J400" s="2" t="inlineStr"/>
@@ -21658,17 +21658,17 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
+          <t>pais_nacim_agrupado</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
           <t>pais_nacimiento</t>
         </is>
       </c>
-      <c r="E401" s="2" t="inlineStr">
-        <is>
-          <t>pais_nacim_agrupado</t>
-        </is>
-      </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>País de nacimiento España ⇒ agrupado 'espana'</t>
+          <t>Agrupado 'espana' ⇒ país de nacimiento España</t>
         </is>
       </c>
       <c r="G401" s="2" t="inlineStr">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento LIKE 'N00%' AND pais_nacim_agrupado IS DISTINCT FROM 'espana'</t>
+          <t>pais_nacim_agrupado = 'espana' AND pais_nacimiento NOT LIKE 'N00%'</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr"/>
@@ -21711,17 +21711,17 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado</t>
+          <t>nacionalidad</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento</t>
+          <t>nacionalidad_agrupado</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>Agrupado 'espana' ⇒ país de nacimiento España</t>
+          <t>Cada código de nacionalidad pertenece a un único grupo</t>
         </is>
       </c>
       <c r="G402" s="2" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado = 'espana' AND pais_nacimiento NOT LIKE 'N00%'</t>
+          <t>nacionalidad IN (SELECT nacionalidad FROM personas GROUP BY 1 HAVING COUNT(DISTINCT nacionalidad_agrupado) &gt; 1)</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr"/>
@@ -21764,17 +21764,17 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad</t>
+          <t>pais_nacimiento</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado</t>
+          <t>pais_nacim_agrupado</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>Cada código de nacionalidad pertenece a un único grupo</t>
+          <t>Cada código de país de nacimiento pertenece a un único grupo</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad IN (SELECT nacionalidad FROM personas GROUP BY 1 HAVING COUNT(DISTINCT nacionalidad_agrupado) &gt; 1)</t>
+          <t>pais_nacimiento IN (SELECT pais_nacimiento FROM personas GROUP BY 1 HAVING COUNT(DISTINCT pais_nacim_agrupado) &gt; 1)</t>
         </is>
       </c>
       <c r="J403" s="2" t="inlineStr"/>
@@ -21817,17 +21817,17 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
+          <t>prov_nacimiento</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
           <t>pais_nacimiento</t>
         </is>
       </c>
-      <c r="E404" s="2" t="inlineStr">
-        <is>
-          <t>pais_nacim_agrupado</t>
-        </is>
-      </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>Cada código de país de nacimiento pertenece a un único grupo</t>
+          <t>Provincia de nacimiento española ⇒ país de nacimiento España</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr">
@@ -21837,12 +21837,12 @@
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento IN (SELECT pais_nacimiento FROM personas GROUP BY 1 HAVING COUNT(DISTINCT pais_nacim_agrupado) &gt; 1)</t>
+          <t>(prov_nacimiento IS NOT NULL AND prov_nacimiento NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND pais_nacimiento NOT LIKE 'N00%' AND pais_nacimiento &lt;&gt; 'NO CONSTA'</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr"/>
@@ -21870,32 +21870,28 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento</t>
-        </is>
-      </c>
-      <c r="E405" s="2" t="inlineStr">
-        <is>
-          <t>pais_nacimiento</t>
-        </is>
-      </c>
+          <t>sexo</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr"/>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>Provincia de nacimiento española ⇒ país de nacimiento España</t>
+          <t>sexo ∈ {Hombre, Mujer, NO CONSTA}</t>
         </is>
       </c>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>(prov_nacimiento IS NOT NULL AND prov_nacimiento NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND pais_nacimiento NOT LIKE 'N00%' AND pais_nacimiento &lt;&gt; 'NO CONSTA'</t>
+          <t>sexo IS NOT NULL AND sexo NOT IN ('Hombre','Mujer','NO CONSTA')</t>
         </is>
       </c>
       <c r="J405" s="2" t="inlineStr"/>
@@ -21923,13 +21919,13 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>domic_resid_habitual</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr"/>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>sexo ∈ {Hombre, Mujer, NO CONSTA}</t>
+          <t>El domicilio (INE) es NO CONSTA o 5 dígitos con provincia 01-52 (guía 1.007)</t>
         </is>
       </c>
       <c r="G406" s="2" t="inlineStr">
@@ -21944,7 +21940,7 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>sexo IS NOT NULL AND sexo NOT IN ('Hombre','Mujer','NO CONSTA')</t>
+          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND (NOT regexp_matches(domic_resid_habitual, '^[0-9]{5}$') OR CAST(left(domic_resid_habitual, 2) AS INTEGER) NOT BETWEEN 1 AND 52)</t>
         </is>
       </c>
       <c r="J406" s="2" t="inlineStr"/>
@@ -21972,28 +21968,32 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual</t>
-        </is>
-      </c>
-      <c r="E407" s="2" t="inlineStr"/>
+          <t>prov_1a_afiliacion</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>fecha_ini_primer_empleo</t>
+        </is>
+      </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>El domicilio (INE) es NO CONSTA o 5 dígitos con provincia 01-52 (guía 1.007)</t>
+          <t>Con primer empleo ⇒ provincia de primera afiliación conocida</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND (NOT regexp_matches(domic_resid_habitual, '^[0-9]{5}$') OR CAST(left(domic_resid_habitual, 2) AS INTEGER) NOT BETWEEN 1 AND 52)</t>
+          <t>fecha_ini_primer_empleo IS NOT NULL AND NOT (prov_1a_afiliacion IS NOT NULL AND prov_1a_afiliacion NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta'))</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr"/>
@@ -22016,22 +22016,22 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>Nacionalidad y geografía</t>
+          <t>Coherencia código→etiqueta</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>prov_1a_afiliacion</t>
+          <t>prov_trabajo_ppal</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>prov_fiscal_actual</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>Con primer empleo ⇒ provincia de primera afiliación conocida</t>
+          <t>Cada código de provincia tiene una única etiqueta en las 5 columnas de provincia</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
@@ -22041,12 +22041,12 @@
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo IS NOT NULL AND NOT (prov_1a_afiliacion IS NOT NULL AND prov_1a_afiliacion NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta'))</t>
+          <t>split_part(prov_trabajo_ppal, ' ', 1) IN (SELECT c FROM (SELECT split_part(p, ' ', 1) c, p FROM (SELECT prov_trabajo_ppal p FROM personas UNION ALL SELECT prov_fiscal_actual FROM personas UNION ALL SELECT prov_nacimiento FROM personas UNION ALL SELECT prov_1a_afiliacion FROM personas UNION ALL SELECT prov_resid_habitual FROM personas) WHERE p &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT p) &gt; 1)</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr"/>
@@ -22074,17 +22074,17 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal</t>
+          <t>act_econ_ppal</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual</t>
+          <t>act_econ_ult_baja</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>Cada código de provincia tiene una única etiqueta en las 5 columnas de provincia</t>
+          <t>Cada código CNAE tiene una única etiqueta en las 2 columnas de actividad</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>split_part(prov_trabajo_ppal, ' ', 1) IN (SELECT c FROM (SELECT split_part(p, ' ', 1) c, p FROM (SELECT prov_trabajo_ppal p FROM personas UNION ALL SELECT prov_fiscal_actual FROM personas UNION ALL SELECT prov_nacimiento FROM personas UNION ALL SELECT prov_1a_afiliacion FROM personas UNION ALL SELECT prov_resid_habitual FROM personas) WHERE p &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT p) &gt; 1)</t>
+          <t>split_part(act_econ_ppal, ' ', 1) IN (SELECT c FROM (SELECT split_part(a, ' ', 1) c, a FROM (SELECT act_econ_ppal a FROM personas UNION ALL SELECT act_econ_ult_baja FROM personas) WHERE a &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT a) &gt; 1)</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr"/>
@@ -22127,17 +22127,17 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja</t>
+          <t>causa_baja_trab_ppal</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>Cada código CNAE tiene una única etiqueta en las 2 columnas de actividad</t>
+          <t>Cada código de causa de baja tiene una única etiqueta en las 3 columnas de causa</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
@@ -22152,7 +22152,7 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>split_part(act_econ_ppal, ' ', 1) IN (SELECT c FROM (SELECT split_part(a, ' ', 1) c, a FROM (SELECT act_econ_ppal a FROM personas UNION ALL SELECT act_econ_ult_baja FROM personas) WHERE a &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT a) &gt; 1)</t>
+          <t>split_part(causa_ult_baja, ' ', 1) IN (SELECT c FROM (SELECT split_part(a, ' ', 1) c, a FROM (SELECT causa_ult_baja a FROM personas UNION ALL SELECT causa_baja_trab_ppal FROM personas UNION ALL SELECT causa_baja_mas_comun FROM personas) WHERE a &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT a) &gt; 1)</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr"/>
@@ -22180,17 +22180,13 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja</t>
-        </is>
-      </c>
-      <c r="E411" s="2" t="inlineStr">
-        <is>
-          <t>causa_baja_trab_ppal</t>
-        </is>
-      </c>
+          <t>grupo_cotiz_ppal</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr"/>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>Cada código de causa de baja tiene una única etiqueta en las 3 columnas de causa</t>
+          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_cotiz_ppal</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
@@ -22205,7 +22201,7 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>split_part(causa_ult_baja, ' ', 1) IN (SELECT c FROM (SELECT split_part(a, ' ', 1) c, a FROM (SELECT causa_ult_baja a FROM personas UNION ALL SELECT causa_baja_trab_ppal FROM personas UNION ALL SELECT causa_baja_mas_comun FROM personas) WHERE a &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT a) &gt; 1)</t>
+          <t>split_part(grupo_cotiz_ppal, ' ', 1) IN (SELECT split_part(grupo_cotiz_ppal, ' ', 1) FROM personas WHERE grupo_cotiz_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_ppal) &gt; 1)</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr"/>
@@ -22233,13 +22229,13 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr"/>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_cotiz_ppal</t>
+          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
@@ -22254,7 +22250,7 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_cotiz_ppal, ' ', 1) IN (SELECT split_part(grupo_cotiz_ppal, ' ', 1) FROM personas WHERE grupo_cotiz_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_ppal) &gt; 1)</t>
+          <t>split_part(grupo_ultimo_empleo, ' ', 1) IN (SELECT split_part(grupo_ultimo_empleo, ' ', 1) FROM personas WHERE grupo_ultimo_empleo &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_ultimo_empleo) &gt; 1)</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr"/>
@@ -22282,13 +22278,13 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo</t>
+          <t>grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr"/>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_ultimo_empleo</t>
+          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
@@ -22303,7 +22299,7 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_ultimo_empleo, ' ', 1) IN (SELECT split_part(grupo_ultimo_empleo, ' ', 1) FROM personas WHERE grupo_ultimo_empleo &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_ultimo_empleo) &gt; 1)</t>
+          <t>split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) IN (SELECT split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) FROM personas WHERE grupo_cotiz_1er_empleo_signif &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_1er_empleo_signif) &gt; 1)</t>
         </is>
       </c>
       <c r="J413" s="2" t="inlineStr"/>
@@ -22326,23 +22322,23 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Coherencia código→etiqueta</t>
+          <t>Dominio de valores (guía)</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif</t>
+          <t>grupo_cotiz_ppal</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr"/>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_cotiz_1er_empleo_signif</t>
+          <t>grupo_cotiz_ppal solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -22352,7 +22348,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) IN (SELECT split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) FROM personas WHERE grupo_cotiz_1er_empleo_signif &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_1er_empleo_signif) &gt; 1)</t>
+          <t>grupo_cotiz_ppal IS NOT NULL AND NOT regexp_matches(grupo_cotiz_ppal, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr"/>
@@ -22380,13 +22376,13 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr"/>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
+          <t>grupo_ultimo_empleo solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
@@ -22401,7 +22397,7 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal IS NOT NULL AND NOT regexp_matches(grupo_cotiz_ppal, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
+          <t>grupo_ultimo_empleo IS NOT NULL AND NOT regexp_matches(grupo_ultimo_empleo, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr"/>
@@ -22429,13 +22425,13 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo</t>
+          <t>grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr"/>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
+          <t>grupo_cotiz_1er_empleo_signif solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
@@ -22450,7 +22446,7 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo IS NOT NULL AND NOT regexp_matches(grupo_ultimo_empleo, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
+          <t>grupo_cotiz_1er_empleo_signif IS NOT NULL AND NOT regexp_matches(grupo_cotiz_1er_empleo_signif, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr"/>
@@ -22478,13 +22474,13 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif</t>
+          <t>reg_cotiz_ppal_agrupado</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr"/>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
+          <t>reg_cotiz_ppal_agrupado solo toma los regímenes 01, 0138, 05, 06, 07, 08, 09, 12</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
@@ -22499,7 +22495,7 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif IS NOT NULL AND NOT regexp_matches(grupo_cotiz_1er_empleo_signif, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
+          <t>reg_cotiz_ppal_agrupado IS NOT NULL AND NOT regexp_matches(reg_cotiz_ppal_agrupado, '^(01|0138|05|06|07|08|09|12) .+')</t>
         </is>
       </c>
       <c r="J417" s="2" t="inlineStr"/>
@@ -22527,18 +22523,18 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado</t>
+          <t>tipo_contr_ppal_agrupado</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr"/>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado solo toma los regímenes 01, 0138, 05, 06, 07, 08, 09, 12</t>
+          <t>tipo_contr_ppal_agrupado solo toma las 7 categorías de tipo de contrato</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -22548,7 +22544,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado IS NOT NULL AND NOT regexp_matches(reg_cotiz_ppal_agrupado, '^(01|0138|05|06|07|08|09|12) .+')</t>
+          <t>tipo_contr_ppal_agrupado IS NOT NULL AND tipo_contr_ppal_agrupado NOT IN ('Indefinido_t_completo','No consta','Temporal_t_completo','Indefinido_t_parcial','Temporal_t_parcial','Indefinido_fijo_discontinuo','Otros')</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr"/>
@@ -22576,13 +22572,13 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado</t>
+          <t>tipo_contr_ult_baja</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr"/>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado solo toma las 7 categorías de tipo de contrato</t>
+          <t>tipo_contr_ult_baja solo toma las 7 categorías de tipo de contrato</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
@@ -22597,7 +22593,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado IS NOT NULL AND tipo_contr_ppal_agrupado NOT IN ('Indefinido_t_completo','No consta','Temporal_t_completo','Indefinido_t_parcial','Temporal_t_parcial','Indefinido_fijo_discontinuo','Otros')</t>
+          <t>tipo_contr_ult_baja IS NOT NULL AND tipo_contr_ult_baja NOT IN ('Indefinido_t_completo','No consta','Temporal_t_completo','Indefinido_t_parcial','Temporal_t_parcial','Indefinido_fijo_discontinuo','Otros')</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr"/>
@@ -22625,18 +22621,18 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ult_baja</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr"/>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ult_baja solo toma las 7 categorías de tipo de contrato</t>
+          <t>causa_ult_baja solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -22646,7 +22642,7 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ult_baja IS NOT NULL AND tipo_contr_ult_baja NOT IN ('Indefinido_t_completo','No consta','Temporal_t_completo','Indefinido_t_parcial','Temporal_t_parcial','Indefinido_fijo_discontinuo','Otros')</t>
+          <t>causa_ult_baja IS NOT NULL AND causa_ult_baja &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_ult_baja, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr"/>
@@ -22674,13 +22670,13 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja</t>
+          <t>causa_baja_trab_ppal</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr"/>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
+          <t>causa_baja_trab_ppal solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr">
@@ -22695,7 +22691,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja IS NOT NULL AND causa_ult_baja &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_ult_baja, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
+          <t>causa_baja_trab_ppal IS NOT NULL AND causa_baja_trab_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_baja_trab_ppal, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr"/>
@@ -22723,13 +22719,13 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_trab_ppal</t>
+          <t>causa_baja_mas_comun</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr"/>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_trab_ppal solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
+          <t>causa_baja_mas_comun solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
         </is>
       </c>
       <c r="G422" s="2" t="inlineStr">
@@ -22744,7 +22740,7 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_trab_ppal IS NOT NULL AND causa_baja_trab_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_baja_trab_ppal, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
+          <t>causa_baja_mas_comun IS NOT NULL AND causa_baja_mas_comun &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_baja_mas_comun, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr"/>
@@ -22772,18 +22768,18 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_mas_comun</t>
+          <t>act_econ_ppal</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr"/>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_mas_comun solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
+          <t>act_econ_ppal = 'NNN texto' (CNAE 3 dígitos) o NO CONSTA</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -22793,7 +22789,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_mas_comun IS NOT NULL AND causa_baja_mas_comun &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_baja_mas_comun, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
+          <t>act_econ_ppal IS NOT NULL AND act_econ_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(act_econ_ppal, '^[0-9]{3} .+')</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr"/>
@@ -22821,13 +22817,13 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal</t>
+          <t>act_econ_ult_baja</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr"/>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal = 'NNN texto' (CNAE 3 dígitos) o NO CONSTA</t>
+          <t>act_econ_ult_baja = 'NNN texto' (CNAE 3 dígitos) o NO CONSTA</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr">
@@ -22842,7 +22838,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal IS NOT NULL AND act_econ_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(act_econ_ppal, '^[0-9]{3} .+')</t>
+          <t>act_econ_ult_baja IS NOT NULL AND act_econ_ult_baja &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(act_econ_ult_baja, '^[0-9]{3} .+')</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr"/>
@@ -22870,13 +22866,13 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja</t>
+          <t>prov_trabajo_ppal</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr"/>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja = 'NNN texto' (CNAE 3 dígitos) o NO CONSTA</t>
+          <t>prov_trabajo_ppal = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
@@ -22891,7 +22887,7 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja IS NOT NULL AND act_econ_ult_baja &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(act_econ_ult_baja, '^[0-9]{3} .+')</t>
+          <t>prov_trabajo_ppal IS NOT NULL AND prov_trabajo_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_trabajo_ppal, '^[0-9]{2} .+')</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr"/>
@@ -22919,13 +22915,13 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal</t>
+          <t>prov_fiscal_actual</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr"/>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_fiscal_actual = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
@@ -22940,7 +22936,7 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal IS NOT NULL AND prov_trabajo_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_trabajo_ppal, '^[0-9]{2} .+')</t>
+          <t>prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_fiscal_actual, '^[0-9]{2} .+')</t>
         </is>
       </c>
       <c r="J426" s="2" t="inlineStr"/>
@@ -22968,13 +22964,13 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual</t>
+          <t>prov_nacimiento</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr"/>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_nacimiento = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G427" s="2" t="inlineStr">
@@ -22989,7 +22985,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_fiscal_actual, '^[0-9]{2} .+')</t>
+          <t>prov_nacimiento IS NOT NULL AND prov_nacimiento &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_nacimiento, '^[0-9]{2} .+')</t>
         </is>
       </c>
       <c r="J427" s="2" t="inlineStr"/>
@@ -23017,13 +23013,13 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento</t>
+          <t>prov_1a_afiliacion</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr"/>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_1a_afiliacion = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G428" s="2" t="inlineStr">
@@ -23038,7 +23034,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento IS NOT NULL AND prov_nacimiento &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_nacimiento, '^[0-9]{2} .+')</t>
+          <t>prov_1a_afiliacion IS NOT NULL AND prov_1a_afiliacion &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_1a_afiliacion, '^[0-9]{2} .+')</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr"/>
@@ -23066,13 +23062,13 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>prov_1a_afiliacion</t>
+          <t>prov_resid_habitual</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr"/>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>prov_1a_afiliacion = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_resid_habitual = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G429" s="2" t="inlineStr">
@@ -23087,7 +23083,7 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>prov_1a_afiliacion IS NOT NULL AND prov_1a_afiliacion &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_1a_afiliacion, '^[0-9]{2} .+')</t>
+          <t>prov_resid_habitual IS NOT NULL AND prov_resid_habitual &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_resid_habitual, '^[0-9]{2} .+')</t>
         </is>
       </c>
       <c r="J429" s="2" t="inlineStr"/>
@@ -23115,13 +23111,13 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual</t>
+          <t>nacionalidad_agrupado</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr"/>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>nacionalidad_agrupado ∈ 5 grupos conocidos</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
@@ -23136,7 +23132,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual IS NOT NULL AND prov_resid_habitual &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_resid_habitual, '^[0-9]{2} .+')</t>
+          <t>nacionalidad_agrupado IS NOT NULL AND nacionalidad_agrupado NOT IN ('espana','paises_UE_UK','paises_latinos','paises_africanos','paises_lejanos')</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr"/>
@@ -23164,13 +23160,13 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado</t>
+          <t>pais_nacim_agrupado</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr"/>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado ∈ 5 grupos conocidos</t>
+          <t>pais_nacim_agrupado ∈ 5 grupos conocidos</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
@@ -23185,7 +23181,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado IS NOT NULL AND nacionalidad_agrupado NOT IN ('espana','paises_UE_UK','paises_latinos','paises_africanos','paises_lejanos')</t>
+          <t>pais_nacim_agrupado IS NOT NULL AND pais_nacim_agrupado NOT IN ('espana','paises_UE_UK','paises_latinos','paises_africanos','paises_lejanos')</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr"/>
@@ -23213,13 +23209,13 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr"/>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado ∈ 5 grupos conocidos</t>
+          <t>cobra_pension_2024_5 ∈ {SI, NO}</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
@@ -23234,7 +23230,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado IS NOT NULL AND pais_nacim_agrupado NOT IN ('espana','paises_UE_UK','paises_latinos','paises_africanos','paises_lejanos')</t>
+          <t>cobra_pension_2024_5 NOT IN ('SI','NO')</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr"/>
@@ -23262,13 +23258,13 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>ha_fallecido</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr"/>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 ∈ {SI, NO}</t>
+          <t>ha_fallecido ∈ {SI, NO}</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
@@ -23283,7 +23279,7 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 NOT IN ('SI','NO')</t>
+          <t>ha_fallecido NOT IN ('SI','NO')</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr"/>
@@ -23311,13 +23307,13 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido</t>
+          <t>situacion_actual_afiliacion</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr"/>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido ∈ {SI, NO}</t>
+          <t>situacion_actual_afiliacion ∈ 9 categorías conocidas</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
@@ -23332,7 +23328,7 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido NOT IN ('SI','NO')</t>
+          <t>situacion_actual_afiliacion NOT IN ('Alta_ocupado','Baja_de_actividad','Baja_para_pension','Baja_de_prestacion','Nunca_ha_cotizado','Baja_de_subsidio','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52','Asimilado_otros')</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr"/>
@@ -23360,13 +23356,13 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion</t>
+          <t>situacion_paro_ocupacion</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr"/>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion ∈ 9 categorías conocidas</t>
+          <t>situacion_paro_ocupacion ∈ 7 categorías conocidas</t>
         </is>
       </c>
       <c r="G435" s="2" t="inlineStr">
@@ -23381,7 +23377,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion NOT IN ('Alta_ocupado','Baja_de_actividad','Baja_para_pension','Baja_de_prestacion','Nunca_ha_cotizado','Baja_de_subsidio','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52','Asimilado_otros')</t>
+          <t>situacion_paro_ocupacion NOT IN ('Ocupado','Ocupado_y_pensionista','Pensionista','Parado_LD','Parado_LD_y_pensionista','Parado_NoLD','Parado_NoLD_y_pensionista')</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr"/>
@@ -23404,18 +23400,18 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Dominio de valores (guía)</t>
+          <t>Campos obligatorios no nulos</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion</t>
+          <t>ipf</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr"/>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion ∈ 7 categorías conocidas</t>
+          <t>ipf no puede ser nulo</t>
         </is>
       </c>
       <c r="G436" s="2" t="inlineStr">
@@ -23430,7 +23426,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion NOT IN ('Ocupado','Ocupado_y_pensionista','Pensionista','Parado_LD','Parado_LD_y_pensionista','Parado_NoLD','Parado_NoLD_y_pensionista')</t>
+          <t>ipf IS NULL</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr"/>
@@ -23458,13 +23454,13 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>ipf</t>
+          <t>fecha_nacimiento</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr"/>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>ipf no puede ser nulo</t>
+          <t>fecha_nacimiento no puede ser nulo</t>
         </is>
       </c>
       <c r="G437" s="2" t="inlineStr">
@@ -23479,7 +23475,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>ipf IS NULL</t>
+          <t>fecha_nacimiento IS NULL</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr"/>
@@ -23507,13 +23503,13 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>fecha_nacimiento</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr"/>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>fecha_nacimiento no puede ser nulo</t>
+          <t>sexo no puede ser nulo</t>
         </is>
       </c>
       <c r="G438" s="2" t="inlineStr">
@@ -23528,7 +23524,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>fecha_nacimiento IS NULL</t>
+          <t>sexo IS NULL</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr"/>
@@ -23556,13 +23552,13 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr"/>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>sexo no puede ser nulo</t>
+          <t>edad_actual_fecha_corte no puede ser nulo</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr">
@@ -23577,7 +23573,7 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>sexo IS NULL</t>
+          <t>edad_actual_fecha_corte IS NULL</t>
         </is>
       </c>
       <c r="J439" s="2" t="inlineStr"/>
@@ -23605,13 +23601,13 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>situacion_actual_afiliacion</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr"/>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte no puede ser nulo</t>
+          <t>situacion_actual_afiliacion no puede ser nulo</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr">
@@ -23626,7 +23622,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte IS NULL</t>
+          <t>situacion_actual_afiliacion IS NULL</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr"/>
@@ -23654,13 +23650,13 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion</t>
+          <t>situacion_paro_ocupacion</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr"/>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion no puede ser nulo</t>
+          <t>situacion_paro_ocupacion no puede ser nulo</t>
         </is>
       </c>
       <c r="G441" s="2" t="inlineStr">
@@ -23675,7 +23671,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion IS NULL</t>
+          <t>situacion_paro_ocupacion IS NULL</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr"/>
@@ -23703,13 +23699,13 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion</t>
+          <t>nacionalidad</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr"/>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion no puede ser nulo</t>
+          <t>nacionalidad no puede ser nulo</t>
         </is>
       </c>
       <c r="G442" s="2" t="inlineStr">
@@ -23724,7 +23720,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion IS NULL</t>
+          <t>nacionalidad IS NULL</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr"/>
@@ -23752,13 +23748,13 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad</t>
+          <t>pais_nacimiento</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr"/>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad no puede ser nulo</t>
+          <t>pais_nacimiento no puede ser nulo</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
@@ -23773,7 +23769,7 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad IS NULL</t>
+          <t>pais_nacimiento IS NULL</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr"/>
@@ -23801,13 +23797,13 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento</t>
+          <t>prov_nacimiento</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr"/>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento no puede ser nulo</t>
+          <t>prov_nacimiento no puede ser nulo</t>
         </is>
       </c>
       <c r="G444" s="2" t="inlineStr">
@@ -23822,7 +23818,7 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento IS NULL</t>
+          <t>prov_nacimiento IS NULL</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr"/>
@@ -23850,13 +23846,13 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr"/>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento no puede ser nulo</t>
+          <t>cobra_pension_2024_5 no puede ser nulo</t>
         </is>
       </c>
       <c r="G445" s="2" t="inlineStr">
@@ -23871,7 +23867,7 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento IS NULL</t>
+          <t>cobra_pension_2024_5 IS NULL</t>
         </is>
       </c>
       <c r="J445" s="2" t="inlineStr"/>
@@ -23899,13 +23895,13 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>discap_afiliacion</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr"/>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 no puede ser nulo</t>
+          <t>discap_afiliacion no puede ser nulo</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr">
@@ -23920,7 +23916,7 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 IS NULL</t>
+          <t>discap_afiliacion IS NULL</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr"/>
@@ -23948,13 +23944,13 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion</t>
+          <t>discap_pension</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr"/>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion no puede ser nulo</t>
+          <t>discap_pension no puede ser nulo</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
@@ -23969,7 +23965,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion IS NULL</t>
+          <t>discap_pension IS NULL</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr"/>
@@ -23997,13 +23993,13 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>discap_pension</t>
+          <t>discap_fiscal</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr"/>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>discap_pension no puede ser nulo</t>
+          <t>discap_fiscal no puede ser nulo</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
@@ -24018,7 +24014,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>discap_pension IS NULL</t>
+          <t>discap_fiscal IS NULL</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr"/>
@@ -24046,13 +24042,13 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal</t>
+          <t>domic_resid_habitual</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr"/>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal no puede ser nulo</t>
+          <t>domic_resid_habitual no puede ser nulo</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
@@ -24067,7 +24063,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal IS NULL</t>
+          <t>domic_resid_habitual IS NULL</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr"/>
@@ -24095,13 +24091,13 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual</t>
+          <t>prov_resid_habitual</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr"/>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual no puede ser nulo</t>
+          <t>prov_resid_habitual no puede ser nulo</t>
         </is>
       </c>
       <c r="G450" s="2" t="inlineStr">
@@ -24116,7 +24112,7 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual IS NULL</t>
+          <t>prov_resid_habitual IS NULL</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr"/>
@@ -24144,13 +24140,13 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual</t>
+          <t>ha_fallecido</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr"/>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual no puede ser nulo</t>
+          <t>ha_fallecido no puede ser nulo</t>
         </is>
       </c>
       <c r="G451" s="2" t="inlineStr">
@@ -24165,7 +24161,7 @@
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual IS NULL</t>
+          <t>ha_fallecido IS NULL</t>
         </is>
       </c>
       <c r="J451" s="2" t="inlineStr"/>
@@ -24193,13 +24189,13 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido</t>
+          <t>clave_subclave_ppal</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr"/>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido no puede ser nulo</t>
+          <t>clave_subclave_ppal no puede ser nulo</t>
         </is>
       </c>
       <c r="G452" s="2" t="inlineStr">
@@ -24214,7 +24210,7 @@
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido IS NULL</t>
+          <t>clave_subclave_ppal IS NULL</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr"/>
@@ -24242,13 +24238,13 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal</t>
+          <t>ipf</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr"/>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal no puede ser nulo</t>
+          <t>ipf es único (una fila por persona)</t>
         </is>
       </c>
       <c r="G453" s="2" t="inlineStr">
@@ -24263,7 +24259,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal IS NULL</t>
+          <t>ipf IN (SELECT ipf FROM personas GROUP BY 1 HAVING COUNT(*) &gt; 1)</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr"/>
@@ -24286,36 +24282,44 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Campos obligatorios no nulos</t>
+          <t>Régimen de cotización</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>ipf</t>
-        </is>
-      </c>
-      <c r="E454" s="2" t="inlineStr"/>
+          <t>reg_cotiz_ppal_agrupado</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>act_econ_ppal</t>
+        </is>
+      </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>ipf es único (una fila por persona)</t>
+          <t>R.E. Agrario cuenta ajena ⇒ actividad agraria/forestal/pesquera (CNAE 01-03)</t>
         </is>
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>ipf IN (SELECT ipf FROM personas GROUP BY 1 HAVING COUNT(*) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J454" s="2" t="inlineStr"/>
+          <t>reg_cotiz_ppal_agrupado LIKE '06 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '01%' OR act_econ_ppal LIKE '02%' OR act_econ_ppal LIKE '03%')</t>
+        </is>
+      </c>
+      <c r="J454" s="2" t="inlineStr">
+        <is>
+          <t>La actividad principal puede ser de otro periodo</t>
+        </is>
+      </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24350,7 +24354,7 @@
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>R.E. Agrario cuenta ajena ⇒ actividad agraria/forestal/pesquera (CNAE 01-03)</t>
+          <t>R.E. Agrario cuenta propia ⇒ actividad agraria (CNAE 01-03)</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
@@ -24365,14 +24369,10 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '06 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '01%' OR act_econ_ppal LIKE '02%' OR act_econ_ppal LIKE '03%')</t>
-        </is>
-      </c>
-      <c r="J455" s="2" t="inlineStr">
-        <is>
-          <t>La actividad principal puede ser de otro periodo</t>
-        </is>
-      </c>
+          <t>reg_cotiz_ppal_agrupado LIKE '07 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '01%' OR act_econ_ppal LIKE '02%' OR act_econ_ppal LIKE '03%')</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr"/>
       <c r="K455" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24407,7 +24407,7 @@
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>R.E. Agrario cuenta propia ⇒ actividad agraria (CNAE 01-03)</t>
+          <t>R.E. Empleados de Hogar ⇒ CNAE 970 (hogares como empleadores)</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
@@ -24417,12 +24417,12 @@
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '07 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '01%' OR act_econ_ppal LIKE '02%' OR act_econ_ppal LIKE '03%')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '970%'</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr"/>
@@ -24460,7 +24460,7 @@
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>R.E. Empleados de Hogar ⇒ CNAE 970 (hogares como empleadores)</t>
+          <t>Régimen General (S.E.C. Empleados de Hogar) ⇒ CNAE 970</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '970%'</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '0138 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '970%'</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr"/>
@@ -24513,7 +24513,7 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>Régimen General (S.E.C. Empleados de Hogar) ⇒ CNAE 970</t>
+          <t>R.E. del Mar ⇒ pesca o transporte marítimo (CNAE 03/50)</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
@@ -24523,12 +24523,12 @@
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '0138 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '970%'</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '08 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '03%' OR act_econ_ppal LIKE '50%')</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>R.E. del Mar ⇒ pesca o transporte marítimo (CNAE 03/50)</t>
+          <t>R.E. Minería del Carbón ⇒ CNAE 05 (extracción de carbón)</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
@@ -24576,12 +24576,12 @@
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '08 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '03%' OR act_econ_ppal LIKE '50%')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '09 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '05%'</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr"/>
@@ -24614,27 +24614,27 @@
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal</t>
+          <t>grupo_cotiz_ppal</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>R.E. Minería del Carbón ⇒ CNAE 05 (extracción de carbón)</t>
+          <t>R.E. Autónomos ⇒ sin grupo de cotización (guía 2.003)</t>
         </is>
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '09 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '05%'</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '05 %' AND grupo_cotiz_ppal NOT IN ('0 NO CONSTA','NO CONSTA')</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr"/>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>R.E. Autónomos ⇒ sin grupo de cotización (guía 2.003)</t>
+          <t>R.E. Empleados de Hogar ⇒ sin grupo de cotización (guía 2.003)</t>
         </is>
       </c>
       <c r="G461" s="2" t="inlineStr">
@@ -24687,7 +24687,7 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '05 %' AND grupo_cotiz_ppal NOT IN ('0 NO CONSTA','NO CONSTA')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND grupo_cotiz_ppal NOT IN ('0 NO CONSTA','NO CONSTA')</t>
         </is>
       </c>
       <c r="J461" s="2" t="inlineStr"/>
@@ -24720,27 +24720,27 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal</t>
+          <t>tipo_contr_ppal_agrupado</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>R.E. Empleados de Hogar ⇒ sin grupo de cotización (guía 2.003)</t>
+          <t>R.E. Autónomos ⇒ sin tipo de contrato ('No consta')</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND grupo_cotiz_ppal NOT IN ('0 NO CONSTA','NO CONSTA')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '05 %' AND tipo_contr_ppal_agrupado NOT IN ('No consta')</t>
         </is>
       </c>
       <c r="J462" s="2" t="inlineStr"/>
@@ -24773,17 +24773,17 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado</t>
+          <t>t_tot_reg_ppal</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>R.E. Autónomos ⇒ sin tipo de contrato ('No consta')</t>
+          <t>R.E. Agrario cuenta propia (extinguido en 2008) ⇒ ≤ 41,5 años en ese régimen (1967-2008)</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -24793,7 +24793,7 @@
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '05 %' AND tipo_contr_ppal_agrupado NOT IN ('No consta')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '07 %' AND t_tot_reg_ppal &gt; 41.5</t>
         </is>
       </c>
       <c r="J463" s="2" t="inlineStr"/>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>R.E. Agrario cuenta propia (extinguido en 2008) ⇒ ≤ 41,5 años en ese régimen (1967-2008)</t>
+          <t>R.E. Agrario cuenta ajena (integrado en 2012) ⇒ ≤ 45,5 años en ese régimen</t>
         </is>
       </c>
       <c r="G464" s="2" t="inlineStr">
@@ -24846,7 +24846,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '07 %' AND t_tot_reg_ppal &gt; 41.5</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '06 %' AND t_tot_reg_ppal &gt; 45.5</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr"/>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>R.E. Agrario cuenta ajena (integrado en 2012) ⇒ ≤ 45,5 años en ese régimen</t>
+          <t>R.E. Empleados de Hogar (integrado en 2012) ⇒ ≤ 45,5 años</t>
         </is>
       </c>
       <c r="G465" s="2" t="inlineStr">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '06 %' AND t_tot_reg_ppal &gt; 45.5</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND t_tot_reg_ppal &gt; 45.5</t>
         </is>
       </c>
       <c r="J465" s="2" t="inlineStr"/>
@@ -24937,7 +24937,7 @@
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>R.E. Empleados de Hogar (integrado en 2012) ⇒ ≤ 45,5 años</t>
+          <t>Régimen General (S.E.C. Hogar), creado en 2012 ⇒ ≤ 13,5 años</t>
         </is>
       </c>
       <c r="G466" s="2" t="inlineStr">
@@ -24947,12 +24947,12 @@
       </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND t_tot_reg_ppal &gt; 45.5</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '0138 %' AND t_tot_reg_ppal &gt; 13.5</t>
         </is>
       </c>
       <c r="J466" s="2" t="inlineStr"/>
@@ -24975,22 +24975,22 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>Régimen de cotización</t>
+          <t>Grupo de cotización × edad</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado</t>
+          <t>grupo_cotiz_ppal</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal</t>
+          <t>t_tot_grupo_ppal</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>Régimen General (S.E.C. Hogar), creado en 2012 ⇒ ≤ 13,5 años</t>
+          <t>Grupo 11 (menores de 18) ⇒ ≤ 2,1 años en ese grupo (16-18 años)</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '0138 %' AND t_tot_reg_ppal &gt; 13.5</t>
+          <t>grupo_cotiz_ppal LIKE '11 %' AND t_tot_grupo_ppal &gt; 2.1</t>
         </is>
       </c>
       <c r="J467" s="2" t="inlineStr"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>Grupo 11 (menores de 18) ⇒ ≤ 2,1 años en ese grupo (16-18 años)</t>
+          <t>Grupo 12 (menores de 17) ⇒ ≤ 1,1 años en ese grupo</t>
         </is>
       </c>
       <c r="G468" s="2" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal LIKE '11 %' AND t_tot_grupo_ppal &gt; 2.1</t>
+          <t>grupo_cotiz_ppal LIKE '12 %' AND t_tot_grupo_ppal &gt; 1.1</t>
         </is>
       </c>
       <c r="J468" s="2" t="inlineStr"/>
@@ -25086,17 +25086,17 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal</t>
+          <t>edad_ultimo_empleo</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>Grupo 12 (menores de 17) ⇒ ≤ 1,1 años en ese grupo</t>
+          <t>Último empleo en grupo 11 ⇒ edad del último empleo &lt; 18</t>
         </is>
       </c>
       <c r="G469" s="2" t="inlineStr">
@@ -25111,7 +25111,7 @@
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal LIKE '12 %' AND t_tot_grupo_ppal &gt; 1.1</t>
+          <t>grupo_ultimo_empleo LIKE '11 %' AND edad_ultimo_empleo &gt;= 18.1</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr"/>
@@ -25149,7 +25149,7 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>Último empleo en grupo 11 ⇒ edad del último empleo &lt; 18</t>
+          <t>Último empleo en grupo 12 ⇒ edad del último empleo &lt; 17</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr">
@@ -25164,7 +25164,7 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo LIKE '11 %' AND edad_ultimo_empleo &gt;= 18.1</t>
+          <t>grupo_ultimo_empleo LIKE '12 %' AND edad_ultimo_empleo &gt;= 17.1</t>
         </is>
       </c>
       <c r="J470" s="2" t="inlineStr"/>
@@ -25192,17 +25192,17 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo</t>
+          <t>grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>edad_ultimo_empleo</t>
+          <t>edad_primer_empleo_signif</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>Último empleo en grupo 12 ⇒ edad del último empleo &lt; 17</t>
+          <t>Primer empleo en grupo 11 ⇒ edad &lt; 18</t>
         </is>
       </c>
       <c r="G471" s="2" t="inlineStr">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo LIKE '12 %' AND edad_ultimo_empleo &gt;= 17.1</t>
+          <t>grupo_cotiz_1er_empleo_signif LIKE '11 %' AND edad_primer_empleo_signif &gt;= 18.1</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr"/>
@@ -25255,7 +25255,7 @@
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo en grupo 11 ⇒ edad &lt; 18</t>
+          <t>Primer empleo en grupo 12 ⇒ edad &lt; 17</t>
         </is>
       </c>
       <c r="G472" s="2" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif LIKE '11 %' AND edad_primer_empleo_signif &gt;= 18.1</t>
+          <t>grupo_cotiz_1er_empleo_signif LIKE '12 %' AND edad_primer_empleo_signif &gt;= 17.1</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr"/>
@@ -25298,17 +25298,17 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>edad_primer_empleo_signif</t>
+          <t>edad_ultimo_empleo</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo en grupo 12 ⇒ edad &lt; 17</t>
+          <t>Último empleo en grupo 10 ('mayores de 18') ⇒ edad ≥ 18</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
@@ -25318,12 +25318,12 @@
       </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif LIKE '12 %' AND edad_primer_empleo_signif &gt;= 17.1</t>
+          <t>grupo_ultimo_empleo LIKE '10 %' AND edad_ultimo_empleo &lt; 17.9</t>
         </is>
       </c>
       <c r="J473" s="2" t="inlineStr"/>
@@ -25351,17 +25351,17 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo</t>
+          <t>grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>edad_ultimo_empleo</t>
+          <t>edad_primer_empleo_signif</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>Último empleo en grupo 10 ('mayores de 18') ⇒ edad ≥ 18</t>
+          <t>Primer empleo en grupo 10 ('mayores de 18') ⇒ edad ≥ 18</t>
         </is>
       </c>
       <c r="G474" s="2" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo LIKE '10 %' AND edad_ultimo_empleo &lt; 17.9</t>
+          <t>grupo_cotiz_1er_empleo_signif LIKE '10 %' AND edad_primer_empleo_signif &lt; 17.9</t>
         </is>
       </c>
       <c r="J474" s="2" t="inlineStr"/>
@@ -25414,22 +25414,22 @@
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo en grupo 10 ('mayores de 18') ⇒ edad ≥ 18</t>
+          <t>Primer empleo como ingeniero/licenciado (grupo 1) ⇒ edad ≥ 18</t>
         </is>
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif LIKE '10 %' AND edad_primer_empleo_signif &lt; 17.9</t>
+          <t>grupo_cotiz_1er_empleo_signif LIKE '1 %' AND edad_primer_empleo_signif &lt; 18</t>
         </is>
       </c>
       <c r="J475" s="2" t="inlineStr"/>
@@ -25452,22 +25452,18 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>Grupo de cotización × edad</t>
+          <t>cotizado_anual_promedio (€/año)</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif</t>
-        </is>
-      </c>
-      <c r="E476" s="2" t="inlineStr">
-        <is>
-          <t>edad_primer_empleo_signif</t>
-        </is>
-      </c>
+          <t>cotizado_anual_promedio</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr"/>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo como ingeniero/licenciado (grupo 1) ⇒ edad ≥ 18</t>
+          <t>Cotizado anual promedio ≤ 100.000 €/año (la base máxima ronda 57.000 €/año)</t>
         </is>
       </c>
       <c r="G476" s="2" t="inlineStr">
@@ -25482,10 +25478,14 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif LIKE '1 %' AND edad_primer_empleo_signif &lt; 18</t>
-        </is>
-      </c>
-      <c r="J476" s="2" t="inlineStr"/>
+          <t>cotizado_anual_promedio &gt; 100000</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>Unidad: euros por año cotizado (confirmado por el usuario); el pluriempleo puede sumar bases</t>
+        </is>
+      </c>
       <c r="K476" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25516,7 +25516,7 @@
       <c r="E477" s="2" t="inlineStr"/>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>Cotizado anual promedio ≤ 100.000 €/año (la base máxima ronda 57.000 €/año)</t>
+          <t>Si es positivo, no es inferior a 100 €/año</t>
         </is>
       </c>
       <c r="G477" s="2" t="inlineStr">
@@ -25531,12 +25531,12 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio &gt; 100000</t>
+          <t>cotizado_anual_promedio &gt; 0 AND cotizado_anual_promedio &lt; 100</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
         <is>
-          <t>Unidad: euros por año cotizado (confirmado por el usuario); el pluriempleo puede sumar bases</t>
+          <t>Bases muy bajas por episodios mínimos o errores de conversión (céntimos/100)</t>
         </is>
       </c>
       <c r="K477" s="2" t="inlineStr">
@@ -25566,30 +25566,34 @@
           <t>cotizado_anual_promedio</t>
         </is>
       </c>
-      <c r="E478" s="2" t="inlineStr"/>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>t_total_empleo</t>
+        </is>
+      </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>Si es positivo, no es inferior a 100 €/año</t>
+          <t>Con tiempo de empleo &gt; 0 ⇒ cotizado_anual_promedio informado</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio &gt; 0 AND cotizado_anual_promedio &lt; 100</t>
+          <t>t_total_empleo &gt; 0 AND cotizado_anual_promedio IS NULL</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>Bases muy bajas por episodios mínimos o errores de conversión (céntimos/100)</t>
+          <t>Puede faltar la tabla de bases de cotización</t>
         </is>
       </c>
       <c r="K478" s="2" t="inlineStr">
@@ -25611,22 +25615,22 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio (€/año)</t>
+          <t>Tasas y recuentos</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio</t>
+          <t>num_bajas_anual_promedio</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo</t>
+          <t>num_altas_anual_promedio</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>Con tiempo de empleo &gt; 0 ⇒ cotizado_anual_promedio informado</t>
+          <t>Nº medio de bajas ≤ nº medio de altas (cada baja cierra un alta)</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr">
@@ -25636,19 +25640,15 @@
       </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo &gt; 0 AND cotizado_anual_promedio IS NULL</t>
-        </is>
-      </c>
-      <c r="J479" s="2" t="inlineStr">
-        <is>
-          <t>Puede faltar la tabla de bases de cotización</t>
-        </is>
-      </c>
+          <t>num_bajas_anual_promedio &gt; num_altas_anual_promedio + 0.001</t>
+        </is>
+      </c>
+      <c r="J479" s="2" t="inlineStr"/>
       <c r="K479" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25673,17 +25673,17 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio</t>
+          <t>num_altas_anual_promedio</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>num_altas_anual_promedio</t>
+          <t>tiempo_total_desde_inicio_vl</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>Nº medio de bajas ≤ nº medio de altas (cada baja cierra un alta)</t>
+          <t>Altas totales (media × años) ≥ 1 si hay historia</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr">
@@ -25693,12 +25693,12 @@
       </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio &gt; num_altas_anual_promedio + 0.001</t>
+          <t>tiempo_total_desde_inicio_vl &gt; 0 AND num_altas_anual_promedio * tiempo_total_desde_inicio_vl &lt; 0.9</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr"/>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>Altas totales (media × años) ≥ 1 si hay historia</t>
+          <t>Altas totales (media × años) es un entero (±0,05)</t>
         </is>
       </c>
       <c r="G481" s="2" t="inlineStr">
@@ -25746,15 +25746,19 @@
       </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND num_altas_anual_promedio * tiempo_total_desde_inicio_vl &lt; 0.9</t>
-        </is>
-      </c>
-      <c r="J481" s="2" t="inlineStr"/>
+          <t>tiempo_total_desde_inicio_vl &gt; 0 AND ABS(num_altas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365 - ROUND(num_altas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365)) &gt; 0.05</t>
+        </is>
+      </c>
+      <c r="J481" s="2" t="inlineStr">
+        <is>
+          <t>El promedio anual se normaliza con 365 días y T va en años de 365,25 (regla corregida 2026-09-21)</t>
+        </is>
+      </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25779,7 +25783,7 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>num_altas_anual_promedio</t>
+          <t>num_bajas_anual_promedio</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
@@ -25789,7 +25793,7 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>Altas totales (media × años) es un entero (±0,05)</t>
+          <t>Bajas totales (media × años) es un entero (±0,05)</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr">
@@ -25804,7 +25808,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND ABS(num_altas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365 - ROUND(num_altas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365)) &gt; 0.05</t>
+          <t>tiempo_total_desde_inicio_vl &gt; 0 AND ABS(num_bajas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365 - ROUND(num_bajas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365)) &gt; 0.05</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -25836,17 +25840,17 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
+          <t>causas_baja_distintas</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
           <t>num_bajas_anual_promedio</t>
         </is>
       </c>
-      <c r="E483" s="2" t="inlineStr">
-        <is>
-          <t>tiempo_total_desde_inicio_vl</t>
-        </is>
-      </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>Bajas totales (media × años) es un entero (±0,05)</t>
+          <t>Causas de baja distintas ≤ bajas totales + 2</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
@@ -25861,14 +25865,10 @@
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND ABS(num_bajas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365 - ROUND(num_bajas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365)) &gt; 0.05</t>
-        </is>
-      </c>
-      <c r="J483" s="2" t="inlineStr">
-        <is>
-          <t>El promedio anual se normaliza con 365 días y T va en años de 365,25 (regla corregida 2026-09-21)</t>
-        </is>
-      </c>
+          <t>tiempo_total_desde_inicio_vl &gt; 0 AND causas_baja_distintas &gt; ROUND(COALESCE(num_bajas_anual_promedio,0) * tiempo_total_desde_inicio_vl) + 2</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr"/>
       <c r="K483" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25898,12 +25898,12 @@
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio</t>
+          <t>num_altas_anual_promedio</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>Causas de baja distintas ≤ bajas totales + 2</t>
+          <t>Causas de baja distintas ≤ altas totales + 1,5</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
@@ -25918,7 +25918,7 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND causas_baja_distintas &gt; ROUND(COALESCE(num_bajas_anual_promedio,0) * tiempo_total_desde_inicio_vl) + 2</t>
+          <t>tiempo_total_desde_inicio_vl &gt; 0 AND causas_baja_distintas &gt; num_altas_anual_promedio * tiempo_total_desde_inicio_vl + 1.5</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr"/>
@@ -25949,14 +25949,10 @@
           <t>causas_baja_distintas</t>
         </is>
       </c>
-      <c r="E485" s="2" t="inlineStr">
-        <is>
-          <t>num_altas_anual_promedio</t>
-        </is>
-      </c>
+      <c r="E485" s="2" t="inlineStr"/>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>Causas de baja distintas ≤ altas totales + 1,5</t>
+          <t>causas_baja_distintas es un entero</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
@@ -25966,12 +25962,12 @@
       </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND causas_baja_distintas &gt; num_altas_anual_promedio * tiempo_total_desde_inicio_vl + 1.5</t>
+          <t>causas_baja_distintas &lt;&gt; ROUND(causas_baja_distintas)</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr"/>
@@ -25999,13 +25995,17 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas</t>
-        </is>
-      </c>
-      <c r="E486" s="2" t="inlineStr"/>
+          <t>duracion_promedio_empleo</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>t_total_empleo</t>
+        </is>
+      </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas es un entero</t>
+          <t>Duración media de empleo ≤ tiempo total de empleo (empleo + mixto empleo/desempleo) (+0,01)</t>
         </is>
       </c>
       <c r="G486" s="2" t="inlineStr">
@@ -26020,10 +26020,14 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>causas_baja_distintas &lt;&gt; ROUND(causas_baja_distintas)</t>
-        </is>
-      </c>
-      <c r="J486" s="2" t="inlineStr"/>
+          <t>duracion_promedio_empleo &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 0.01</t>
+        </is>
+      </c>
+      <c r="J486" s="2" t="inlineStr">
+        <is>
+          <t>El tiempo 'mixto' (empleo y desempleo a la vez) también es empleo; regla corregida tras la 1ª ejecución con las tablas v2.2</t>
+        </is>
+      </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26058,7 +26062,7 @@
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>Duración media de empleo ≤ tiempo total de empleo (empleo + mixto empleo/desempleo) (+0,01)</t>
+          <t>Con tiempo de empleo &gt; 0 la duración media de empleo no puede ser 0</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr">
@@ -26073,14 +26077,10 @@
       </c>
       <c r="I487" s="2" t="inlineStr">
         <is>
-          <t>duracion_promedio_empleo &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 0.01</t>
-        </is>
-      </c>
-      <c r="J487" s="2" t="inlineStr">
-        <is>
-          <t>El tiempo 'mixto' (empleo y desempleo a la vez) también es empleo; regla corregida tras la 1ª ejecución con las tablas v2.2</t>
-        </is>
-      </c>
+          <t>duracion_promedio_empleo = 0 AND t_total_empleo &gt; 0</t>
+        </is>
+      </c>
+      <c r="J487" s="2" t="inlineStr"/>
       <c r="K487" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26105,7 +26105,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>duracion_promedio_empleo</t>
+          <t>t_contrato_mas_largo</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -26115,7 +26115,7 @@
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>Con tiempo de empleo &gt; 0 la duración media de empleo no puede ser 0</t>
+          <t>El contrato más largo no supera el tiempo total de empleo (+1)</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr">
@@ -26125,12 +26125,12 @@
       </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>duracion_promedio_empleo = 0 AND t_total_empleo &gt; 0</t>
+          <t>t_contrato_mas_largo &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1</t>
         </is>
       </c>
       <c r="J488" s="2" t="inlineStr"/>
@@ -26158,7 +26158,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>t_contrato_mas_largo</t>
+          <t>duracion_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -26168,7 +26168,7 @@
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>El contrato más largo no supera el tiempo total de empleo (+1)</t>
+          <t>La duración del primer empleo significativo no supera el tiempo total de empleo (+1)</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr">
@@ -26183,7 +26183,7 @@
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>t_contrato_mas_largo &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1</t>
+          <t>duracion_1er_empleo_signif &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1</t>
         </is>
       </c>
       <c r="J489" s="2" t="inlineStr"/>
@@ -26211,7 +26211,7 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>duracion_1er_empleo_signif</t>
+          <t>t_tot_reg_ppal</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>La duración del primer empleo significativo no supera el tiempo total de empleo (+1)</t>
+          <t>El régimen principal acumula al menos 1/8 del tiempo de empleo (−1)</t>
         </is>
       </c>
       <c r="G490" s="2" t="inlineStr">
@@ -26231,15 +26231,19 @@
       </c>
       <c r="H490" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>duracion_1er_empleo_signif &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1</t>
-        </is>
-      </c>
-      <c r="J490" s="2" t="inlineStr"/>
+          <t>t_tot_reg_ppal &lt; COALESCE(t_total_empleo,0) / 8 - 1</t>
+        </is>
+      </c>
+      <c r="J490" s="2" t="inlineStr">
+        <is>
+          <t>La categoría 'principal' es la de más tiempo</t>
+        </is>
+      </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26264,7 +26268,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal</t>
+          <t>t_tot_tipo_contrato_ppal</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
@@ -26274,7 +26278,7 @@
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>El régimen principal acumula al menos 1/8 del tiempo de empleo (−1)</t>
+          <t>El tipo de contrato principal acumula al menos 1/7 del tiempo de empleo (−1)</t>
         </is>
       </c>
       <c r="G491" s="2" t="inlineStr">
@@ -26289,7 +26293,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal &lt; COALESCE(t_total_empleo,0) / 8 - 1</t>
+          <t>t_tot_tipo_contrato_ppal &lt; COALESCE(t_total_empleo,0) / 7 - 1</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr">
@@ -26321,7 +26325,7 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>t_tot_tipo_contrato_ppal</t>
+          <t>t_tot_grupo_ppal</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
@@ -26331,7 +26335,7 @@
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>El tipo de contrato principal acumula al menos 1/7 del tiempo de empleo (−1)</t>
+          <t>El grupo de cotización principal acumula al menos 1/13 del tiempo de empleo (−1)</t>
         </is>
       </c>
       <c r="G492" s="2" t="inlineStr">
@@ -26346,7 +26350,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>t_tot_tipo_contrato_ppal &lt; COALESCE(t_total_empleo,0) / 7 - 1</t>
+          <t>t_tot_grupo_ppal &lt; COALESCE(t_total_empleo,0) / 13 - 1</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
@@ -26378,7 +26382,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal</t>
+          <t>t_tot_prov_ppal</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -26388,7 +26392,7 @@
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>El grupo de cotización principal acumula al menos 1/13 del tiempo de empleo (−1)</t>
+          <t>El provincia principal acumula al menos 1/52 del tiempo de empleo (−1)</t>
         </is>
       </c>
       <c r="G493" s="2" t="inlineStr">
@@ -26403,7 +26407,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal &lt; COALESCE(t_total_empleo,0) / 13 - 1</t>
+          <t>t_tot_prov_ppal &lt; COALESCE(t_total_empleo,0) / 52 - 1</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr">
@@ -26430,44 +26434,40 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>Tasas y recuentos</t>
+          <t>Causa de baja y último episodio</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>t_tot_prov_ppal</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>El provincia principal acumula al menos 1/52 del tiempo de empleo (−1)</t>
+          <t>Última baja por fallecimiento (56) ⇒ fecha_fallecimiento informada</t>
         </is>
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>t_tot_prov_ppal &lt; COALESCE(t_total_empleo,0) / 52 - 1</t>
-        </is>
-      </c>
-      <c r="J494" s="2" t="inlineStr">
-        <is>
-          <t>La categoría 'principal' es la de más tiempo</t>
-        </is>
-      </c>
+          <t>causa_ult_baja LIKE '56 %' AND fecha_fallecimiento = 0</t>
+        </is>
+      </c>
+      <c r="J494" s="2" t="inlineStr"/>
       <c r="K494" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26492,32 +26492,32 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
+          <t>fecha_ultima_baja</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
           <t>causa_ult_baja</t>
         </is>
       </c>
-      <c r="E495" s="2" t="inlineStr">
-        <is>
-          <t>fecha_fallecimiento</t>
-        </is>
-      </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>Última baja por fallecimiento (56) ⇒ fecha_fallecimiento informada</t>
+          <t>Con última baja informada ⇒ causa de última baja informada</t>
         </is>
       </c>
       <c r="G495" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H495" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja LIKE '56 %' AND fecha_fallecimiento = 0</t>
+          <t>fecha_ultima_baja IS NOT NULL AND causa_ult_baja IS NULL</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr"/>
@@ -26555,12 +26555,12 @@
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>Con última baja informada ⇒ causa de última baja informada</t>
+          <t>Episodio vigente (2099) ⇒ causa 00 (guía 2.008)</t>
         </is>
       </c>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H496" s="2" t="inlineStr">
@@ -26570,7 +26570,7 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja IS NOT NULL AND causa_ult_baja IS NULL</t>
+          <t>year(fecha_ultima_baja) = 2099 AND causa_ult_baja NOT LIKE '00 %'</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr"/>
@@ -26603,17 +26603,17 @@
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja</t>
+          <t>tipo_contr_ult_baja</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>Episodio vigente (2099) ⇒ causa 00 (guía 2.008)</t>
+          <t>Con última baja informada ⇒ tipo de contrato del último episodio informado</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>year(fecha_ultima_baja) = 2099 AND causa_ult_baja NOT LIKE '00 %'</t>
+          <t>fecha_ultima_baja IS NOT NULL AND tipo_contr_ult_baja IS NULL</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr"/>
@@ -26656,12 +26656,12 @@
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ult_baja</t>
+          <t>act_econ_ult_baja</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>Con última baja informada ⇒ tipo de contrato del último episodio informado</t>
+          <t>Con última baja informada ⇒ actividad económica del último episodio informada</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
@@ -26676,7 +26676,7 @@
       </c>
       <c r="I498" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja IS NOT NULL AND tipo_contr_ult_baja IS NULL</t>
+          <t>fecha_ultima_baja IS NOT NULL AND act_econ_ult_baja IS NULL</t>
         </is>
       </c>
       <c r="J498" s="2" t="inlineStr"/>
@@ -26709,12 +26709,12 @@
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>Con última baja informada ⇒ actividad económica del último episodio informada</t>
+          <t>Con última baja informada ⇒ grupo del último empleo informado</t>
         </is>
       </c>
       <c r="G499" s="2" t="inlineStr">
@@ -26729,7 +26729,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja IS NOT NULL AND act_econ_ult_baja IS NULL</t>
+          <t>fecha_ultima_baja IS NOT NULL AND grupo_ultimo_empleo IS NULL</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr"/>
@@ -26752,27 +26752,27 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>Causa de baja y último episodio</t>
+          <t>Situación de afiliación × otras columnas</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
+          <t>situacion_actual_afiliacion</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
           <t>fecha_ultima_baja</t>
         </is>
       </c>
-      <c r="E500" s="2" t="inlineStr">
-        <is>
-          <t>grupo_ultimo_empleo</t>
-        </is>
-      </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>Con última baja informada ⇒ grupo del último empleo informado</t>
+          <t>Episodio vigente (2099) ⇒ Alta_ocupado o Asimilado_*</t>
         </is>
       </c>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
@@ -26782,7 +26782,7 @@
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja IS NOT NULL AND grupo_ultimo_empleo IS NULL</t>
+          <t>year(fecha_ultima_baja) = 2099 AND situacion_actual_afiliacion NOT IN ('Alta_ocupado','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52','Asimilado_otros')</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr"/>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>Episodio vigente (2099) ⇒ Alta_ocupado o Asimilado_*</t>
+          <t>Episodio finalizado ⇒ no Alta_ocupado ni Asimilado_al_alta_*</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>year(fecha_ultima_baja) = 2099 AND situacion_actual_afiliacion NOT IN ('Alta_ocupado','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52','Asimilado_otros')</t>
+          <t>(fecha_ultima_baja IS NULL OR year(fecha_ultima_baja) &lt;&gt; 2099) AND fecha_ultima_baja IS NOT NULL AND situacion_actual_afiliacion IN ('Alta_ocupado','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52')</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr"/>
@@ -26863,22 +26863,22 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
+          <t>num_bajas_anual_promedio</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
           <t>situacion_actual_afiliacion</t>
         </is>
       </c>
-      <c r="E502" s="2" t="inlineStr">
-        <is>
-          <t>fecha_ultima_baja</t>
-        </is>
-      </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>Episodio finalizado ⇒ no Alta_ocupado ni Asimilado_al_alta_*</t>
+          <t>Con historia de empleo real, sin ninguna baja ⇒ su episodio sigue vigente (no está de baja)</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
@@ -26888,10 +26888,14 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>(fecha_ultima_baja IS NULL OR year(fecha_ultima_baja) &lt;&gt; 2099) AND fecha_ultima_baja IS NOT NULL AND situacion_actual_afiliacion IN ('Alta_ocupado','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52')</t>
-        </is>
-      </c>
-      <c r="J502" s="2" t="inlineStr"/>
+          <t>num_bajas_anual_promedio IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion IN ('Baja_de_actividad','Baja_para_pension','Baja_de_prestacion','Baja_de_subsidio')</t>
+        </is>
+      </c>
+      <c r="J502" s="2" t="inlineStr">
+        <is>
+          <t>Regla corregida 2026-09-22: num_bajas_anual_promedio solo cuenta bajas de empleo REAL (decisión 'bajas reales' del 2026-09-21); quien nunca ha trabajado (t_total_empleo=0, solo prestación/subsidio/asimilado) tiene NULL por diseño aunque esté de baja. Verificado: los 1.024 incumplimientos anteriores tenían t_total_empleo=0.</t>
+        </is>
+      </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26916,17 +26920,17 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
+          <t>t_total_desempleo</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
           <t>num_bajas_anual_promedio</t>
         </is>
       </c>
-      <c r="E503" s="2" t="inlineStr">
-        <is>
-          <t>situacion_actual_afiliacion</t>
-        </is>
-      </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>Con historia de empleo real, sin ninguna baja ⇒ su episodio sigue vigente (no está de baja)</t>
+          <t>Con tiempo de desempleo &gt; 0 ⇒ ha tenido bajas</t>
         </is>
       </c>
       <c r="G503" s="2" t="inlineStr">
@@ -26936,19 +26940,15 @@
       </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion IN ('Baja_de_actividad','Baja_para_pension','Baja_de_prestacion','Baja_de_subsidio')</t>
-        </is>
-      </c>
-      <c r="J503" s="2" t="inlineStr">
-        <is>
-          <t>Regla corregida 2026-09-22: num_bajas_anual_promedio solo cuenta bajas de empleo REAL (decisión 'bajas reales' del 2026-09-21); quien nunca ha trabajado (t_total_empleo=0, solo prestación/subsidio/asimilado) tiene NULL por diseño aunque esté de baja. Verificado: los 1.024 incumplimientos anteriores tenían t_total_empleo=0.</t>
-        </is>
-      </c>
+          <t>t_total_desempleo &gt; 0 AND num_bajas_anual_promedio IS NULL</t>
+        </is>
+      </c>
+      <c r="J503" s="2" t="inlineStr"/>
       <c r="K503" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26973,17 +26973,17 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo</t>
+          <t>situacion_actual_afiliacion</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio</t>
+          <t>fecha_ini_primer_empleo</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>Con tiempo de desempleo &gt; 0 ⇒ ha tenido bajas</t>
+          <t>Sin fecha de primer empleo ⇒ Nunca_ha_cotizado</t>
         </is>
       </c>
       <c r="G504" s="2" t="inlineStr">
@@ -26993,12 +26993,12 @@
       </c>
       <c r="H504" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo &gt; 0 AND num_bajas_anual_promedio IS NULL</t>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND fecha_ini_primer_empleo IS NULL</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr"/>
@@ -27031,12 +27031,12 @@
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>reg_cotiz_ppal_agrupado</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>Sin fecha de primer empleo ⇒ Nunca_ha_cotizado</t>
+          <t>Sin régimen de cotización, con empleo real ⇒ Nunca_ha_cotizado</t>
         </is>
       </c>
       <c r="G505" s="2" t="inlineStr">
@@ -27051,10 +27051,14 @@
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND fecha_ini_primer_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J505" s="2" t="inlineStr"/>
+          <t>reg_cotiz_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="inlineStr">
+        <is>
+          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene régimen principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
+        </is>
+      </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27084,12 +27088,12 @@
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado</t>
+          <t>tipo_contr_ppal_agrupado</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>Sin régimen de cotización, con empleo real ⇒ Nunca_ha_cotizado</t>
+          <t>Sin tipo de contrato principal (nulo), con empleo real ⇒ Nunca_ha_cotizado</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr">
@@ -27104,12 +27108,12 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
+          <t>tipo_contr_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene régimen principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
+          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene tipo de contrato principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
         </is>
       </c>
       <c r="K506" s="2" t="inlineStr">
@@ -27141,12 +27145,12 @@
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>Sin tipo de contrato principal (nulo), con empleo real ⇒ Nunca_ha_cotizado</t>
+          <t>Con afiliación ⇒ causa_ult_baja no es el 'NO CONSTA' sin código</t>
         </is>
       </c>
       <c r="G507" s="2" t="inlineStr">
@@ -27161,14 +27165,10 @@
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
-        </is>
-      </c>
-      <c r="J507" s="2" t="inlineStr">
-        <is>
-          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene tipo de contrato principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
-        </is>
-      </c>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND causa_ult_baja = 'NO CONSTA'</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="inlineStr"/>
       <c r="K507" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27193,17 +27193,13 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion</t>
-        </is>
-      </c>
-      <c r="E508" s="2" t="inlineStr">
-        <is>
-          <t>causa_ult_baja</t>
-        </is>
-      </c>
+          <t>duracion_actual_sin_empleo</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr"/>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>Con afiliación ⇒ causa_ult_baja no es el 'NO CONSTA' sin código</t>
+          <t>duracion_actual_sin_empleo es un número entero de días</t>
         </is>
       </c>
       <c r="G508" s="2" t="inlineStr">
@@ -27213,12 +27209,12 @@
       </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND causa_ult_baja = 'NO CONSTA'</t>
+          <t>duracion_actual_sin_empleo &lt;&gt; ROUND(duracion_actual_sin_empleo)</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr"/>
@@ -27241,18 +27237,22 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>Situación de afiliación × otras columnas</t>
+          <t>Ingresos por tipo (v2.2)</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>duracion_actual_sin_empleo</t>
-        </is>
-      </c>
-      <c r="E509" s="2" t="inlineStr"/>
+          <t>ingresos_bruto_total_2024</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_sueldo_2024</t>
+        </is>
+      </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>duracion_actual_sin_empleo es un número entero de días</t>
+          <t>ingresos_sueldo_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G509" s="2" t="inlineStr">
@@ -27262,12 +27262,12 @@
       </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
-          <t>duracion_actual_sin_empleo &lt;&gt; ROUND(duracion_actual_sin_empleo)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_sueldo_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J509" s="2" t="inlineStr"/>
@@ -27300,12 +27300,12 @@
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_pension_2024</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_pension_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
@@ -27320,7 +27320,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_sueldo_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_pension_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr"/>
@@ -27353,12 +27353,12 @@
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_prestacion_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
@@ -27373,7 +27373,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_pension_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_prestacion_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J511" s="2" t="inlineStr"/>
@@ -27406,12 +27406,12 @@
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_actividad_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G512" s="2" t="inlineStr">
@@ -27426,7 +27426,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_prestacion_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_actividad_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr"/>
@@ -27459,12 +27459,12 @@
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_otras_exentas_2024</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_otras_exentas_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr">
@@ -27479,7 +27479,7 @@
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_actividad_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_otras_exentas_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J513" s="2" t="inlineStr"/>
@@ -27512,12 +27512,12 @@
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024</t>
+          <t>retenciones_irpf_2024</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>retenciones_irpf_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G514" s="2" t="inlineStr">
@@ -27532,7 +27532,7 @@
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_otras_exentas_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (retenciones_irpf_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr"/>
@@ -27563,14 +27563,10 @@
           <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
-      <c r="E515" s="2" t="inlineStr">
-        <is>
-          <t>retenciones_irpf_2024</t>
-        </is>
-      </c>
+      <c r="E515" s="2" t="inlineStr"/>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>Las 5 partes suman el total de ingresos (±0,01 €)</t>
         </is>
       </c>
       <c r="G515" s="2" t="inlineStr">
@@ -27585,7 +27581,7 @@
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (retenciones_irpf_2024 IS NULL)</t>
+          <t>ingresos_bruto_total_2024 IS NOT NULL AND ABS(ingresos_bruto_total_2024 - (ingresos_sueldo_2024 + ingresos_pension_2024 + ingresos_prestacion_2024 + ingresos_actividad_2024 + ingresos_otras_exentas_2024)) &gt; 0.01</t>
         </is>
       </c>
       <c r="J515" s="2" t="inlineStr"/>
@@ -27613,13 +27609,13 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr"/>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>Las 5 partes suman el total de ingresos (±0,01 €)</t>
+          <t>ingresos_sueldo_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G516" s="2" t="inlineStr">
@@ -27629,15 +27625,19 @@
       </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I516" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 IS NOT NULL AND ABS(ingresos_bruto_total_2024 - (ingresos_sueldo_2024 + ingresos_pension_2024 + ingresos_prestacion_2024 + ingresos_actividad_2024 + ingresos_otras_exentas_2024)) &gt; 0.01</t>
-        </is>
-      </c>
-      <c r="J516" s="2" t="inlineStr"/>
+          <t>ingresos_sueldo_2024 &lt; 0</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="inlineStr">
+        <is>
+          <t>Una rectificación de Hacienda podría dar importes negativos</t>
+        </is>
+      </c>
       <c r="K516" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27662,13 +27662,13 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_pension_2024</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr"/>
       <c r="F517" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 ≥ 0</t>
+          <t>ingresos_pension_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G517" s="2" t="inlineStr">
@@ -27683,7 +27683,7 @@
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &lt; 0</t>
+          <t>ingresos_pension_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J517" s="2" t="inlineStr">
@@ -27715,13 +27715,13 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr"/>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 ≥ 0</t>
+          <t>ingresos_prestacion_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G518" s="2" t="inlineStr">
@@ -27736,7 +27736,7 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 &lt; 0</t>
+          <t>ingresos_prestacion_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr">
@@ -27768,13 +27768,13 @@
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr"/>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 ≥ 0</t>
+          <t>ingresos_actividad_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G519" s="2" t="inlineStr">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &lt; 0</t>
+          <t>ingresos_actividad_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J519" s="2" t="inlineStr">
@@ -27821,13 +27821,13 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_otras_exentas_2024</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr"/>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 ≥ 0</t>
+          <t>ingresos_otras_exentas_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G520" s="2" t="inlineStr">
@@ -27842,7 +27842,7 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &lt; 0</t>
+          <t>ingresos_otras_exentas_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
@@ -27874,13 +27874,13 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024</t>
+          <t>retenciones_irpf_2024</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr"/>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024 ≥ 0</t>
+          <t>Las retenciones de IRPF no son negativas</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
@@ -27895,14 +27895,10 @@
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024 &lt; 0</t>
-        </is>
-      </c>
-      <c r="J521" s="2" t="inlineStr">
-        <is>
-          <t>Una rectificación de Hacienda podría dar importes negativos</t>
-        </is>
-      </c>
+          <t>retenciones_irpf_2024 &lt; 0</t>
+        </is>
+      </c>
+      <c r="J521" s="2" t="inlineStr"/>
       <c r="K521" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27930,10 +27926,14 @@
           <t>retenciones_irpf_2024</t>
         </is>
       </c>
-      <c r="E522" s="2" t="inlineStr"/>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_bruto_total_2024</t>
+        </is>
+      </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>Las retenciones de IRPF no son negativas</t>
+          <t>Las retenciones no superan el total de ingresos</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024 &lt; 0</t>
+          <t>retenciones_irpf_2024 &gt; ingresos_bruto_total_2024 + 0.01</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr"/>
@@ -27986,22 +27986,22 @@
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
-          <t>Las retenciones no superan el total de ingresos</t>
+          <t>Retenciones ≤ 50 % del total (tipo máximo de IRPF ≈ 47 %)</t>
         </is>
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I523" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024 &gt; ingresos_bruto_total_2024 + 0.01</t>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND retenciones_irpf_2024 &gt; 0.5 * ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="J523" s="2" t="inlineStr"/>
@@ -28029,17 +28029,13 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024</t>
-        </is>
-      </c>
-      <c r="E524" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_bruto_total_2024</t>
-        </is>
-      </c>
+          <t>ingresos_sueldo_2024</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr"/>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>Retenciones ≤ 50 % del total (tipo máximo de IRPF ≈ 47 %)</t>
+          <t>Sueldo anual ≤ 1.000.000 €</t>
         </is>
       </c>
       <c r="G524" s="2" t="inlineStr">
@@ -28054,10 +28050,14 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND retenciones_irpf_2024 &gt; 0.5 * ingresos_bruto_total_2024</t>
-        </is>
-      </c>
-      <c r="J524" s="2" t="inlineStr"/>
+          <t>ingresos_sueldo_2024 &gt; 1000000</t>
+        </is>
+      </c>
+      <c r="J524" s="2" t="inlineStr">
+        <is>
+          <t>Outliers (directivos)</t>
+        </is>
+      </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28082,13 +28082,13 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr"/>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>Sueldo anual ≤ 1.000.000 €</t>
+          <t>Ingresos de actividad anual ≤ 1.000.000 €</t>
         </is>
       </c>
       <c r="G525" s="2" t="inlineStr">
@@ -28103,12 +28103,12 @@
       </c>
       <c r="I525" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 1000000</t>
+          <t>ingresos_actividad_2024 &gt; 1000000</t>
         </is>
       </c>
       <c r="J525" s="2" t="inlineStr">
         <is>
-          <t>Outliers (directivos)</t>
+          <t>Outliers</t>
         </is>
       </c>
       <c r="K525" s="2" t="inlineStr">
@@ -28135,13 +28135,17 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
-        </is>
-      </c>
-      <c r="E526" s="2" t="inlineStr"/>
+          <t>ingresos_sueldo_2024</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>edad_actual_fecha_corte</t>
+        </is>
+      </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>Ingresos de actividad anual ≤ 1.000.000 €</t>
+          <t>Con ingresos de sueldo ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G526" s="2" t="inlineStr">
@@ -28151,19 +28155,15 @@
       </c>
       <c r="H526" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &gt; 1000000</t>
-        </is>
-      </c>
-      <c r="J526" s="2" t="inlineStr">
-        <is>
-          <t>Outliers</t>
-        </is>
-      </c>
+          <t>ingresos_sueldo_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+        </is>
+      </c>
+      <c r="J526" s="2" t="inlineStr"/>
       <c r="K526" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28193,27 +28193,27 @@
       </c>
       <c r="E527" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de sueldo ⇒ edad ≥ 16</t>
+          <t>Con ingresos de sueldo 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H527" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I527" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J527" s="2" t="inlineStr"/>
@@ -28241,32 +28241,32 @@
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de sueldo 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con ingresos de prestación ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H528" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+          <t>ingresos_prestacion_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
         </is>
       </c>
       <c r="J528" s="2" t="inlineStr"/>
@@ -28299,27 +28299,27 @@
       </c>
       <c r="E529" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F529" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de prestación ⇒ edad ≥ 16</t>
+          <t>Con ingresos de prestación 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G529" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H529" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I529" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+          <t>ingresos_prestacion_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J529" s="2" t="inlineStr"/>
@@ -28347,32 +28347,32 @@
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de prestación 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con ingresos de actividad ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H530" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+          <t>ingresos_actividad_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
         </is>
       </c>
       <c r="J530" s="2" t="inlineStr"/>
@@ -28405,27 +28405,27 @@
       </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de actividad ⇒ edad ≥ 16</t>
+          <t>Con ingresos de actividad 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G531" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H531" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I531" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+          <t>ingresos_actividad_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J531" s="2" t="inlineStr"/>
@@ -28453,7 +28453,7 @@
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_pension_2024</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
@@ -28463,7 +28463,7 @@
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de actividad 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con pensiones cobradas en 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G532" s="2" t="inlineStr">
@@ -28478,7 +28478,7 @@
       </c>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+          <t>ingresos_pension_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr"/>
@@ -28506,35 +28506,39 @@
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>t_total_desempleo</t>
         </is>
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>Con pensiones cobradas en 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con prestación por desempleo en 2024 ⇒ ha tenido tiempo de desempleo</t>
         </is>
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I533" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
-        </is>
-      </c>
-      <c r="J533" s="2" t="inlineStr"/>
+          <t>ingresos_prestacion_2024 &gt; 0 AND COALESCE(t_total_desempleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0</t>
+        </is>
+      </c>
+      <c r="J533" s="2" t="inlineStr">
+        <is>
+          <t>Los subsidios pueden no figurar como desempleo en afiliación</t>
+        </is>
+      </c>
       <c r="K533" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28559,37 +28563,37 @@
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo</t>
+          <t>fecha_ini_primer_empleo</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>Con prestación por desempleo en 2024 ⇒ ha tenido tiempo de desempleo</t>
+          <t>Con sueldo en 2024 ⇒ tiene primer empleo en afiliación</t>
         </is>
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND COALESCE(t_total_desempleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0</t>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ini_primer_empleo IS NULL</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr">
         <is>
-          <t>Los subsidios pueden no figurar como desempleo en afiliación</t>
+          <t>Los funcionarios de MUFACE no cotizan en el sistema de la MCVL</t>
         </is>
       </c>
       <c r="K534" s="2" t="inlineStr">
@@ -28621,32 +28625,32 @@
       </c>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>fecha_ultima_baja</t>
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>Con sueldo en 2024 ⇒ tiene primer empleo en afiliación</t>
+          <t>Con sueldo en 2024 ⇒ la última baja no es anterior a 2024</t>
         </is>
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I535" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ini_primer_empleo IS NULL</t>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ultima_baja IS NOT NULL AND year(fecha_ultima_baja) &lt; 2024</t>
         </is>
       </c>
       <c r="J535" s="2" t="inlineStr">
         <is>
-          <t>Los funcionarios de MUFACE no cotizan en el sistema de la MCVL</t>
+          <t>Pagos atrasados o indemnizaciones podrían dar sueldo sin alta en 2024</t>
         </is>
       </c>
       <c r="K535" s="2" t="inlineStr">
@@ -28673,17 +28677,17 @@
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_pension_2024</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>Con sueldo en 2024 ⇒ la última baja no es anterior a 2024</t>
+          <t>Con pensión en fiscal ⇒ cobra pensión en la tabla de pensiones</t>
         </is>
       </c>
       <c r="G536" s="2" t="inlineStr">
@@ -28693,17 +28697,17 @@
       </c>
       <c r="H536" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ultima_baja IS NOT NULL AND year(fecha_ultima_baja) &lt; 2024</t>
+          <t>ingresos_pension_2024 &gt; 0 AND cobra_pension_2024_5 = 'NO'</t>
         </is>
       </c>
       <c r="J536" s="2" t="inlineStr">
         <is>
-          <t>Pagos atrasados o indemnizaciones podrían dar sueldo sin alta en 2024</t>
+          <t>Mutualidades y Clases Pasivas pueden no estar en la tabla de pensiones de la MCVL</t>
         </is>
       </c>
       <c r="K536" s="2" t="inlineStr">
@@ -28730,17 +28734,17 @@
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
+          <t>cobra_pension_2024_5</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
           <t>ingresos_pension_2024</t>
         </is>
       </c>
-      <c r="E537" s="2" t="inlineStr">
-        <is>
-          <t>cobra_pension_2024_5</t>
-        </is>
-      </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>Con pensión en fiscal ⇒ cobra pensión en la tabla de pensiones</t>
+          <t>Cobra pensión en la tabla de pensiones ⇒ tiene pensión en fiscal (si consta en fiscal)</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
@@ -28755,12 +28759,12 @@
       </c>
       <c r="I537" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 &gt; 0 AND cobra_pension_2024_5 = 'NO'</t>
+          <t>cobra_pension_2024_5 = 'SI' AND ingresos_bruto_total_2024 IS NOT NULL AND ingresos_pension_2024 = 0</t>
         </is>
       </c>
       <c r="J537" s="2" t="inlineStr">
         <is>
-          <t>Mutualidades y Clases Pasivas pueden no estar en la tabla de pensiones de la MCVL</t>
+          <t>Puede haber empezado a cobrar en 2025</t>
         </is>
       </c>
       <c r="K537" s="2" t="inlineStr">
@@ -28782,44 +28786,40 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>Ingresos por tipo (v2.2)</t>
+          <t>Clave y subclave de percepción (v2.2)</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>clave_subclave_ppal</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>Cobra pensión en la tabla de pensiones ⇒ tiene pensión en fiscal (si consta en fiscal)</t>
+          <t>clave_subclave_ppal = NO CONSTA ⇔ no hay datos fiscales</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H538" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 = 'SI' AND ingresos_bruto_total_2024 IS NOT NULL AND ingresos_pension_2024 = 0</t>
-        </is>
-      </c>
-      <c r="J538" s="2" t="inlineStr">
-        <is>
-          <t>Puede haber empezado a cobrar en 2025</t>
-        </is>
-      </c>
+          <t>(clave_subclave_ppal = 'NO CONSTA') &lt;&gt; (ingresos_bruto_total_2024 IS NULL)</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr"/>
       <c r="K538" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28847,19 +28847,15 @@
           <t>clave_subclave_ppal</t>
         </is>
       </c>
-      <c r="E539" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_bruto_total_2024</t>
-        </is>
-      </c>
+      <c r="E539" s="2" t="inlineStr"/>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal = NO CONSTA ⇔ no hay datos fiscales</t>
+          <t>clave_subclave_ppal = 'letra + 2 (dígito/X)' con etiqueta, o NO CONSTA</t>
         </is>
       </c>
       <c r="G539" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H539" s="2" t="inlineStr">
@@ -28869,10 +28865,14 @@
       </c>
       <c r="I539" s="2" t="inlineStr">
         <is>
-          <t>(clave_subclave_ppal = 'NO CONSTA') &lt;&gt; (ingresos_bruto_total_2024 IS NULL)</t>
-        </is>
-      </c>
-      <c r="J539" s="2" t="inlineStr"/>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(clave_subclave_ppal, '^[ABCFGHL][0-9X]{2}( .+)?$')</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="inlineStr">
+        <is>
+          <t>Claves del modelo 190 presentes en la MCVL: A, B, C, F, G, H, L</t>
+        </is>
+      </c>
       <c r="K539" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28903,12 +28903,12 @@
       <c r="E540" s="2" t="inlineStr"/>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal = 'letra + 2 (dígito/X)' con etiqueta, o NO CONSTA</t>
+          <t>Cada código de clave+subclave tiene una única etiqueta</t>
         </is>
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -28918,14 +28918,10 @@
       </c>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(clave_subclave_ppal, '^[ABCFGHL][0-9X]{2}( .+)?$')</t>
-        </is>
-      </c>
-      <c r="J540" s="2" t="inlineStr">
-        <is>
-          <t>Claves del modelo 190 presentes en la MCVL: A, B, C, F, G, H, L</t>
-        </is>
-      </c>
+          <t>split_part(clave_subclave_ppal, ' ', 1) IN (SELECT split_part(clave_subclave_ppal, ' ', 1) FROM personas WHERE clave_subclave_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT clave_subclave_ppal) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr"/>
       <c r="K540" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28953,10 +28949,14 @@
           <t>clave_subclave_ppal</t>
         </is>
       </c>
-      <c r="E541" s="2" t="inlineStr"/>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_sueldo_2024</t>
+        </is>
+      </c>
       <c r="F541" s="2" t="inlineStr">
         <is>
-          <t>Cada código de clave+subclave tiene una única etiqueta</t>
+          <t>Tipo principal de sueldo (A) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G541" s="2" t="inlineStr">
@@ -28971,7 +28971,7 @@
       </c>
       <c r="I541" s="2" t="inlineStr">
         <is>
-          <t>split_part(clave_subclave_ppal, ' ', 1) IN (SELECT split_part(clave_subclave_ppal, ' ', 1) FROM personas WHERE clave_subclave_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT clave_subclave_ppal) &gt; 1)</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'A%' AND COALESCE(ingresos_sueldo_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J541" s="2" t="inlineStr"/>
@@ -29004,12 +29004,12 @@
       </c>
       <c r="E542" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_pension_2024</t>
         </is>
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de sueldo (A) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de pensión (B, L06, L07, L08) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G542" s="2" t="inlineStr">
@@ -29024,7 +29024,7 @@
       </c>
       <c r="I542" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'A%' AND COALESCE(ingresos_sueldo_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'B%' OR split_part(clave_subclave_ppal, ' ', 1) IN ('L06','L07','L08')) AND COALESCE(ingresos_pension_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J542" s="2" t="inlineStr"/>
@@ -29057,12 +29057,12 @@
       </c>
       <c r="E543" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="F543" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de pensión (B, L06, L07, L08) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de prestación (C) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G543" s="2" t="inlineStr">
@@ -29077,7 +29077,7 @@
       </c>
       <c r="I543" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'B%' OR split_part(clave_subclave_ppal, ' ', 1) IN ('L06','L07','L08')) AND COALESCE(ingresos_pension_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'C%' AND COALESCE(ingresos_prestacion_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J543" s="2" t="inlineStr"/>
@@ -29110,12 +29110,12 @@
       </c>
       <c r="E544" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de prestación (C) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de actividad (F, G, H) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G544" s="2" t="inlineStr">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="I544" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'C%' AND COALESCE(ingresos_prestacion_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'F%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'G%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'H%') AND COALESCE(ingresos_actividad_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J544" s="2" t="inlineStr"/>
@@ -29163,12 +29163,12 @@
       </c>
       <c r="E545" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_otras_exentas_2024</t>
         </is>
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de actividad (F, G, H) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de otras exentas (resto de L) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G545" s="2" t="inlineStr">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="I545" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'F%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'G%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'H%') AND COALESCE(ingresos_actividad_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'L%' AND split_part(clave_subclave_ppal, ' ', 1) NOT IN ('L06','L07','L08')) AND COALESCE(ingresos_otras_exentas_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J545" s="2" t="inlineStr"/>
@@ -29211,17 +29211,17 @@
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal</t>
+          <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024</t>
+          <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de otras exentas (resto de L) ⇒ ese importe es positivo</t>
+          <t>Con lista de tipos cobrados ⇒ total de ingresos &gt; 0</t>
         </is>
       </c>
       <c r="G546" s="2" t="inlineStr">
@@ -29236,7 +29236,7 @@
       </c>
       <c r="I546" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'L%' AND split_part(clave_subclave_ppal, ' ', 1) NOT IN ('L06','L07','L08')) AND COALESCE(ingresos_otras_exentas_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND COALESCE(ingresos_bruto_total_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J546" s="2" t="inlineStr"/>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="F547" s="2" t="inlineStr">
         <is>
-          <t>Con lista de tipos cobrados ⇒ total de ingresos &gt; 0</t>
+          <t>Total de ingresos &gt; 0 ⇒ hay lista de tipos cobrados</t>
         </is>
       </c>
       <c r="G547" s="2" t="inlineStr">
@@ -29289,7 +29289,7 @@
       </c>
       <c r="I547" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND COALESCE(ingresos_bruto_total_2024, 0) &lt;= 0</t>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND clave_subclave_todas_cobradas IS NULL</t>
         </is>
       </c>
       <c r="J547" s="2" t="inlineStr"/>
@@ -29322,12 +29322,12 @@
       </c>
       <c r="E548" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>clave_subclave_ppal</t>
         </is>
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>Total de ingresos &gt; 0 ⇒ hay lista de tipos cobrados</t>
+          <t>El primer tipo cobrado es el tipo principal</t>
         </is>
       </c>
       <c r="G548" s="2" t="inlineStr">
@@ -29342,7 +29342,7 @@
       </c>
       <c r="I548" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND clave_subclave_todas_cobradas IS NULL</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND clave_subclave_todas_cobradas[1] &lt;&gt; split_part(clave_subclave_ppal, ' ', 1)</t>
         </is>
       </c>
       <c r="J548" s="2" t="inlineStr"/>
@@ -29373,14 +29373,10 @@
           <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
-      <c r="E549" s="2" t="inlineStr">
-        <is>
-          <t>clave_subclave_ppal</t>
-        </is>
-      </c>
+      <c r="E549" s="2" t="inlineStr"/>
       <c r="F549" s="2" t="inlineStr">
         <is>
-          <t>El primer tipo cobrado es el tipo principal</t>
+          <t>La lista de tipos cobrados no repite códigos</t>
         </is>
       </c>
       <c r="G549" s="2" t="inlineStr">
@@ -29395,7 +29391,7 @@
       </c>
       <c r="I549" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND clave_subclave_todas_cobradas[1] &lt;&gt; split_part(clave_subclave_ppal, ' ', 1)</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) &lt;&gt; len(list_distinct(clave_subclave_todas_cobradas))</t>
         </is>
       </c>
       <c r="J549" s="2" t="inlineStr"/>
@@ -29429,12 +29425,12 @@
       <c r="E550" s="2" t="inlineStr"/>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>La lista de tipos cobrados no repite códigos</t>
+          <t>Los códigos de la lista tienen formato letra + 2 (dígito/X)</t>
         </is>
       </c>
       <c r="G550" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H550" s="2" t="inlineStr">
@@ -29444,7 +29440,7 @@
       </c>
       <c r="I550" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) &lt;&gt; len(list_distinct(clave_subclave_todas_cobradas))</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(list_filter(clave_subclave_todas_cobradas, x -&gt; NOT regexp_matches(x, '^[ABCFGHL][0-9X]{2}$'))) &gt; 0</t>
         </is>
       </c>
       <c r="J550" s="2" t="inlineStr"/>
@@ -29478,22 +29474,22 @@
       <c r="E551" s="2" t="inlineStr"/>
       <c r="F551" s="2" t="inlineStr">
         <is>
-          <t>Los códigos de la lista tienen formato letra + 2 (dígito/X)</t>
+          <t>Sin tipos cobrados ⇒ NULL, no lista vacía</t>
         </is>
       </c>
       <c r="G551" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H551" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I551" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(list_filter(clave_subclave_todas_cobradas, x -&gt; NOT regexp_matches(x, '^[ABCFGHL][0-9X]{2}$'))) &gt; 0</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) = 0</t>
         </is>
       </c>
       <c r="J551" s="2" t="inlineStr"/>
@@ -29524,10 +29520,14 @@
           <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
-      <c r="E552" s="2" t="inlineStr"/>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_sueldo_2024</t>
+        </is>
+      </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>Sin tipos cobrados ⇒ NULL, no lista vacía</t>
+          <t>A00 en la lista ⇔ sueldo positivo</t>
         </is>
       </c>
       <c r="G552" s="2" t="inlineStr">
@@ -29537,12 +29537,12 @@
       </c>
       <c r="H552" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I552" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) = 0</t>
+          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'A00'), false) &lt;&gt; (COALESCE(ingresos_sueldo_2024, 0) &gt; 0)</t>
         </is>
       </c>
       <c r="J552" s="2" t="inlineStr"/>
@@ -29575,12 +29575,12 @@
       </c>
       <c r="E553" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>A00 en la lista ⇔ sueldo positivo</t>
+          <t>C00 en la lista ⇔ prestación positiva</t>
         </is>
       </c>
       <c r="G553" s="2" t="inlineStr">
@@ -29595,7 +29595,7 @@
       </c>
       <c r="I553" s="2" t="inlineStr">
         <is>
-          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'A00'), false) &lt;&gt; (COALESCE(ingresos_sueldo_2024, 0) &gt; 0)</t>
+          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'C00'), false) &lt;&gt; (COALESCE(ingresos_prestacion_2024, 0) &gt; 0)</t>
         </is>
       </c>
       <c r="J553" s="2" t="inlineStr"/>
@@ -29618,27 +29618,27 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>Clave y subclave de percepción (v2.2)</t>
+          <t>Fallecimiento (v2.2)</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas</t>
+          <t>ha_fallecido</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>C00 en la lista ⇔ prestación positiva</t>
+          <t>ha_fallecido = SI ⇔ fecha_fallecimiento informada</t>
         </is>
       </c>
       <c r="G554" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H554" s="2" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="I554" s="2" t="inlineStr">
         <is>
-          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'C00'), false) &lt;&gt; (COALESCE(ingresos_prestacion_2024, 0) &gt; 0)</t>
+          <t>(ha_fallecido = 'SI') &lt;&gt; (COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0)</t>
         </is>
       </c>
       <c r="J554" s="2" t="inlineStr"/>
@@ -29681,17 +29681,17 @@
       </c>
       <c r="E555" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>edad_fallecimiento</t>
         </is>
       </c>
       <c r="F555" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = SI ⇔ fecha_fallecimiento informada</t>
+          <t>ha_fallecido = SI ⇔ edad_fallecimiento informada</t>
         </is>
       </c>
       <c r="G555" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H555" s="2" t="inlineStr">
@@ -29701,7 +29701,7 @@
       </c>
       <c r="I555" s="2" t="inlineStr">
         <is>
-          <t>(ha_fallecido = 'SI') &lt;&gt; (COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0)</t>
+          <t>(ha_fallecido = 'SI') &lt;&gt; (edad_fallecimiento IS NOT NULL)</t>
         </is>
       </c>
       <c r="J555" s="2" t="inlineStr"/>
@@ -29729,17 +29729,13 @@
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido</t>
-        </is>
-      </c>
-      <c r="E556" s="2" t="inlineStr">
-        <is>
           <t>edad_fallecimiento</t>
         </is>
       </c>
+      <c r="E556" s="2" t="inlineStr"/>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = SI ⇔ edad_fallecimiento informada</t>
+          <t>edad_fallecimiento ≥ 0 (no se muere antes de nacer)</t>
         </is>
       </c>
       <c r="G556" s="2" t="inlineStr">
@@ -29754,7 +29750,7 @@
       </c>
       <c r="I556" s="2" t="inlineStr">
         <is>
-          <t>(ha_fallecido = 'SI') &lt;&gt; (edad_fallecimiento IS NOT NULL)</t>
+          <t>edad_fallecimiento &lt; 0</t>
         </is>
       </c>
       <c r="J556" s="2" t="inlineStr"/>
@@ -29788,22 +29784,22 @@
       <c r="E557" s="2" t="inlineStr"/>
       <c r="F557" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento ≥ 0 (no se muere antes de nacer)</t>
+          <t>edad_fallecimiento ≤ 115</t>
         </is>
       </c>
       <c r="G557" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H557" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I557" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento &lt; 0</t>
+          <t>edad_fallecimiento &gt; 115</t>
         </is>
       </c>
       <c r="J557" s="2" t="inlineStr"/>
@@ -29834,28 +29830,36 @@
           <t>edad_fallecimiento</t>
         </is>
       </c>
-      <c r="E558" s="2" t="inlineStr"/>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>edad_actual_fecha_corte</t>
+        </is>
+      </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento ≤ 115</t>
+          <t>La edad al fallecer es anterior a la edad a fecha de corte</t>
         </is>
       </c>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H558" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento &gt; 115</t>
-        </is>
-      </c>
-      <c r="J558" s="2" t="inlineStr"/>
+          <t>ha_fallecido = 'SI' AND edad_fallecimiento &gt;= edad_actual_fecha_corte</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="inlineStr">
+        <is>
+          <t>Comprobación pedida por el usuario 2026-09-21</t>
+        </is>
+      </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -29885,12 +29889,12 @@
       </c>
       <c r="E559" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F559" s="2" t="inlineStr">
         <is>
-          <t>La edad al fallecer es anterior a la edad a fecha de corte</t>
+          <t>edad_fallecimiento = meses entre nacimiento y fallecimiento / 12 (±0,001)</t>
         </is>
       </c>
       <c r="G559" s="2" t="inlineStr">
@@ -29905,14 +29909,10 @@
       </c>
       <c r="I559" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = 'SI' AND edad_fallecimiento &gt;= edad_actual_fecha_corte</t>
-        </is>
-      </c>
-      <c r="J559" s="2" t="inlineStr">
-        <is>
-          <t>Comprobación pedida por el usuario 2026-09-21</t>
-        </is>
-      </c>
+          <t>ha_fallecido = 'SI' AND ABS(edad_fallecimiento - (((fecha_fallecimiento // 100 - year(fecha_nacimiento)) * 12 + (fecha_fallecimiento % 100 - month(fecha_nacimiento))) / 12.0)) &gt; 0.001</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="inlineStr"/>
       <c r="K559" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -29932,22 +29932,22 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>Fallecimiento (v2.2)</t>
+          <t>Residencia (v2.2)</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento</t>
+          <t>domic_resid_habitual</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>prov_resid_habitual</t>
         </is>
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento = meses entre nacimiento y fallecimiento / 12 (±0,001)</t>
+          <t>domicilio NO CONSTA ⇔ provincia de residencia NO CONSTA</t>
         </is>
       </c>
       <c r="G560" s="2" t="inlineStr">
@@ -29962,7 +29962,7 @@
       </c>
       <c r="I560" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = 'SI' AND ABS(edad_fallecimiento - (((fecha_fallecimiento // 100 - year(fecha_nacimiento)) * 12 + (fecha_fallecimiento % 100 - month(fecha_nacimiento))) / 12.0)) &gt; 0.001</t>
+          <t>(domic_resid_habitual = 'NO CONSTA') &lt;&gt; (prov_resid_habitual = 'NO CONSTA')</t>
         </is>
       </c>
       <c r="J560" s="2" t="inlineStr"/>
@@ -30000,7 +30000,7 @@
       </c>
       <c r="F561" s="2" t="inlineStr">
         <is>
-          <t>domicilio NO CONSTA ⇔ provincia de residencia NO CONSTA</t>
+          <t>El código de provincia del domicilio coincide con prov_resid_habitual</t>
         </is>
       </c>
       <c r="G561" s="2" t="inlineStr">
@@ -30015,7 +30015,7 @@
       </c>
       <c r="I561" s="2" t="inlineStr">
         <is>
-          <t>(domic_resid_habitual = 'NO CONSTA') &lt;&gt; (prov_resid_habitual = 'NO CONSTA')</t>
+          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND split_part(prov_resid_habitual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
         </is>
       </c>
       <c r="J561" s="2" t="inlineStr"/>
@@ -30048,95 +30048,42 @@
       </c>
       <c r="E562" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual</t>
+          <t>prov_fiscal_actual</t>
         </is>
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
-          <t>El código de provincia del domicilio coincide con prov_resid_habitual</t>
+          <t>La provincia de residencia coincide con la provincia fiscal</t>
         </is>
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND split_part(prov_resid_habitual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
-        </is>
-      </c>
-      <c r="J562" s="2" t="inlineStr"/>
+          <t>(domic_resid_habitual IS NOT NULL AND domic_resid_habitual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND split_part(prov_fiscal_actual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="inlineStr">
+        <is>
+          <t>El domicilio fiscal es el del 31-12-2024; puede haber mudanzas</t>
+        </is>
+      </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" s="2" t="inlineStr">
-        <is>
-          <t>C-339</t>
-        </is>
-      </c>
-      <c r="B563" s="2" t="inlineStr">
-        <is>
-          <t>C · otras columnas</t>
-        </is>
-      </c>
-      <c r="C563" s="2" t="inlineStr">
-        <is>
-          <t>Residencia (v2.2)</t>
-        </is>
-      </c>
-      <c r="D563" s="2" t="inlineStr">
-        <is>
-          <t>domic_resid_habitual</t>
-        </is>
-      </c>
-      <c r="E563" s="2" t="inlineStr">
-        <is>
-          <t>prov_fiscal_actual</t>
-        </is>
-      </c>
-      <c r="F563" s="2" t="inlineStr">
-        <is>
-          <t>La provincia de residencia coincide con la provincia fiscal</t>
-        </is>
-      </c>
-      <c r="G563" s="2" t="inlineStr">
-        <is>
-          <t>Dominio (Seg. Social / lógica)</t>
-        </is>
-      </c>
-      <c r="H563" s="2" t="inlineStr">
-        <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
-        </is>
-      </c>
-      <c r="I563" s="2" t="inlineStr">
-        <is>
-          <t>(domic_resid_habitual IS NOT NULL AND domic_resid_habitual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND split_part(prov_fiscal_actual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
-        </is>
-      </c>
-      <c r="J563" s="2" t="inlineStr">
-        <is>
-          <t>El domicilio fiscal es el del 31-12-2024; puede haber mudanzas</t>
-        </is>
-      </c>
-      <c r="K563" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K563"/>
+  <autoFilter ref="A1:K562"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30193,7 +30140,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5">
@@ -30203,7 +30150,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="6"/>
@@ -30226,7 +30173,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -30269,7 +30216,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14">

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -18068,12 +18068,12 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>tiempo desde inicio de vida laboral = (fin − primer empleo)/365,25 (±0,05); fin = corte, o el fallecimiento si murió antes</t>
+          <t>tiempo desde inicio de vida laboral ≥ (fin − primer empleo)/365,25 (−0,05); fin = corte, o el fallecimiento si murió antes</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>Inicio de vida laboral = primer empleo (confirmado por el usuario). La vida laboral de un fallecido termina en el fallecimiento (regla corregida 2026-09-21)</t>
+          <t>Regla corregida 2026-09-23: el inicio de vida laboral NO es el primer empleo real, es el primer episodio de CUALQUIER tipo (Fecha_inicio_vida_laboral_total, decision explicita del usuario 2026-09-08 - ver etl/personas_extendida.py), que puede ser bastante anterior si el primer episodio fue una prestacion/asimilado. T solo puede ser MAYOR o igual que lo calculado desde el primer empleo real, nunca menor (verificado con datos reales: de 8.612 incumplimientos con la igualdad estricta, 8.612 eran T mayor de lo esperado -osea, correcto por diseño- y 0 eran T menor -que si seria una anomalia real). Esta version solo marca el caso realmente anomalo.</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -18083,7 +18083,7 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl IS NOT NULL AND fecha_ini_primer_empleo IS NOT NULL AND ABS(tiempo_total_desde_inicio_vl - date_diff('day', fecha_ini_primer_empleo, LEAST(DATE '2025-05-01', CASE WHEN COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0 THEN last_day(make_date(CAST(fecha_fallecimiento // 100 AS INTEGER), CAST(fecha_fallecimiento % 100 AS INTEGER), 1)) ELSE DATE '2025-05-01' END)) / 365.25) &gt; 0.05</t>
+          <t>tiempo_total_desde_inicio_vl IS NOT NULL AND fecha_ini_primer_empleo IS NOT NULL AND tiempo_total_desde_inicio_vl &lt; date_diff('day', fecha_ini_primer_empleo, LEAST(DATE '2025-05-01', CASE WHEN COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0 THEN last_day(make_date(CAST(fecha_fallecimiento // 100 AS INTEGER), CAST(fecha_fallecimiento % 100 AS INTEGER), 1)) ELSE DATE '2025-05-01' END)) / 365.25 - 0.05</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr"/>
@@ -18121,12 +18121,12 @@
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>edad al fin de la vida laboral − tiempo desde inicio ≈ edad al inicio del primer empleo (±0,5)</t>
+          <t>edad al fin de la vida laboral − tiempo desde inicio ≤ edad al inicio del primer empleo (+0,5)</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>Inicio de vida laboral = primer empleo (confirmado por el usuario)</t>
+          <t>Regla corregida 2026-09-23, mismo motivo que la anterior: la 'edad al inicio de vida laboral' resultante (edad_fin_vl - T) solo puede ser MENOR o igual que la edad al inicio del primer empleo real, nunca mayor (verificado: de 6.749 incumplimientos con la igualdad estricta, los 6.749 eran del lado esperado por diseño, 0 anomalos).</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
@@ -18136,7 +18136,7 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl IS NOT NULL AND fecha_ini_primer_empleo IS NOT NULL AND ABS(date_diff('day', fecha_nacimiento, LEAST(DATE '2025-05-01', CASE WHEN COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0 THEN last_day(make_date(CAST(fecha_fallecimiento // 100 AS INTEGER), CAST(fecha_fallecimiento % 100 AS INTEGER), 1)) ELSE DATE '2025-05-01' END)) / 365.25 - tiempo_total_desde_inicio_vl - date_diff('day', fecha_nacimiento, fecha_ini_primer_empleo) / 365.25) &gt; 0.5</t>
+          <t>tiempo_total_desde_inicio_vl IS NOT NULL AND fecha_ini_primer_empleo IS NOT NULL AND (date_diff('day', fecha_nacimiento, LEAST(DATE '2025-05-01', CASE WHEN COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0 THEN last_day(make_date(CAST(fecha_fallecimiento // 100 AS INTEGER), CAST(fecha_fallecimiento % 100 AS INTEGER), 1)) ELSE DATE '2025-05-01' END)) / 365.25 - tiempo_total_desde_inicio_vl) &gt; date_diff('day', fecha_nacimiento, fecha_ini_primer_empleo) / 365.25 + 0.5</t>
         </is>
       </c>
       <c r="J334" s="2" t="inlineStr"/>
@@ -30262,7 +30262,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Inicio de vida laboral = primer empleo (confirmado por el usuario). La vida laboral de un fallecido termina en el fallecimiento (regla corregida 2026-09-21)</t>
+          <t>Regla corregida 2026-09-23: el inicio de vida laboral NO es el primer empleo real, es el primer episodio de CUALQUIER tipo (Fecha_inicio_vida_laboral_total, decision explicita del usuario 2026-09-08 - ver etl/personas_extendida.py), que puede ser bastante anterior si el primer episodio fue una prestacion/asimilado. T solo puede ser MAYOR o igual que lo calculado desde el primer empleo real, nunca menor (verificado con datos reales: de 8.612 incumplimientos con la igualdad estricta, 8.612 eran T mayor de lo esperado -osea, correcto por diseño- y 0 eran T menor -que si seria una anomalia real). Esta version solo marca el caso realmente anomalo.</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -30272,7 +30272,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Inicio de vida laboral = primer empleo (confirmado por el usuario)</t>
+          <t>Regla corregida 2026-09-23, mismo motivo que la anterior: la 'edad al inicio de vida laboral' resultante (edad_fin_vl - T) solo puede ser MENOR o igual que la edad al inicio del primer empleo real, nunca mayor (verificado: de 6.749 incumplimientos con la igualdad estricta, los 6.749 eran del lado esperado por diseño, 0 anomalos).</t>
         </is>
       </c>
       <c r="B19" t="n">

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -9176,7 +9176,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ no está en Alta_ocupado</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ no está en Alta_ocupado</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND situacion_actual_afiliacion = 'Alta_ocupado'</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND situacion_actual_afiliacion = 'Alta_ocupado'</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ ha cotizado alguna vez (no Nunca_ha_cotizado)</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ ha cotizado alguna vez (no Nunca_ha_cotizado)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND situacion_actual_afiliacion = 'Nunca_ha_cotizado'</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND situacion_actual_afiliacion = 'Nunca_ha_cotizado'</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ edad ≥ 16</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND edad_actual_fecha_corte &lt; 16</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND edad_actual_fecha_corte &lt; 16</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ tiene tiempo actual sin empleo</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ tiene tiempo actual sin empleo</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND duracion_actual_sin_empleo IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND duracion_actual_sin_empleo IS NULL</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr"/>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ larga duración: más de 365 días sin empleo</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ larga duración: más de 365 días sin empleo</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND duracion_actual_sin_empleo &lt; 365</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND duracion_actual_sin_empleo &lt; 365</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ tiempo sin empleo ≤ edad − 16 años</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ tiempo sin empleo ≤ edad − 16 años</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - 16</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - 16</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ tiempo actual sin empleo ≤ tiempo desde inicio de vida laboral (+1 año)</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ tiempo actual sin empleo ≤ tiempo desde inicio de vida laboral (+1 año)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND duracion_actual_sin_empleo / 365.25 &gt; tiempo_total_desde_inicio_vl + 1</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND duracion_actual_sin_empleo / 365.25 &gt; tiempo_total_desde_inicio_vl + 1</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr"/>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ tiene historia laboral (tiempo desde inicio &gt; 0)</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ tiene historia laboral (tiempo desde inicio &gt; 0)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND COALESCE(tiempo_total_desde_inicio_vl, 0) = 0</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND COALESCE(tiempo_total_desde_inicio_vl, 0) = 0</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr"/>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ ha trabajado alguna vez (t_total_empleo &gt; 0)</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ ha trabajado alguna vez (t_total_empleo &gt; 0)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND COALESCE(t_total_empleo, 0) = 0</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND COALESCE(t_total_empleo, 0) = 0</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ tiene fecha de primer empleo</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ tiene fecha de primer empleo</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND fecha_ini_primer_empleo IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND fecha_ini_primer_empleo IS NULL</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr"/>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ no fallecido antes de 2025</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ no fallecido antes de 2025</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ edad al final del último empleo ≈ edad actual − tiempo sin empleo (±2)</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ edad al final del último empleo ≈ edad actual − tiempo sin empleo (±2)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND ABS(edad_ultimo_empleo - (edad_actual_fecha_corte - duracion_actual_sin_empleo / 365.25)) &gt; 2</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND ABS(edad_ultimo_empleo - (edad_actual_fecha_corte - duracion_actual_sin_empleo / 365.25)) &gt; 2</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ cobra pensión</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ cobra pensión</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND cobra_pension_2024_5 &lt;&gt; 'SI'</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND cobra_pension_2024_5 &lt;&gt; 'SI'</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ pension_actual informada</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ pension_actual informada</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND pension_actual IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND pension_actual IS NULL</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ sin jubilación (un jubilado no está 'parado')</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ sin jubilación (un jubilado no está 'parado')</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND array_to_string(pension_actual, ',') LIKE '%Jubilaci%'</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND array_to_string(pension_actual, ',') LIKE '%Jubilaci%'</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Debería clasificarse como Pensionista</t>
+          <t>Corregido 2026-09-23: quien cobra jubilación se reclasifica a Pensionista en el ETL, así que esta categoría (renombrada de '_y_pensionista' a '_pension_no_jubilacion') ya no debería tener nunca jubilación - regla de regresión</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista</t>
+          <t>Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ ha cobrado alguna pensión</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ ha cobrado alguna pensión</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND pension_todas_cobradas IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND pension_todas_cobradas IS NULL</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ no está en Alta_ocupado</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ no está en Alta_ocupado</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND situacion_actual_afiliacion = 'Alta_ocupado'</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND situacion_actual_afiliacion = 'Alta_ocupado'</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ ha cotizado alguna vez (no Nunca_ha_cotizado)</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ ha cotizado alguna vez (no Nunca_ha_cotizado)</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND situacion_actual_afiliacion = 'Nunca_ha_cotizado'</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND situacion_actual_afiliacion = 'Nunca_ha_cotizado'</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ edad ≥ 16</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND edad_actual_fecha_corte &lt; 16</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND edad_actual_fecha_corte &lt; 16</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr"/>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ tiene tiempo actual sin empleo</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ tiene tiempo actual sin empleo</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND duracion_actual_sin_empleo IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND duracion_actual_sin_empleo IS NULL</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr"/>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ no es larga duración: ≤ 365 días sin empleo</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ no es larga duración: ≤ 365 días sin empleo</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND duracion_actual_sin_empleo &gt; 365</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND duracion_actual_sin_empleo &gt; 365</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ tiempo sin empleo ≤ edad − 16 años</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ tiempo sin empleo ≤ edad − 16 años</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - 16</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - 16</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ tiempo actual sin empleo ≤ tiempo desde inicio de vida laboral (+1 año)</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ tiempo actual sin empleo ≤ tiempo desde inicio de vida laboral (+1 año)</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND duracion_actual_sin_empleo / 365.25 &gt; tiempo_total_desde_inicio_vl + 1</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND duracion_actual_sin_empleo / 365.25 &gt; tiempo_total_desde_inicio_vl + 1</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ tiene historia laboral (tiempo desde inicio &gt; 0)</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ tiene historia laboral (tiempo desde inicio &gt; 0)</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND COALESCE(tiempo_total_desde_inicio_vl, 0) = 0</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND COALESCE(tiempo_total_desde_inicio_vl, 0) = 0</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr"/>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ ha trabajado alguna vez (t_total_empleo &gt; 0)</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ ha trabajado alguna vez (t_total_empleo &gt; 0)</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND COALESCE(t_total_empleo, 0) = 0</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND COALESCE(t_total_empleo, 0) = 0</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ tiene fecha de primer empleo</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ tiene fecha de primer empleo</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND fecha_ini_primer_empleo IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND fecha_ini_primer_empleo IS NULL</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr"/>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ no fallecido antes de 2025</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ no fallecido antes de 2025</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr"/>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ edad al final del último empleo ≈ edad actual − tiempo sin empleo (±2)</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ edad al final del último empleo ≈ edad actual − tiempo sin empleo (±2)</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND ABS(edad_ultimo_empleo - (edad_actual_fecha_corte - duracion_actual_sin_empleo / 365.25)) &gt; 2</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND ABS(edad_ultimo_empleo - (edad_actual_fecha_corte - duracion_actual_sin_empleo / 365.25)) &gt; 2</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ cobra pensión</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ cobra pensión</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND cobra_pension_2024_5 &lt;&gt; 'SI'</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND cobra_pension_2024_5 &lt;&gt; 'SI'</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ pension_actual informada</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ pension_actual informada</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND pension_actual IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND pension_actual IS NULL</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr"/>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ sin jubilación (un jubilado no está 'parado')</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ sin jubilación (un jubilado no está 'parado')</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND array_to_string(pension_actual, ',') LIKE '%Jubilaci%'</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND array_to_string(pension_actual, ',') LIKE '%Jubilaci%'</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>Debería clasificarse como Pensionista</t>
+          <t>Corregido 2026-09-23: quien cobra jubilación se reclasifica a Pensionista en el ETL, así que esta categoría (renombrada de '_y_pensionista' a '_pension_no_jubilacion') ya no debería tener nunca jubilación - regla de regresión</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista</t>
+          <t>Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ ha cobrado alguna pensión</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ ha cobrado alguna pensión</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND pension_todas_cobradas IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND pension_todas_cobradas IS NULL</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr"/>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>Si cobra pensión ⇒ la categoría contiene 'pensionista'</t>
+          <t>Si cobra pensión ⇒ la categoría es una de las que implican pensión</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 = 'SI' AND situacion_paro_ocupacion NOT LIKE '%ensionista'</t>
+          <t>cobra_pension_2024_5 = 'SI' AND situacion_paro_ocupacion NOT IN ('Ocupado_y_pensionista','Parado_LD_pension_no_jubilacion','Parado_NoLD_pension_no_jubilacion','Pensionista')</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr"/>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Si la categoría contiene 'pensionista' ⇒ cobra pensión</t>
+          <t>Si la categoría implica pensión ⇒ cobra pensión</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion LIKE '%ensionista' AND cobra_pension_2024_5 &lt;&gt; 'SI'</t>
+          <t>situacion_paro_ocupacion IN ('Ocupado_y_pensionista','Parado_LD_pension_no_jubilacion','Parado_NoLD_pension_no_jubilacion','Pensionista') AND cobra_pension_2024_5 &lt;&gt; 'SI'</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr"/>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_y_pensionista ⇒ edad ≤ 100</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ edad ≤ 100</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_y_pensionista' AND edad_actual_fecha_corte &gt; 100</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND edad_actual_fecha_corte &gt; 100</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr"/>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_y_pensionista ⇒ edad ≤ 100</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ edad ≤ 100</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_y_pensionista' AND edad_actual_fecha_corte &gt; 100</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND edad_actual_fecha_corte &gt; 100</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr"/>
@@ -23377,7 +23377,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion NOT IN ('Ocupado','Ocupado_y_pensionista','Pensionista','Parado_LD','Parado_LD_y_pensionista','Parado_NoLD','Parado_NoLD_y_pensionista')</t>
+          <t>situacion_paro_ocupacion NOT IN ('Ocupado','Ocupado_y_pensionista','Pensionista','Parado_LD','Parado_LD_pension_no_jubilacion','Parado_NoLD','Parado_NoLD_pension_no_jubilacion')</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr"/>
@@ -30481,7 +30481,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B · Parado_LD_y_pensionista</t>
+          <t>B · Parado_LD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -30501,7 +30501,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B · Parado_NoLD_y_pensionista</t>
+          <t>B · Parado_NoLD_pension_no_jubilacion</t>
         </is>
       </c>
       <c r="B43" t="n">

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -2570,10 +2570,14 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND fecha_ini_primer_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND fecha_ini_primer_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2729,10 +2733,14 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND t_total_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND t_total_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2782,10 +2790,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND num_altas_anual_promedio IS NULL</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr"/>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND num_altas_anual_promedio IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2941,10 +2953,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND edad_ultimo_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr"/>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND edad_ultimo_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8880,12 +8896,12 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD' AND COALESCE(t_total_empleo, 0) = 0</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD' AND COALESCE(t_total_empleo, 0) = 0 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Alguien puede haber tenido solo prestaciones</t>
+          <t>Alguien puede haber tenido solo prestaciones | Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -8937,10 +8953,14 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD' AND fecha_ini_primer_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Parado_LD' AND fecha_ini_primer_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10506,12 +10526,12 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND COALESCE(t_total_empleo, 0) = 0</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND COALESCE(t_total_empleo, 0) = 0 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Alguien puede haber tenido solo prestaciones</t>
+          <t>Alguien puede haber tenido solo prestaciones | Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -10563,10 +10583,14 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND fecha_ini_primer_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND fecha_ini_primer_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16594,10 +16618,14 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja &lt; fecha_ini_primer_empleo</t>
-        </is>
-      </c>
-      <c r="J304" s="2" t="inlineStr"/>
+          <t>fecha_ultima_baja &lt; fecha_ini_primer_empleo AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -19086,10 +19114,14 @@
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="J352" s="2" t="inlineStr"/>
+          <t>fecha_ini_primer_empleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -19192,10 +19224,14 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="J354" s="2" t="inlineStr"/>
+          <t>t_total_empleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -19298,10 +19334,14 @@
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>num_altas_anual_promedio IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="J356" s="2" t="inlineStr"/>
+          <t>num_altas_anual_promedio IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -19510,10 +19550,14 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>edad_ultimo_empleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="J360" s="2" t="inlineStr"/>
+          <t>edad_ultimo_empleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -19616,10 +19660,14 @@
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL</t>
-        </is>
-      </c>
-      <c r="J362" s="2" t="inlineStr"/>
+          <t>t_total_desempleo IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26183,10 +26231,14 @@
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>duracion_1er_empleo_signif &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1</t>
-        </is>
-      </c>
-      <c r="J489" s="2" t="inlineStr"/>
+          <t>duracion_1er_empleo_signif &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J489" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26998,10 +27050,14 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND fecha_ini_primer_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J504" s="2" t="inlineStr"/>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND fecha_ini_primer_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -30153,7 +30209,6 @@
         <v>561</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -30196,7 +30251,6 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -30290,7 +30344,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
         <v>1</v>
       </c>
@@ -30305,7 +30358,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -21890,10 +21890,14 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>(prov_nacimiento IS NOT NULL AND prov_nacimiento NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND pais_nacimiento NOT LIKE 'N00%' AND pais_nacimiento &lt;&gt; 'NO CONSTA'</t>
-        </is>
-      </c>
-      <c r="J404" s="2" t="inlineStr"/>
+          <t>(prov_nacimiento IS NOT NULL AND prov_nacimiento NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND pais_nacimiento NOT LIKE 'N00%' AND pais_nacimiento &lt;&gt; 'NO CONSTA' AND pais_nacimiento NOT LIKE 'N99%'</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>Regla ajustada 2026-09-24: 'N99 No consta' también es país desconocido.</t>
+        </is>
+      </c>
       <c r="K404" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25898,7 +25902,7 @@
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>Causas de baja distintas ≤ bajas totales + 2</t>
+          <t>Causas de baja distintas coincide con las causas distintas de todos sus episodios en Afiliación</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
@@ -25913,10 +25917,14 @@
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND causas_baja_distintas &gt; ROUND(COALESCE(num_bajas_anual_promedio,0) * tiempo_total_desde_inicio_vl) + 2</t>
-        </is>
-      </c>
-      <c r="J483" s="2" t="inlineStr"/>
+          <t>causas_baja_distintas IS NOT NULL AND causas_baja_distintas &lt;&gt; (SELECT n FROM causas_por_persona c WHERE c.ipf = personas.ipf)</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>Regla reformulada 2026-09-24: la anterior comparaba con num_bajas (solo bajas de empleo real) y ese universo no es el de causas_baja_distintas (todos los episodios, prestaciones incluidas): 4.140 falsos incumplimientos, 0 personas con más causas que episodios.</t>
+        </is>
+      </c>
       <c r="K483" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26997,10 +27005,14 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo &gt; 0 AND num_bajas_anual_promedio IS NULL</t>
-        </is>
-      </c>
-      <c r="J503" s="2" t="inlineStr"/>
+          <t>t_total_desempleo &gt; 0 AND num_bajas_anual_promedio IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones) AND situacion_actual_afiliacion &lt;&gt; 'Alta_ocupado'</t>
+        </is>
+      </c>
+      <c r="J503" s="2" t="inlineStr">
+        <is>
+          <t>Regla ajustada 2026-09-24: excluye solo-prestaciones (G08) y empleo aún abierto (Alta_ocupado: sin bajas pero con tiempo de desempleo).</t>
+        </is>
+      </c>
       <c r="K503" s="2" t="inlineStr">
         <is>
           <t>OK</t>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -22924,7 +22924,7 @@
       <c r="E425" s="2" t="inlineStr"/>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_trabajo_ppal = 'NN NOMBRE' (provincia), 'MAR' o NO CONSTA</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
@@ -22939,10 +22939,14 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal IS NOT NULL AND prov_trabajo_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_trabajo_ppal, '^[0-9]{2} .+')</t>
-        </is>
-      </c>
-      <c r="J425" s="2" t="inlineStr"/>
+          <t>prov_trabajo_ppal IS NOT NULL AND prov_trabajo_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_trabajo_ppal, '^[0-9]{2} .+') AND prov_trabajo_ppal &lt;&gt; 'MAR'</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>Regla ajustada 2026-09-24: 'MAR' (codigos 53/56 del CCC, Regimen del Mar) es una etiqueta valida sin codigo numerico.</t>
+        </is>
+      </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
           <t>OK</t>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -21890,12 +21890,12 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>(prov_nacimiento IS NOT NULL AND prov_nacimiento NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND pais_nacimiento NOT LIKE 'N00%' AND pais_nacimiento &lt;&gt; 'NO CONSTA' AND pais_nacimiento NOT LIKE 'N99%'</t>
+          <t>(prov_nacimiento IS NOT NULL AND prov_nacimiento NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND pais_nacimiento NOT LIKE 'N00%' AND pais_nacimiento &lt;&gt; 'NO CONSTA' AND pais_nacimiento NOT LIKE 'N99%' AND prov_nacimiento &lt;&gt; '66 EXTRANJERO'</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>Regla ajustada 2026-09-24: 'N99 No consta' también es país desconocido.</t>
+          <t>Regla ajustada 2026-09-24: '66 EXTRANJERO' (nacidos en el extranjero, codificacion comun de provincias) no es una provincia española.</t>
         </is>
       </c>
       <c r="K404" s="2" t="inlineStr">
@@ -22924,7 +22924,7 @@
       <c r="E425" s="2" t="inlineStr"/>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal = 'NN NOMBRE' (provincia), 'MAR' o NO CONSTA</t>
+          <t>prov_trabajo_ppal = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
@@ -22939,14 +22939,10 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal IS NOT NULL AND prov_trabajo_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_trabajo_ppal, '^[0-9]{2} .+') AND prov_trabajo_ppal &lt;&gt; 'MAR'</t>
-        </is>
-      </c>
-      <c r="J425" s="2" t="inlineStr">
-        <is>
-          <t>Regla ajustada 2026-09-24: 'MAR' (codigos 53/56 del CCC, Regimen del Mar) es una etiqueta valida sin codigo numerico.</t>
-        </is>
-      </c>
+          <t>prov_trabajo_ppal IS NOT NULL AND prov_trabajo_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_trabajo_ppal, '^[0-9]{2} .+')</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="n"/>
       <c r="K425" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -30140,12 +30136,12 @@
       </c>
       <c r="I562" s="2" t="inlineStr">
         <is>
-          <t>(domic_resid_habitual IS NOT NULL AND domic_resid_habitual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND split_part(prov_fiscal_actual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
+          <t>(domic_resid_habitual IS NOT NULL AND domic_resid_habitual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND CASE WHEN split_part(prov_fiscal_actual, ' ', 1) = '53' THEN '38' ELSE split_part(prov_fiscal_actual, ' ', 1) END &lt;&gt; left(domic_resid_habitual, 2) AND split_part(prov_fiscal_actual, ' ', 1) &lt;&gt; '98'</t>
         </is>
       </c>
       <c r="J562" s="2" t="inlineStr">
         <is>
-          <t>El domicilio fiscal es el del 31-12-2024; puede haber mudanzas</t>
+          <t>El domicilio fiscal es el del 31-12-2024; puede haber mudanzas | Regla ajustada 2026-09-24: el 53 fiscal (Isla de La Palma) es provincia 38 (Santa Cruz de Tenerife) en el INE, y el 98 (residencia fiscal en el extranjero) no es comparable.</t>
         </is>
       </c>
       <c r="K562" s="2" t="inlineStr">

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -28869,7 +28869,7 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal = NO CONSTA ⇔ no hay datos fiscales</t>
+          <t>clave_subclave_ppal = NO CONSTA ⇔ ingresos fiscales nulos o 0</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
@@ -28884,10 +28884,14 @@
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>(clave_subclave_ppal = 'NO CONSTA') &lt;&gt; (ingresos_bruto_total_2024 IS NULL)</t>
-        </is>
-      </c>
-      <c r="J538" s="2" t="inlineStr"/>
+          <t>(clave_subclave_ppal = 'NO CONSTA') &lt;&gt; (COALESCE(ingresos_bruto_total_2024, 0) = 0)</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr">
+        <is>
+          <t>Regla reformulada 2026-09-24: la clave sale de la percepción con más ingresos; las 278 personas con fila fiscal a 0 en todas las partes no tienen ninguna que elegir. La versión anterior (ingresos IS NULL) las marcaba como incumplimiento.</t>
+        </is>
+      </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
           <t>OK</t>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -20452,7 +20452,7 @@
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>Orfandad ⇒ edad ≤ 60</t>
+          <t>Orfandad ⇒ edad ≤ 60, salvo orfandad vitalicia (incapacidad permanente reconocida, sin límite de edad)</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
@@ -20467,12 +20467,12 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>array_to_string(pension_actual, ',') LIKE '%Orfandad%' AND edad_actual_fecha_corte &gt; 60</t>
+          <t>array_to_string(pension_actual, ',') LIKE '%Orfandad%' AND edad_actual_fecha_corte &gt; 60 AND ipf NOT IN (SELECT ipf FROM orfandad_vitalicia)</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>Puede haber orfandad de discapacitados</t>
+          <t>Regla ajustada 2026-09-24: la orfandad no tiene límite de edad si el beneficiario tiene incapacidad permanente (art. 224 LGSS; guía MCVL 4.030 prestación vitalicia). El 99,5 % de las 2.615 anteriores tenía orfandad vitalicia.</t>
         </is>
       </c>
       <c r="K377" s="2" t="inlineStr">

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -8718,7 +8718,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD ⇒ tiempo sin empleo ≤ edad − 16 años</t>
+          <t>Parado_LD ⇒ tiempo sin empleo ≤ edad − mínimo legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - 16</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario); antes de 1980 la edad mínima legal era 14</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD ⇒ tiempo sin empleo ≤ edad − 16 años</t>
+          <t>Parado_NoLD ⇒ tiempo sin empleo ≤ edad − mínimo legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - 16</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario); antes de 1980 la edad mínima legal era 14</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal no puede superar edad − 16 años (+1): no se trabaja antes de los 16</t>
+          <t>t_tot_reg_ppal no puede superar edad − mínimo legal (+1): no se trabaja antes de la edad mínima legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal &gt; edad_actual_fecha_corte - 16 + 1</t>
+          <t>t_tot_reg_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario). Hasta 1980 la edad mínima legal era 14: pueden salir casos antiguos legítimos</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal no puede superar edad − 16 años (+1): no se trabaja antes de los 16</t>
+          <t>t_tot_grupo_ppal no puede superar edad − mínimo legal (+1): no se trabaja antes de la edad mínima legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal &gt; edad_actual_fecha_corte - 16 + 1</t>
+          <t>t_tot_grupo_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario). Hasta 1980 la edad mínima legal era 14: pueden salir casos antiguos legítimos</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>t_tot_tipo_contrato_ppal no puede superar edad − 16 años (+1): no se trabaja antes de los 16</t>
+          <t>t_tot_tipo_contrato_ppal no puede superar edad − mínimo legal (+1): no se trabaja antes de la edad mínima legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -15183,12 +15183,12 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>t_tot_tipo_contrato_ppal &gt; edad_actual_fecha_corte - 16 + 1</t>
+          <t>t_tot_tipo_contrato_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario). Hasta 1980 la edad mínima legal era 14: pueden salir casos antiguos legítimos</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>t_tot_prov_ppal no puede superar edad − 16 años (+1): no se trabaja antes de los 16</t>
+          <t>t_tot_prov_ppal no puede superar edad − mínimo legal (+1): no se trabaja antes de la edad mínima legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>t_tot_prov_ppal &gt; edad_actual_fecha_corte - 16 + 1</t>
+          <t>t_tot_prov_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario). Hasta 1980 la edad mínima legal era 14: pueden salir casos antiguos legítimos</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>t_tot_act_econ_ppal no puede superar edad − 16 años (+1): no se trabaja antes de los 16</t>
+          <t>t_tot_act_econ_ppal no puede superar edad − mínimo legal (+1): no se trabaja antes de la edad mínima legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -15297,12 +15297,12 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>t_tot_act_econ_ppal &gt; edad_actual_fecha_corte - 16 + 1</t>
+          <t>t_tot_act_econ_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario). Hasta 1980 la edad mínima legal era 14: pueden salir casos antiguos legítimos</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo no puede superar edad − 16 años (+1): no se trabaja antes de los 16</t>
+          <t>t_total_empleo no puede superar edad − mínimo legal (+1): no se trabaja antes de la edad mínima legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -15354,12 +15354,12 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo &gt; edad_actual_fecha_corte - 16 + 1</t>
+          <t>t_total_empleo &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario). Hasta 1980 la edad mínima legal era 14: pueden salir casos antiguos legítimos</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>t_contrato_mas_largo no puede superar edad − 16 años (+1): no se trabaja antes de los 16</t>
+          <t>t_contrato_mas_largo no puede superar edad − mínimo legal (+1): no se trabaja antes de la edad mínima legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>t_contrato_mas_largo &gt; edad_actual_fecha_corte - 16 + 1</t>
+          <t>t_contrato_mas_largo &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario). Hasta 1980 la edad mínima legal era 14: pueden salir casos antiguos legítimos</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl no puede superar edad − 16 años (+1): no se trabaja antes de los 16</t>
+          <t>tiempo_total_desde_inicio_vl no puede superar edad − mínimo legal (+1): no se trabaja antes de la edad mínima legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; edad_actual_fecha_corte - 16 + 1</t>
+          <t>tiempo_total_desde_inicio_vl &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>16 años (decisión del usuario). Hasta 1980 la edad mínima legal era 14: pueden salir casos antiguos legítimos</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo a los 16 años o más</t>
+          <t>Primer empleo a la edad mínima legal o más (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
@@ -16565,10 +16565,14 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>date_diff('year', fecha_nacimiento, fecha_ini_primer_empleo) &lt; 16</t>
-        </is>
-      </c>
-      <c r="J303" s="2" t="inlineStr"/>
+          <t>date_diff('year', fecha_nacimiento, fecha_ini_primer_empleo) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+        </is>
+      </c>
       <c r="K303" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16758,7 +16762,7 @@
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>Última baja a los 16 años o más</t>
+          <t>Última baja a la edad mínima legal o más (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
@@ -16773,10 +16777,14 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>date_diff('year', fecha_nacimiento, fecha_ultima_baja) &lt; 16 AND (fecha_ultima_baja IS NULL OR year(fecha_ultima_baja) &lt;&gt; 2099)</t>
-        </is>
-      </c>
-      <c r="J307" s="2" t="inlineStr"/>
+          <t>date_diff('year', fecha_nacimiento, fecha_ultima_baja) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND (fecha_ultima_baja IS NULL OR year(fecha_ultima_baja) &lt;&gt; 2099)</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+        </is>
+      </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16860,7 +16868,7 @@
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>Inicio de racha sin empleo a los 16 años o más</t>
+          <t>Inicio de racha sin empleo a la edad mínima legal o más (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
@@ -16875,10 +16883,14 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>date_diff('year', fecha_nacimiento, fecha_inicio_ultima_racha_sin_empleo) &lt; 16</t>
-        </is>
-      </c>
-      <c r="J309" s="2" t="inlineStr"/>
+          <t>date_diff('year', fecha_nacimiento, fecha_inicio_ultima_racha_sin_empleo) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+        </is>
+      </c>
       <c r="K309" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -17888,7 +17900,7 @@
       <c r="E329" s="2" t="inlineStr"/>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo significativo a los 16 o más</t>
+          <t>Primer empleo significativo a la edad mínima legal o más (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
@@ -17903,10 +17915,14 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>edad_primer_empleo_signif &lt; 16</t>
-        </is>
-      </c>
-      <c r="J329" s="2" t="inlineStr"/>
+          <t>edad_primer_empleo_signif &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+        </is>
+      </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -17937,7 +17953,7 @@
       <c r="E330" s="2" t="inlineStr"/>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>Edad al final del último empleo ≥ 16</t>
+          <t>Edad al final del último empleo ≥ mínimo legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
@@ -17952,10 +17968,14 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>edad_ultimo_empleo &lt; 16</t>
-        </is>
-      </c>
-      <c r="J330" s="2" t="inlineStr"/>
+          <t>edad_ultimo_empleo &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+        </is>
+      </c>
       <c r="K330" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -17990,7 +18010,7 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>edad − tiempo desde inicio de vida laboral ≥ 16</t>
+          <t>edad − tiempo desde inicio de vida laboral ≥ mínimo legal (14 hasta la cohorte 1965, 16 después)</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
@@ -18005,10 +18025,14 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte - tiempo_total_desde_inicio_vl &lt; 16</t>
-        </is>
-      </c>
-      <c r="J331" s="2" t="inlineStr"/>
+          <t>edad_actual_fecha_corte - tiempo_total_desde_inicio_vl &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+        </is>
+      </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
           <t>OK</t>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -8733,12 +8733,12 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND duracion_actual_sin_empleo / 365.25 &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
+          <t>t_tot_reg_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
+          <t>t_tot_grupo_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr">
@@ -15183,12 +15183,12 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>t_tot_tipo_contrato_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
+          <t>t_tot_tipo_contrato_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>t_tot_prov_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
+          <t>t_tot_prov_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr">
@@ -15297,12 +15297,12 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>t_tot_act_econ_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
+          <t>t_tot_act_econ_ppal &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr">
@@ -15354,12 +15354,12 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
+          <t>t_total_empleo &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>t_contrato_mas_largo &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
+          <t>t_contrato_mas_largo &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1</t>
+          <t>tiempo_total_desde_inicio_vl &gt; edad_actual_fecha_corte - (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) + 1 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr">
@@ -16565,12 +16565,12 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>date_diff('year', fecha_nacimiento, fecha_ini_primer_empleo) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+          <t>date_diff('year', fecha_nacimiento, fecha_ini_primer_empleo) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -16777,12 +16777,12 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>date_diff('year', fecha_nacimiento, fecha_ultima_baja) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND (fecha_ultima_baja IS NULL OR year(fecha_ultima_baja) &lt;&gt; 2099)</t>
+          <t>date_diff('year', fecha_nacimiento, fecha_ultima_baja) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND (fecha_ultima_baja IS NULL OR year(fecha_ultima_baja) &lt;&gt; 2099) AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>date_diff('year', fecha_nacimiento, fecha_inicio_ultima_racha_sin_empleo) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+          <t>date_diff('year', fecha_nacimiento, fecha_inicio_ultima_racha_sin_empleo) &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr">
@@ -17915,12 +17915,12 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>edad_primer_empleo_signif &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+          <t>edad_primer_empleo_signif &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J329" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K329" s="2" t="inlineStr">
@@ -17968,12 +17968,12 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>edad_ultimo_empleo &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+          <t>edad_ultimo_empleo &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -18025,12 +18025,12 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte - tiempo_total_desde_inicio_vl &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END)</t>
+          <t>edad_actual_fecha_corte - tiempo_total_desde_inicio_vl &lt; (CASE WHEN year(fecha_nacimiento) &lt;= 1965 THEN 14 ELSE 16 END) AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
         </is>
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos.</t>
+          <t>Mínimo legal por cohorte (decisión del usuario 2026-09-24): 14 años para nacidos hasta 1965 (el Estatuto de los Trabajadores, Ley 8/1980, lo subió a 16) y 16 para los posteriores. Antes: 16 para todos. Excluye a quien tiene algún episodio que empieza antes de esa edad en régimen 0112 (artistas) o en sectores de espectáculos/artes/publicidad/deporte (menores autorizados, art. 6.4 ET; ver ejecutar_reglas.py).</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -8881,7 +8881,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD ⇒ ha trabajado alguna vez (t_total_empleo &gt; 0)</t>
+          <t>Parado_LD ⇒ ha trabajado alguna vez (t_total_empleo + t_total_mixto_empl_desempl &gt; 0)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD' AND COALESCE(t_total_empleo, 0) = 0 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD' AND COALESCE(t_total_empleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Alguien puede haber tenido solo prestaciones | Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+          <t>Alguien puede haber tenido solo prestaciones | Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen). | Reformulada 2026-09-24: con la arquitectura EMPLEO/DESEMPLEO/MIXTO sin solape, quien trabajó siempre a la vez que cobraba prestación tiene t_total_empleo = 0 y su tiempo de trabajo en t_total_mixto_empl_desempl (52 personas, de las que 26+26 salían aquí).</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD ⇒ ha trabajado alguna vez (t_total_empleo &gt; 0)</t>
+          <t>Parado_NoLD ⇒ ha trabajado alguna vez (t_total_empleo + t_total_mixto_empl_desempl &gt; 0)</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -10526,12 +10526,12 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND COALESCE(t_total_empleo, 0) = 0 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND COALESCE(t_total_empleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Alguien puede haber tenido solo prestaciones | Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+          <t>Alguien puede haber tenido solo prestaciones | Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen). | Reformulada 2026-09-24: con la arquitectura EMPLEO/DESEMPLEO/MIXTO sin solape, quien trabajó siempre a la vez que cobraba prestación tiene t_total_empleo = 0 y su tiempo de trabajo en t_total_mixto_empl_desempl (52 personas, de las que 26+26 salían aquí).</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -3313,7 +3313,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Alta_ocupado ⇒ no fallecido antes de 2025</t>
+          <t>Alta_ocupado ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion = 'Alta_ocupado' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
+          <t>situacion_actual_afiliacion = 'Alta_ocupado' AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>La guía admite retrasos al registrar fallecimientos, pero no al revés</t>
+          <t>La guía admite retrasos al registrar fallecimientos, pero no al revés | Ajustada 2026-09-25 (decisión del usuario): 'antes de 2024' (&lt;= 202312). En la edición 2024, quien falleció DURANTE 2024 aún cobraba prestación o pensión ese año: las 3.115 incumplidoras anteriores fallecieron todas en 2024.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Asimilado_otros ⇒ no fallecido antes de 2025</t>
+          <t>Asimilado_otros ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -6161,10 +6161,14 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion = 'Asimilado_otros' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr"/>
+          <t>situacion_actual_afiliacion = 'Asimilado_otros' AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Ajustada 2026-09-25 (decisión del usuario): 'antes de 2024' (&lt;= 202312). En la edición 2024, quien falleció DURANTE 2024 aún cobraba prestación o pensión ese año: las 3.115 incumplidoras anteriores fallecieron todas en 2024.</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6676,7 +6680,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Ocupado ⇒ no fallecido antes de 2025</t>
+          <t>Ocupado ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -6691,10 +6695,14 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Ocupado' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Ocupado' AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Ajustada 2026-09-25 (decisión del usuario): 'antes de 2024' (&lt;= 202312). En la edición 2024, quien falleció DURANTE 2024 aún cobraba prestación o pensión ese año: las 3.115 incumplidoras anteriores fallecieron todas en 2024.</t>
+        </is>
+      </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7536,7 +7544,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Ocupado_y_pensionista ⇒ no fallecido antes de 2025</t>
+          <t>Ocupado_y_pensionista ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -7551,10 +7559,14 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Ocupado_y_pensionista' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Ocupado_y_pensionista' AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Ajustada 2026-09-25 (decisión del usuario): 'antes de 2024' (&lt;= 202312). En la edición 2024, quien falleció DURANTE 2024 aún cobraba prestación o pensión ese año: las 3.115 incumplidoras anteriores fallecieron todas en 2024.</t>
+        </is>
+      </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8889,7 +8901,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD ⇒ no fallecido antes de 2025</t>
+          <t>Parado_LD ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -8904,10 +8916,14 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Parado_LD' AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>Ajustada 2026-09-25 (decisión del usuario): 'antes de 2024' (&lt;= 202312). En la edición 2024, quien falleció DURANTE 2024 aún cobraba prestación o pensión ese año: las 3.115 incumplidoras anteriores fallecieron todas en 2024.</t>
+        </is>
+      </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9647,7 +9663,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_pension_no_jubilacion ⇒ no fallecido antes de 2025</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -9662,10 +9678,14 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Ajustada 2026-09-25 (decisión del usuario): 'antes de 2024' (&lt;= 202312). En la edición 2024, quien falleció DURANTE 2024 aún cobraba prestación o pensión ese año: las 3.115 incumplidoras anteriores fallecieron todas en 2024.</t>
+        </is>
+      </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10519,7 +10539,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD ⇒ no fallecido antes de 2025</t>
+          <t>Parado_NoLD ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -10534,10 +10554,14 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD' AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>Ajustada 2026-09-25 (decisión del usuario): 'antes de 2024' (&lt;= 202312). En la edición 2024, quien falleció DURANTE 2024 aún cobraba prestación o pensión ese año: las 3.115 incumplidoras anteriores fallecieron todas en 2024.</t>
+        </is>
+      </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11277,7 +11301,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_pension_no_jubilacion ⇒ no fallecido antes de 2025</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -11292,10 +11316,14 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND fecha_fallecimiento BETWEEN 1 AND 202412</t>
-        </is>
-      </c>
-      <c r="J202" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>Ajustada 2026-09-25 (decisión del usuario): 'antes de 2024' (&lt;= 202312). En la edición 2024, quien falleció DURANTE 2024 aún cobraba prestación o pensión ese año: las 3.115 incumplidoras anteriores fallecieron todas en 2024.</t>
+        </is>
+      </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -29303,7 +29331,6 @@
         <v>561</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -29344,7 +29371,6 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -29452,7 +29478,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -17198,7 +17198,7 @@
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>edad_actual = (1-5-2025 − nacimiento)/365,25 (±0,02)</t>
+          <t>Para no fallecidos: edad_actual = (1-5-2025 − nacimiento)/365,25 (±0,02)</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
@@ -17213,10 +17213,14 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>ABS(edad_actual_fecha_corte - date_diff('day', fecha_nacimiento, DATE '2025-05-01') / 365.25) &gt; 0.02</t>
-        </is>
-      </c>
-      <c r="J315" s="2" t="inlineStr"/>
+          <t>ha_fallecido = 'NO' AND ABS(edad_actual_fecha_corte - date_diff('day', fecha_nacimiento, DATE '2025-05-01') / 365.25) &gt; 0.02</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>Ajustada 2026-09-25: los fallecidos tienen la edad calculada a su fecha de fallecimiento (ver C-334).</t>
+        </is>
+      </c>
       <c r="K315" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -29015,7 +29019,7 @@
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>La edad al fallecer es anterior a la edad a fecha de corte</t>
+          <t>Fallecidos: edad_actual_fecha_corte = edad_fallecimiento (la edad se calcula a la fecha de fallecimiento)</t>
         </is>
       </c>
       <c r="G540" s="2" t="inlineStr">
@@ -29030,12 +29034,12 @@
       </c>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = 'SI' AND edad_fallecimiento &gt;= edad_actual_fecha_corte</t>
+          <t>ha_fallecido = 'SI' AND ABS(edad_actual_fecha_corte - edad_fallecimiento) &gt; 0.01</t>
         </is>
       </c>
       <c r="J540" s="2" t="inlineStr">
         <is>
-          <t>Comprobación pedida por el usuario 2026-09-21</t>
+          <t>Comprobación pedida por el usuario 2026-09-21 | Reformulada 2026-09-25 (decisión del usuario): Edad_Actual_Fecha_Corte de los fallecidos se calcula a su fecha de fallecimiento. Con el Parquet anterior a esa regeneración da 18.801 incumplimientos; debe dar 0 tras regenerar.</t>
         </is>
       </c>
       <c r="K540" s="2" t="inlineStr">

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K544"/>
+  <dimension ref="A1:K540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -26478,12 +26478,12 @@
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_pension_y_bajas_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G492" s="2" t="inlineStr">
@@ -26498,7 +26498,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_pension_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_pension_y_bajas_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr"/>
@@ -26759,7 +26759,7 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 IS NOT NULL AND ABS(ingresos_bruto_total_2024 - (ingresos_sueldo_2024 + ingresos_pension_2024 + ingresos_prestacion_2024 + ingresos_actividad_2024 + ingresos_otras_exentas_2024)) &gt; 0.01</t>
+          <t>ingresos_bruto_total_2024 IS NOT NULL AND ABS(ingresos_bruto_total_2024 - (ingresos_sueldo_2024 + ingresos_pension_y_bajas_2024 + ingresos_prestacion_2024 + ingresos_actividad_2024 + ingresos_otras_exentas_2024)) &gt; 0.01</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr"/>
@@ -26840,13 +26840,13 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr"/>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 ≥ 0</t>
+          <t>ingresos_pension_y_bajas_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G499" s="2" t="inlineStr">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 &lt; 0</t>
+          <t>ingresos_pension_y_bajas_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -27139,7 +27139,7 @@
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>C-299</t>
+          <t>C-302</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -27154,17 +27154,17 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>Retenciones ≤ 50 % del total (tipo máximo de IRPF ≈ 47 %)</t>
+          <t>Con ingresos de sueldo ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G505" s="2" t="inlineStr">
@@ -27174,15 +27174,19 @@
       </c>
       <c r="H505" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND retenciones_irpf_2024 &gt; 0.5 * ingresos_bruto_total_2024</t>
-        </is>
-      </c>
-      <c r="J505" s="2" t="inlineStr"/>
+          <t>ingresos_sueldo_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a los menores autorizados (art. 6.4 ET: espectáculos públicos; régimen 0112 de artistas y sectores de espectáculos, artes, publicidad y deporte). Decisión del usuario 2026-09-25.</t>
+        </is>
+      </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27192,7 +27196,7 @@
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>C-300</t>
+          <t>C-303</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -27210,32 +27214,32 @@
           <t>ingresos_sueldo_2024</t>
         </is>
       </c>
-      <c r="E506" s="2" t="inlineStr"/>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>fecha_fallecimiento</t>
+        </is>
+      </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>Sueldo anual ≤ 1.000.000 €</t>
+          <t>Con ingresos de sueldo 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 1000000</t>
-        </is>
-      </c>
-      <c r="J506" s="2" t="inlineStr">
-        <is>
-          <t>Outliers (directivos)</t>
-        </is>
-      </c>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="inlineStr"/>
       <c r="K506" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27245,7 +27249,7 @@
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>C-301</t>
+          <t>C-304</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
@@ -27260,13 +27264,17 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
-        </is>
-      </c>
-      <c r="E507" s="2" t="inlineStr"/>
+          <t>ingresos_prestacion_2024</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>edad_actual_fecha_corte</t>
+        </is>
+      </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>Ingresos de actividad anual ≤ 1.000.000 €</t>
+          <t>Con ingresos de prestación ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G507" s="2" t="inlineStr">
@@ -27276,19 +27284,15 @@
       </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &gt; 1000000</t>
-        </is>
-      </c>
-      <c r="J507" s="2" t="inlineStr">
-        <is>
-          <t>Outliers</t>
-        </is>
-      </c>
+          <t>ingresos_prestacion_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="inlineStr"/>
       <c r="K507" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27298,7 +27302,7 @@
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>C-302</t>
+          <t>C-305</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
@@ -27313,32 +27317,32 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de sueldo ⇒ edad ≥ 16</t>
+          <t>Con ingresos de prestación 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+          <t>ingresos_prestacion_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr"/>
@@ -27351,7 +27355,7 @@
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>C-303</t>
+          <t>C-306</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
@@ -27366,35 +27370,39 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de sueldo 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con ingresos de actividad ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
-        </is>
-      </c>
-      <c r="J509" s="2" t="inlineStr"/>
+          <t>ingresos_actividad_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
+        </is>
+      </c>
+      <c r="J509" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a los menores autorizados (art. 6.4 ET: espectáculos públicos; régimen 0112 de artistas y sectores de espectáculos, artes, publicidad y deporte). Decisión del usuario 2026-09-25.</t>
+        </is>
+      </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27404,7 +27412,7 @@
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>C-304</t>
+          <t>C-307</t>
         </is>
       </c>
       <c r="B510" s="2" t="inlineStr">
@@ -27419,32 +27427,32 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de prestación ⇒ edad ≥ 16</t>
+          <t>Con ingresos de actividad 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+          <t>ingresos_actividad_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr"/>
@@ -27457,7 +27465,7 @@
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>C-305</t>
+          <t>C-308</t>
         </is>
       </c>
       <c r="B511" s="2" t="inlineStr">
@@ -27472,7 +27480,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -27482,7 +27490,7 @@
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de prestación 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con pensiones cobradas en 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
@@ -27497,7 +27505,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+          <t>ingresos_pension_y_bajas_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J511" s="2" t="inlineStr"/>
@@ -27510,7 +27518,7 @@
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>C-306</t>
+          <t>C-309</t>
         </is>
       </c>
       <c r="B512" s="2" t="inlineStr">
@@ -27525,17 +27533,17 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>t_total_desempleo</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de actividad ⇒ edad ≥ 16</t>
+          <t>Con prestación por desempleo en 2024 ⇒ ha tenido tiempo de desempleo</t>
         </is>
       </c>
       <c r="G512" s="2" t="inlineStr">
@@ -27550,10 +27558,14 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
-        </is>
-      </c>
-      <c r="J512" s="2" t="inlineStr"/>
+          <t>ingresos_prestacion_2024 &gt; 0 AND COALESCE(t_total_desempleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0</t>
+        </is>
+      </c>
+      <c r="J512" s="2" t="inlineStr">
+        <is>
+          <t>Los subsidios pueden no figurar como desempleo en afiliación</t>
+        </is>
+      </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27563,7 +27575,7 @@
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>C-307</t>
+          <t>C-310</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
@@ -27578,35 +27590,39 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>fecha_ini_primer_empleo</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de actividad 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con sueldo en 2024 ⇒ tiene primer empleo en afiliación</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
-        </is>
-      </c>
-      <c r="J513" s="2" t="inlineStr"/>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ini_primer_empleo IS NULL</t>
+        </is>
+      </c>
+      <c r="J513" s="2" t="inlineStr">
+        <is>
+          <t>Los funcionarios de MUFACE no cotizan en el sistema de la MCVL</t>
+        </is>
+      </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27616,7 +27632,7 @@
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>C-308</t>
+          <t>C-311</t>
         </is>
       </c>
       <c r="B514" s="2" t="inlineStr">
@@ -27631,35 +27647,39 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>fecha_ultima_baja</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>Con pensiones cobradas en 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con sueldo en 2024 ⇒ la última baja no es anterior a 2024</t>
         </is>
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
-        </is>
-      </c>
-      <c r="J514" s="2" t="inlineStr"/>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ultima_baja IS NOT NULL AND year(fecha_ultima_baja) &lt; 2024</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr">
+        <is>
+          <t>Pagos atrasados o indemnizaciones podrían dar sueldo sin alta en 2024</t>
+        </is>
+      </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27669,7 +27689,7 @@
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>C-309</t>
+          <t>C-313</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
@@ -27684,17 +27704,17 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>Con prestación por desempleo en 2024 ⇒ ha tenido tiempo de desempleo</t>
+          <t>Cobra pensión en la tabla de pensiones ⇒ tiene pensión en fiscal (si consta en fiscal)</t>
         </is>
       </c>
       <c r="G515" s="2" t="inlineStr">
@@ -27704,17 +27724,17 @@
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND COALESCE(t_total_desempleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0</t>
+          <t>cobra_pension_2024_5 = 'SI' AND ingresos_bruto_total_2024 IS NOT NULL AND ingresos_pension_y_bajas_2024 = 0</t>
         </is>
       </c>
       <c r="J515" s="2" t="inlineStr">
         <is>
-          <t>Los subsidios pueden no figurar como desempleo en afiliación</t>
+          <t>Puede haber empezado a cobrar en 2025</t>
         </is>
       </c>
       <c r="K515" s="2" t="inlineStr">
@@ -27726,7 +27746,7 @@
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>C-310</t>
+          <t>C-314</t>
         </is>
       </c>
       <c r="B516" s="2" t="inlineStr">
@@ -27736,22 +27756,22 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>Ingresos por tipo (v2.2)</t>
+          <t>Clave y subclave de percepción (v2.2)</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>clave_subclave_ppal</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>Con sueldo en 2024 ⇒ tiene primer empleo en afiliación</t>
+          <t>clave_subclave_ppal = NO CONSTA ⇔ ingresos fiscales nulos o 0</t>
         </is>
       </c>
       <c r="G516" s="2" t="inlineStr">
@@ -27761,17 +27781,17 @@
       </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I516" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ini_primer_empleo IS NULL</t>
+          <t>(clave_subclave_ppal = 'NO CONSTA') &lt;&gt; (COALESCE(ingresos_bruto_total_2024, 0) = 0)</t>
         </is>
       </c>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>Los funcionarios de MUFACE no cotizan en el sistema de la MCVL</t>
+          <t>Regla reformulada 2026-09-24: la clave sale de la percepción con más ingresos; las 278 personas con fila fiscal a 0 en todas las partes no tienen ninguna que elegir. La versión anterior (ingresos IS NULL) las marcaba como incumplimiento.</t>
         </is>
       </c>
       <c r="K516" s="2" t="inlineStr">
@@ -27783,7 +27803,7 @@
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>C-311</t>
+          <t>C-315</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
@@ -27793,42 +27813,38 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>Ingresos por tipo (v2.2)</t>
+          <t>Clave y subclave de percepción (v2.2)</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
-        </is>
-      </c>
-      <c r="E517" s="2" t="inlineStr">
-        <is>
-          <t>fecha_ultima_baja</t>
-        </is>
-      </c>
+          <t>clave_subclave_ppal</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr"/>
       <c r="F517" s="2" t="inlineStr">
         <is>
-          <t>Con sueldo en 2024 ⇒ la última baja no es anterior a 2024</t>
+          <t>clave_subclave_ppal = 'letra + 2 (dígito/X)' con etiqueta, o NO CONSTA</t>
         </is>
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ultima_baja IS NOT NULL AND year(fecha_ultima_baja) &lt; 2024</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(clave_subclave_ppal, '^[ABCFGHL][0-9X]{2}( .+)?$')</t>
         </is>
       </c>
       <c r="J517" s="2" t="inlineStr">
         <is>
-          <t>Pagos atrasados o indemnizaciones podrían dar sueldo sin alta en 2024</t>
+          <t>Claves del modelo 190 presentes en la MCVL: A, B, C, F, G, H, L</t>
         </is>
       </c>
       <c r="K517" s="2" t="inlineStr">
@@ -27840,7 +27856,7 @@
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>C-312</t>
+          <t>C-316</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
@@ -27850,44 +27866,36 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>Ingresos por tipo (v2.2)</t>
+          <t>Clave y subclave de percepción (v2.2)</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
-        </is>
-      </c>
-      <c r="E518" s="2" t="inlineStr">
-        <is>
-          <t>cobra_pension_2024_5</t>
-        </is>
-      </c>
+          <t>clave_subclave_ppal</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr"/>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>Con pensión en fiscal ⇒ cobra pensión en la tabla de pensiones</t>
+          <t>Cada código de clave+subclave tiene una única etiqueta</t>
         </is>
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024 &gt; 0 AND cobra_pension_2024_5 = 'NO'</t>
-        </is>
-      </c>
-      <c r="J518" s="2" t="inlineStr">
-        <is>
-          <t>Mutualidades y Clases Pasivas pueden no estar en la tabla de pensiones de la MCVL</t>
-        </is>
-      </c>
+          <t>split_part(clave_subclave_ppal, ' ', 1) IN (SELECT split_part(clave_subclave_ppal, ' ', 1) FROM personas WHERE clave_subclave_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT clave_subclave_ppal) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="inlineStr"/>
       <c r="K518" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27897,7 +27905,7 @@
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>C-313</t>
+          <t>C-317</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
@@ -27907,44 +27915,40 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>Ingresos por tipo (v2.2)</t>
+          <t>Clave y subclave de percepción (v2.2)</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>clave_subclave_ppal</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>Cobra pensión en la tabla de pensiones ⇒ tiene pensión en fiscal (si consta en fiscal)</t>
+          <t>Tipo principal de sueldo (A) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 = 'SI' AND ingresos_bruto_total_2024 IS NOT NULL AND ingresos_pension_2024 = 0</t>
-        </is>
-      </c>
-      <c r="J519" s="2" t="inlineStr">
-        <is>
-          <t>Puede haber empezado a cobrar en 2025</t>
-        </is>
-      </c>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'A%' AND COALESCE(ingresos_sueldo_2024, 0) &lt;= 0</t>
+        </is>
+      </c>
+      <c r="J519" s="2" t="inlineStr"/>
       <c r="K519" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27954,7 +27958,7 @@
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>C-314</t>
+          <t>C-318</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
@@ -27974,12 +27978,12 @@
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal = NO CONSTA ⇔ ingresos fiscales nulos o 0</t>
+          <t>Tipo principal de pensión (B, L06, L07, L08) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G520" s="2" t="inlineStr">
@@ -27994,14 +27998,10 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>(clave_subclave_ppal = 'NO CONSTA') &lt;&gt; (COALESCE(ingresos_bruto_total_2024, 0) = 0)</t>
-        </is>
-      </c>
-      <c r="J520" s="2" t="inlineStr">
-        <is>
-          <t>Regla reformulada 2026-09-24: la clave sale de la percepción con más ingresos; las 278 personas con fila fiscal a 0 en todas las partes no tienen ninguna que elegir. La versión anterior (ingresos IS NULL) las marcaba como incumplimiento.</t>
-        </is>
-      </c>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'B%' OR split_part(clave_subclave_ppal, ' ', 1) IN ('L06','L07','L08')) AND COALESCE(ingresos_pension_y_bajas_2024, 0) &lt;= 0</t>
+        </is>
+      </c>
+      <c r="J520" s="2" t="inlineStr"/>
       <c r="K520" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28011,7 +28011,7 @@
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>C-315</t>
+          <t>C-319</t>
         </is>
       </c>
       <c r="B521" s="2" t="inlineStr">
@@ -28029,15 +28029,19 @@
           <t>clave_subclave_ppal</t>
         </is>
       </c>
-      <c r="E521" s="2" t="inlineStr"/>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_prestacion_2024</t>
+        </is>
+      </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal = 'letra + 2 (dígito/X)' con etiqueta, o NO CONSTA</t>
+          <t>Tipo principal de prestación (C) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
@@ -28047,14 +28051,10 @@
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(clave_subclave_ppal, '^[ABCFGHL][0-9X]{2}( .+)?$')</t>
-        </is>
-      </c>
-      <c r="J521" s="2" t="inlineStr">
-        <is>
-          <t>Claves del modelo 190 presentes en la MCVL: A, B, C, F, G, H, L</t>
-        </is>
-      </c>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'C%' AND COALESCE(ingresos_prestacion_2024, 0) &lt;= 0</t>
+        </is>
+      </c>
+      <c r="J521" s="2" t="inlineStr"/>
       <c r="K521" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28064,7 +28064,7 @@
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>C-316</t>
+          <t>C-320</t>
         </is>
       </c>
       <c r="B522" s="2" t="inlineStr">
@@ -28082,10 +28082,14 @@
           <t>clave_subclave_ppal</t>
         </is>
       </c>
-      <c r="E522" s="2" t="inlineStr"/>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_actividad_2024</t>
+        </is>
+      </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>Cada código de clave+subclave tiene una única etiqueta</t>
+          <t>Tipo principal de actividad (F, G, H) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
@@ -28100,7 +28104,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>split_part(clave_subclave_ppal, ' ', 1) IN (SELECT split_part(clave_subclave_ppal, ' ', 1) FROM personas WHERE clave_subclave_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT clave_subclave_ppal) &gt; 1)</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'F%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'G%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'H%') AND COALESCE(ingresos_actividad_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr"/>
@@ -28113,7 +28117,7 @@
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>C-317</t>
+          <t>C-321</t>
         </is>
       </c>
       <c r="B523" s="2" t="inlineStr">
@@ -28133,12 +28137,12 @@
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_otras_exentas_2024</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de sueldo (A) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de otras exentas (resto de L) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G523" s="2" t="inlineStr">
@@ -28153,7 +28157,7 @@
       </c>
       <c r="I523" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'A%' AND COALESCE(ingresos_sueldo_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'L%' AND split_part(clave_subclave_ppal, ' ', 1) NOT IN ('L06','L07','L08')) AND COALESCE(ingresos_otras_exentas_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J523" s="2" t="inlineStr"/>
@@ -28166,7 +28170,7 @@
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>C-318</t>
+          <t>C-322</t>
         </is>
       </c>
       <c r="B524" s="2" t="inlineStr">
@@ -28181,17 +28185,17 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal</t>
+          <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_2024</t>
+          <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de pensión (B, L06, L07, L08) ⇒ ese importe es positivo</t>
+          <t>Con lista de tipos cobrados ⇒ total de ingresos &gt; 0</t>
         </is>
       </c>
       <c r="G524" s="2" t="inlineStr">
@@ -28206,7 +28210,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'B%' OR split_part(clave_subclave_ppal, ' ', 1) IN ('L06','L07','L08')) AND COALESCE(ingresos_pension_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND COALESCE(ingresos_bruto_total_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr"/>
@@ -28219,7 +28223,7 @@
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>C-319</t>
+          <t>C-323</t>
         </is>
       </c>
       <c r="B525" s="2" t="inlineStr">
@@ -28234,17 +28238,17 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal</t>
+          <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de prestación (C) ⇒ ese importe es positivo</t>
+          <t>Total de ingresos &gt; 0 ⇒ hay lista de tipos cobrados</t>
         </is>
       </c>
       <c r="G525" s="2" t="inlineStr">
@@ -28259,7 +28263,7 @@
       </c>
       <c r="I525" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'C%' AND COALESCE(ingresos_prestacion_2024, 0) &lt;= 0</t>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND clave_subclave_todas_cobradas IS NULL</t>
         </is>
       </c>
       <c r="J525" s="2" t="inlineStr"/>
@@ -28272,7 +28276,7 @@
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>C-320</t>
+          <t>C-324</t>
         </is>
       </c>
       <c r="B526" s="2" t="inlineStr">
@@ -28287,17 +28291,17 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
+          <t>clave_subclave_todas_cobradas</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
           <t>clave_subclave_ppal</t>
         </is>
       </c>
-      <c r="E526" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_actividad_2024</t>
-        </is>
-      </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de actividad (F, G, H) ⇒ ese importe es positivo</t>
+          <t>El primer tipo cobrado es el tipo principal</t>
         </is>
       </c>
       <c r="G526" s="2" t="inlineStr">
@@ -28312,7 +28316,7 @@
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'F%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'G%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'H%') AND COALESCE(ingresos_actividad_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND clave_subclave_todas_cobradas[1] &lt;&gt; split_part(clave_subclave_ppal, ' ', 1)</t>
         </is>
       </c>
       <c r="J526" s="2" t="inlineStr"/>
@@ -28325,7 +28329,7 @@
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>C-321</t>
+          <t>C-325</t>
         </is>
       </c>
       <c r="B527" s="2" t="inlineStr">
@@ -28340,17 +28344,13 @@
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal</t>
-        </is>
-      </c>
-      <c r="E527" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_otras_exentas_2024</t>
-        </is>
-      </c>
+          <t>clave_subclave_todas_cobradas</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr"/>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de otras exentas (resto de L) ⇒ ese importe es positivo</t>
+          <t>La lista de tipos cobrados no repite códigos</t>
         </is>
       </c>
       <c r="G527" s="2" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="I527" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'L%' AND split_part(clave_subclave_ppal, ' ', 1) NOT IN ('L06','L07','L08')) AND COALESCE(ingresos_otras_exentas_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) &lt;&gt; len(list_distinct(clave_subclave_todas_cobradas))</t>
         </is>
       </c>
       <c r="J527" s="2" t="inlineStr"/>
@@ -28378,7 +28378,7 @@
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>C-322</t>
+          <t>C-326</t>
         </is>
       </c>
       <c r="B528" s="2" t="inlineStr">
@@ -28396,19 +28396,15 @@
           <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
-      <c r="E528" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_bruto_total_2024</t>
-        </is>
-      </c>
+      <c r="E528" s="2" t="inlineStr"/>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>Con lista de tipos cobrados ⇒ total de ingresos &gt; 0</t>
+          <t>Los códigos de la lista tienen formato letra + 2 (dígito/X)</t>
         </is>
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H528" s="2" t="inlineStr">
@@ -28418,7 +28414,7 @@
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND COALESCE(ingresos_bruto_total_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(list_filter(clave_subclave_todas_cobradas, x -&gt; NOT regexp_matches(x, '^[ABCFGHL][0-9X]{2}$'))) &gt; 0</t>
         </is>
       </c>
       <c r="J528" s="2" t="inlineStr"/>
@@ -28431,7 +28427,7 @@
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>C-323</t>
+          <t>C-327</t>
         </is>
       </c>
       <c r="B529" s="2" t="inlineStr">
@@ -28449,14 +28445,10 @@
           <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
-      <c r="E529" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_bruto_total_2024</t>
-        </is>
-      </c>
+      <c r="E529" s="2" t="inlineStr"/>
       <c r="F529" s="2" t="inlineStr">
         <is>
-          <t>Total de ingresos &gt; 0 ⇒ hay lista de tipos cobrados</t>
+          <t>Sin tipos cobrados ⇒ NULL, no lista vacía</t>
         </is>
       </c>
       <c r="G529" s="2" t="inlineStr">
@@ -28466,12 +28458,12 @@
       </c>
       <c r="H529" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I529" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND clave_subclave_todas_cobradas IS NULL</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) = 0</t>
         </is>
       </c>
       <c r="J529" s="2" t="inlineStr"/>
@@ -28484,7 +28476,7 @@
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>C-324</t>
+          <t>C-328</t>
         </is>
       </c>
       <c r="B530" s="2" t="inlineStr">
@@ -28504,12 +28496,12 @@
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>El primer tipo cobrado es el tipo principal</t>
+          <t>A00 en la lista ⇔ sueldo positivo</t>
         </is>
       </c>
       <c r="G530" s="2" t="inlineStr">
@@ -28524,7 +28516,7 @@
       </c>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND clave_subclave_todas_cobradas[1] &lt;&gt; split_part(clave_subclave_ppal, ' ', 1)</t>
+          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'A00'), false) &lt;&gt; (COALESCE(ingresos_sueldo_2024, 0) &gt; 0)</t>
         </is>
       </c>
       <c r="J530" s="2" t="inlineStr"/>
@@ -28537,7 +28529,7 @@
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>C-325</t>
+          <t>C-329</t>
         </is>
       </c>
       <c r="B531" s="2" t="inlineStr">
@@ -28555,10 +28547,14 @@
           <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
-      <c r="E531" s="2" t="inlineStr"/>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_prestacion_2024</t>
+        </is>
+      </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>La lista de tipos cobrados no repite códigos</t>
+          <t>C00 en la lista ⇔ prestación positiva</t>
         </is>
       </c>
       <c r="G531" s="2" t="inlineStr">
@@ -28573,7 +28569,7 @@
       </c>
       <c r="I531" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) &lt;&gt; len(list_distinct(clave_subclave_todas_cobradas))</t>
+          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'C00'), false) &lt;&gt; (COALESCE(ingresos_prestacion_2024, 0) &gt; 0)</t>
         </is>
       </c>
       <c r="J531" s="2" t="inlineStr"/>
@@ -28586,7 +28582,7 @@
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>C-326</t>
+          <t>C-330</t>
         </is>
       </c>
       <c r="B532" s="2" t="inlineStr">
@@ -28596,18 +28592,22 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>Clave y subclave de percepción (v2.2)</t>
+          <t>Fallecimiento (v2.2)</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas</t>
-        </is>
-      </c>
-      <c r="E532" s="2" t="inlineStr"/>
+          <t>ha_fallecido</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>fecha_fallecimiento</t>
+        </is>
+      </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>Los códigos de la lista tienen formato letra + 2 (dígito/X)</t>
+          <t>ha_fallecido = SI ⇔ fecha_fallecimiento informada</t>
         </is>
       </c>
       <c r="G532" s="2" t="inlineStr">
@@ -28622,7 +28622,7 @@
       </c>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(list_filter(clave_subclave_todas_cobradas, x -&gt; NOT regexp_matches(x, '^[ABCFGHL][0-9X]{2}$'))) &gt; 0</t>
+          <t>(ha_fallecido = 'SI') &lt;&gt; (COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0)</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr"/>
@@ -28635,7 +28635,7 @@
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>C-327</t>
+          <t>C-331</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
@@ -28645,18 +28645,22 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>Clave y subclave de percepción (v2.2)</t>
+          <t>Fallecimiento (v2.2)</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas</t>
-        </is>
-      </c>
-      <c r="E533" s="2" t="inlineStr"/>
+          <t>ha_fallecido</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>edad_fallecimiento</t>
+        </is>
+      </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>Sin tipos cobrados ⇒ NULL, no lista vacía</t>
+          <t>ha_fallecido = SI ⇔ edad_fallecimiento informada</t>
         </is>
       </c>
       <c r="G533" s="2" t="inlineStr">
@@ -28666,12 +28670,12 @@
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I533" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) = 0</t>
+          <t>(ha_fallecido = 'SI') &lt;&gt; (edad_fallecimiento IS NOT NULL)</t>
         </is>
       </c>
       <c r="J533" s="2" t="inlineStr"/>
@@ -28684,7 +28688,7 @@
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>C-328</t>
+          <t>C-332</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
@@ -28694,22 +28698,18 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>Clave y subclave de percepción (v2.2)</t>
+          <t>Fallecimiento (v2.2)</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas</t>
-        </is>
-      </c>
-      <c r="E534" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_sueldo_2024</t>
-        </is>
-      </c>
+          <t>edad_fallecimiento</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr"/>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>A00 en la lista ⇔ sueldo positivo</t>
+          <t>edad_fallecimiento ≥ 0 (no se muere antes de nacer)</t>
         </is>
       </c>
       <c r="G534" s="2" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'A00'), false) &lt;&gt; (COALESCE(ingresos_sueldo_2024, 0) &gt; 0)</t>
+          <t>edad_fallecimiento &lt; 0</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr"/>
@@ -28737,7 +28737,7 @@
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>C-329</t>
+          <t>C-333</t>
         </is>
       </c>
       <c r="B535" s="2" t="inlineStr">
@@ -28747,37 +28747,33 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>Clave y subclave de percepción (v2.2)</t>
+          <t>Fallecimiento (v2.2)</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas</t>
-        </is>
-      </c>
-      <c r="E535" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_prestacion_2024</t>
-        </is>
-      </c>
+          <t>edad_fallecimiento</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr"/>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>C00 en la lista ⇔ prestación positiva</t>
+          <t>edad_fallecimiento ≤ 115</t>
         </is>
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I535" s="2" t="inlineStr">
         <is>
-          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'C00'), false) &lt;&gt; (COALESCE(ingresos_prestacion_2024, 0) &gt; 0)</t>
+          <t>edad_fallecimiento &gt; 115</t>
         </is>
       </c>
       <c r="J535" s="2" t="inlineStr"/>
@@ -28790,7 +28786,7 @@
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>C-330</t>
+          <t>C-334</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
@@ -28805,22 +28801,22 @@
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido</t>
+          <t>edad_fallecimiento</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = SI ⇔ fecha_fallecimiento informada</t>
+          <t>Fallecidos: edad_actual_fecha_corte = edad_fallecimiento (la edad se calcula a la fecha de fallecimiento)</t>
         </is>
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
@@ -28830,10 +28826,14 @@
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>(ha_fallecido = 'SI') &lt;&gt; (COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0)</t>
-        </is>
-      </c>
-      <c r="J536" s="2" t="inlineStr"/>
+          <t>ha_fallecido = 'SI' AND ABS(edad_actual_fecha_corte - edad_fallecimiento) &gt; 0.01</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr">
+        <is>
+          <t>Comprobación pedida por el usuario 2026-09-21 | Reformulada 2026-09-25 (decisión del usuario): Edad_Actual_Fecha_Corte de los fallecidos se calcula a su fecha de fallecimiento. Con el Parquet anterior a esa regeneración da 18.801 incumplimientos; debe dar 0 tras regenerar.</t>
+        </is>
+      </c>
       <c r="K536" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28843,7 +28843,7 @@
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>C-331</t>
+          <t>C-335</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
@@ -28858,17 +28858,17 @@
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido</t>
+          <t>edad_fallecimiento</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = SI ⇔ edad_fallecimiento informada</t>
+          <t>edad_fallecimiento = meses entre nacimiento y fallecimiento / 12 (±0,001)</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="I537" s="2" t="inlineStr">
         <is>
-          <t>(ha_fallecido = 'SI') &lt;&gt; (edad_fallecimiento IS NOT NULL)</t>
+          <t>ha_fallecido = 'SI' AND ABS(edad_fallecimiento - (((fecha_fallecimiento // 100 - year(fecha_nacimiento)) * 12 + (fecha_fallecimiento % 100 - month(fecha_nacimiento))) / 12.0)) &gt; 0.001</t>
         </is>
       </c>
       <c r="J537" s="2" t="inlineStr"/>
@@ -28896,7 +28896,7 @@
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>C-332</t>
+          <t>C-336</t>
         </is>
       </c>
       <c r="B538" s="2" t="inlineStr">
@@ -28906,18 +28906,22 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>Fallecimiento (v2.2)</t>
+          <t>Residencia (v2.2)</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento</t>
-        </is>
-      </c>
-      <c r="E538" s="2" t="inlineStr"/>
+          <t>domic_resid_habitual</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>prov_resid_habitual</t>
+        </is>
+      </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento ≥ 0 (no se muere antes de nacer)</t>
+          <t>domicilio NO CONSTA ⇔ provincia de residencia NO CONSTA</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
@@ -28932,7 +28936,7 @@
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento &lt; 0</t>
+          <t>(domic_resid_habitual = 'NO CONSTA') &lt;&gt; (prov_resid_habitual = 'NO CONSTA')</t>
         </is>
       </c>
       <c r="J538" s="2" t="inlineStr"/>
@@ -28945,7 +28949,7 @@
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>C-333</t>
+          <t>C-337</t>
         </is>
       </c>
       <c r="B539" s="2" t="inlineStr">
@@ -28955,33 +28959,37 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>Fallecimiento (v2.2)</t>
+          <t>Residencia (v2.2)</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento</t>
-        </is>
-      </c>
-      <c r="E539" s="2" t="inlineStr"/>
+          <t>domic_resid_habitual</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>prov_resid_habitual</t>
+        </is>
+      </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento ≤ 115</t>
+          <t>El código de provincia del domicilio coincide con prov_resid_habitual</t>
         </is>
       </c>
       <c r="G539" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H539" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I539" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento &gt; 115</t>
+          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND split_part(prov_resid_habitual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
         </is>
       </c>
       <c r="J539" s="2" t="inlineStr"/>
@@ -28994,7 +29002,7 @@
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>C-334</t>
+          <t>C-338</t>
         </is>
       </c>
       <c r="B540" s="2" t="inlineStr">
@@ -29004,261 +29012,45 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>Fallecimiento (v2.2)</t>
+          <t>Residencia (v2.2)</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento</t>
+          <t>domic_resid_habitual</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>prov_fiscal_actual</t>
         </is>
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>Fallecidos: edad_actual_fecha_corte = edad_fallecimiento (la edad se calcula a la fecha de fallecimiento)</t>
+          <t>La provincia de residencia coincide con la provincia fiscal</t>
         </is>
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = 'SI' AND ABS(edad_actual_fecha_corte - edad_fallecimiento) &gt; 0.01</t>
+          <t>(domic_resid_habitual IS NOT NULL AND domic_resid_habitual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND CASE WHEN split_part(prov_fiscal_actual, ' ', 1) = '53' THEN '38' ELSE split_part(prov_fiscal_actual, ' ', 1) END &lt;&gt; left(domic_resid_habitual, 2) AND split_part(prov_fiscal_actual, ' ', 1) &lt;&gt; '98'</t>
         </is>
       </c>
       <c r="J540" s="2" t="inlineStr">
         <is>
-          <t>Comprobación pedida por el usuario 2026-09-21 | Reformulada 2026-09-25 (decisión del usuario): Edad_Actual_Fecha_Corte de los fallecidos se calcula a su fecha de fallecimiento. Con el Parquet anterior a esa regeneración da 18.801 incumplimientos; debe dar 0 tras regenerar.</t>
+          <t>El domicilio fiscal es el del 31-12-2024; puede haber mudanzas | Regla ajustada 2026-09-24: el 53 fiscal (Isla de La Palma) es provincia 38 (Santa Cruz de Tenerife) en el INE, y el 98 (residencia fiscal en el extranjero) no es comparable.</t>
         </is>
       </c>
       <c r="K540" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" s="2" t="inlineStr">
-        <is>
-          <t>C-335</t>
-        </is>
-      </c>
-      <c r="B541" s="2" t="inlineStr">
-        <is>
-          <t>C · otras columnas</t>
-        </is>
-      </c>
-      <c r="C541" s="2" t="inlineStr">
-        <is>
-          <t>Fallecimiento (v2.2)</t>
-        </is>
-      </c>
-      <c r="D541" s="2" t="inlineStr">
-        <is>
-          <t>edad_fallecimiento</t>
-        </is>
-      </c>
-      <c r="E541" s="2" t="inlineStr">
-        <is>
-          <t>fecha_fallecimiento</t>
-        </is>
-      </c>
-      <c r="F541" s="2" t="inlineStr">
-        <is>
-          <t>edad_fallecimiento = meses entre nacimiento y fallecimiento / 12 (±0,001)</t>
-        </is>
-      </c>
-      <c r="G541" s="2" t="inlineStr">
-        <is>
-          <t>Significado del nombre</t>
-        </is>
-      </c>
-      <c r="H541" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="I541" s="2" t="inlineStr">
-        <is>
-          <t>ha_fallecido = 'SI' AND ABS(edad_fallecimiento - (((fecha_fallecimiento // 100 - year(fecha_nacimiento)) * 12 + (fecha_fallecimiento % 100 - month(fecha_nacimiento))) / 12.0)) &gt; 0.001</t>
-        </is>
-      </c>
-      <c r="J541" s="2" t="inlineStr"/>
-      <c r="K541" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" s="2" t="inlineStr">
-        <is>
-          <t>C-336</t>
-        </is>
-      </c>
-      <c r="B542" s="2" t="inlineStr">
-        <is>
-          <t>C · otras columnas</t>
-        </is>
-      </c>
-      <c r="C542" s="2" t="inlineStr">
-        <is>
-          <t>Residencia (v2.2)</t>
-        </is>
-      </c>
-      <c r="D542" s="2" t="inlineStr">
-        <is>
-          <t>domic_resid_habitual</t>
-        </is>
-      </c>
-      <c r="E542" s="2" t="inlineStr">
-        <is>
-          <t>prov_resid_habitual</t>
-        </is>
-      </c>
-      <c r="F542" s="2" t="inlineStr">
-        <is>
-          <t>domicilio NO CONSTA ⇔ provincia de residencia NO CONSTA</t>
-        </is>
-      </c>
-      <c r="G542" s="2" t="inlineStr">
-        <is>
-          <t>Significado del nombre</t>
-        </is>
-      </c>
-      <c r="H542" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="I542" s="2" t="inlineStr">
-        <is>
-          <t>(domic_resid_habitual = 'NO CONSTA') &lt;&gt; (prov_resid_habitual = 'NO CONSTA')</t>
-        </is>
-      </c>
-      <c r="J542" s="2" t="inlineStr"/>
-      <c r="K542" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" s="2" t="inlineStr">
-        <is>
-          <t>C-337</t>
-        </is>
-      </c>
-      <c r="B543" s="2" t="inlineStr">
-        <is>
-          <t>C · otras columnas</t>
-        </is>
-      </c>
-      <c r="C543" s="2" t="inlineStr">
-        <is>
-          <t>Residencia (v2.2)</t>
-        </is>
-      </c>
-      <c r="D543" s="2" t="inlineStr">
-        <is>
-          <t>domic_resid_habitual</t>
-        </is>
-      </c>
-      <c r="E543" s="2" t="inlineStr">
-        <is>
-          <t>prov_resid_habitual</t>
-        </is>
-      </c>
-      <c r="F543" s="2" t="inlineStr">
-        <is>
-          <t>El código de provincia del domicilio coincide con prov_resid_habitual</t>
-        </is>
-      </c>
-      <c r="G543" s="2" t="inlineStr">
-        <is>
-          <t>Significado del nombre</t>
-        </is>
-      </c>
-      <c r="H543" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="I543" s="2" t="inlineStr">
-        <is>
-          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND split_part(prov_resid_habitual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
-        </is>
-      </c>
-      <c r="J543" s="2" t="inlineStr"/>
-      <c r="K543" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" s="2" t="inlineStr">
-        <is>
-          <t>C-338</t>
-        </is>
-      </c>
-      <c r="B544" s="2" t="inlineStr">
-        <is>
-          <t>C · otras columnas</t>
-        </is>
-      </c>
-      <c r="C544" s="2" t="inlineStr">
-        <is>
-          <t>Residencia (v2.2)</t>
-        </is>
-      </c>
-      <c r="D544" s="2" t="inlineStr">
-        <is>
-          <t>domic_resid_habitual</t>
-        </is>
-      </c>
-      <c r="E544" s="2" t="inlineStr">
-        <is>
-          <t>prov_fiscal_actual</t>
-        </is>
-      </c>
-      <c r="F544" s="2" t="inlineStr">
-        <is>
-          <t>La provincia de residencia coincide con la provincia fiscal</t>
-        </is>
-      </c>
-      <c r="G544" s="2" t="inlineStr">
-        <is>
-          <t>Dominio (Seg. Social / lógica)</t>
-        </is>
-      </c>
-      <c r="H544" s="2" t="inlineStr">
-        <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
-        </is>
-      </c>
-      <c r="I544" s="2" t="inlineStr">
-        <is>
-          <t>(domic_resid_habitual IS NOT NULL AND domic_resid_habitual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND CASE WHEN split_part(prov_fiscal_actual, ' ', 1) = '53' THEN '38' ELSE split_part(prov_fiscal_actual, ' ', 1) END &lt;&gt; left(domic_resid_habitual, 2) AND split_part(prov_fiscal_actual, ' ', 1) &lt;&gt; '98'</t>
-        </is>
-      </c>
-      <c r="J544" s="2" t="inlineStr">
-        <is>
-          <t>El domicilio fiscal es el del 31-12-2024; puede haber mudanzas | Regla ajustada 2026-09-24: el 53 fiscal (Isla de La Palma) es provincia 38 (Santa Cruz de Tenerife) en el INE, y el 98 (residencia fiscal en el extranjero) no es comparable.</t>
-        </is>
-      </c>
-      <c r="K544" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -29322,7 +29114,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5">
@@ -29332,9 +29124,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>561</v>
-      </c>
-    </row>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -29375,6 +29168,7 @@
         <v>120</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -29482,6 +29276,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -9553,7 +9553,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Parado_LD_pension_no_jubilacion ⇒ ha trabajado alguna vez (t_total_empleo &gt; 0)</t>
+          <t>Parado_LD_pension_no_jubilacion ⇒ ha trabajado alguna vez (t_total_empleo + t_total_mixto_empl_desempl &gt; 0)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND COALESCE(t_total_empleo, 0) = 0</t>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND COALESCE(t_total_empleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Alguien puede haber tenido solo prestaciones</t>
+          <t>Alguien puede haber tenido solo prestaciones | Reformulada 2026-09-25 (G06, como B-046/B-076): suma el tiempo mixto (trabajo simultáneo con prestación) y excluye a quien solo tiene episodios de prestación o subsidio TRL 7xx/400 (G08, dato de origen).</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -9625,10 +9625,14 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND fecha_ini_primer_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Parado_LD_pension_no_jubilacion' AND fecha_ini_primer_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Reformulada 2026-09-25 (G06): excluye a quien solo tiene episodios de prestación o subsidio TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11191,7 +11195,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Parado_NoLD_pension_no_jubilacion ⇒ ha trabajado alguna vez (t_total_empleo &gt; 0)</t>
+          <t>Parado_NoLD_pension_no_jubilacion ⇒ ha trabajado alguna vez (t_total_empleo + t_total_mixto_empl_desempl &gt; 0)</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -11206,12 +11210,12 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND COALESCE(t_total_empleo, 0) = 0</t>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND COALESCE(t_total_empleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Alguien puede haber tenido solo prestaciones</t>
+          <t>Alguien puede haber tenido solo prestaciones | Reformulada 2026-09-25 (G06, como B-046/B-076): suma el tiempo mixto (trabajo simultáneo con prestación) y excluye a quien solo tiene episodios de prestación o subsidio TRL 7xx/400 (G08, dato de origen).</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -11263,10 +11267,14 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND fecha_ini_primer_empleo IS NULL</t>
-        </is>
-      </c>
-      <c r="J201" s="2" t="inlineStr"/>
+          <t>situacion_paro_ocupacion = 'Parado_NoLD_pension_no_jubilacion' AND fecha_ini_primer_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>Reformulada 2026-09-25 (G06): excluye a quien solo tiene episodios de prestación o subsidio TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -29127,7 +29135,6 @@
         <v>539</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -29168,7 +29175,6 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -29276,7 +29282,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K540"/>
+  <dimension ref="A1:K539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Ocupado' AND ingresos_bruto_total_2024 IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Ocupado' AND ingresos_bruto_total_2024 IS NULL AND prov_trabajo_ppal NOT IN ('01 ÁLAVA','20 GIPUZKOA','48 BIZKAIA','31 NAVARRA') AND ipf NOT IN (SELECT ipf FROM sin_190_esperable)</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Quien empezó a trabajar en 2025 no tiene ingresos 2024</t>
+          <t>Reformulada 2026-09-25 (G15, decisión del usuario): excluye a quien no tiene un modelo 190 esperable: (1) territorios forales (Álava, Guipúzcoa, Navarra y Vizcaya: la AEAT no tiene sus datos fiscales según la guía; 83,6 % de los ocupados sin ingresos frente al 8,0 % del resto), (2) episodio abierto en un régimen distinto del general (autónomos 521, empleados de hogar 138...) y (3) empleador que no es una entidad con NIF/CIF (persona física: hogares o autónomos con un empleado). La hipótesis anterior ('empezó a trabajar en 2025') era falsa: ninguno de los 91.329 empezó en 2025.</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion = 'Ocupado_y_pensionista' AND ingresos_bruto_total_2024 IS NULL</t>
+          <t>situacion_paro_ocupacion = 'Ocupado_y_pensionista' AND ingresos_bruto_total_2024 IS NULL AND prov_trabajo_ppal NOT IN ('01 ÁLAVA','20 GIPUZKOA','48 BIZKAIA','31 NAVARRA') AND ipf NOT IN (SELECT ipf FROM sin_190_esperable)</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Quien empezó a trabajar en 2025 no tiene ingresos 2024</t>
+          <t>Reformulada 2026-09-25 (G15, decisión del usuario): excluye a quien no tiene un modelo 190 esperable: (1) territorios forales (Álava, Guipúzcoa, Navarra y Vizcaya: la AEAT no tiene sus datos fiscales según la guía; 83,6 % de los ocupados sin ingresos frente al 8,0 % del resto), (2) episodio abierto en un régimen distinto del general (autónomos 521, empleados de hogar 138...) y (3) empleador que no es una entidad con NIF/CIF (persona física: hogares o autónomos con un empleado). La hipótesis anterior ('empezó a trabajar en 2025') era falsa: ninguno de los 91.329 empezó en 2025.</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -20544,7 +20544,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>C-169</t>
+          <t>C-170</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -20562,10 +20562,14 @@
           <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
-      <c r="E378" s="2" t="inlineStr"/>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>situacion_actual_afiliacion</t>
+        </is>
+      </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>Ingresos brutos anuales ≤ 1.000.000 €</t>
+          <t>Con ingresos, sin afiliación ni pensión ⇒ raro</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
@@ -20580,14 +20584,10 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 1000000</t>
-        </is>
-      </c>
-      <c r="J378" s="2" t="inlineStr">
-        <is>
-          <t>Outliers (directivos)</t>
-        </is>
-      </c>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND situacion_actual_afiliacion = 'Nunca_ha_cotizado' AND cobra_pension_2024_5 = 'NO'</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
       <c r="K378" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -20597,7 +20597,7 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>C-170</t>
+          <t>C-171</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -20617,27 +20617,27 @@
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos, sin afiliación ni pensión ⇒ raro</t>
+          <t>Con ingresos 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND situacion_actual_afiliacion = 'Nunca_ha_cotizado' AND cobra_pension_2024_5 = 'NO'</t>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr"/>
@@ -20650,7 +20650,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>C-171</t>
+          <t>C-172</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -20665,32 +20665,32 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
+          <t>discap_fiscal</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
           <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>fecha_fallecimiento</t>
-        </is>
-      </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Discapacidad fiscal ⇒ tiene registro de ingresos</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+          <t>discap_fiscal AND ingresos_bruto_total_2024 IS NULL</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr"/>
@@ -20703,7 +20703,7 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>C-172</t>
+          <t>C-173</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -20718,17 +20718,17 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal</t>
+          <t>discap_afiliacion</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>fecha_ini_primer_empleo</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>Discapacidad fiscal ⇒ tiene registro de ingresos</t>
+          <t>Discapacidad en afiliación ⇒ tiene primer empleo</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
@@ -20738,12 +20738,12 @@
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal AND ingresos_bruto_total_2024 IS NULL</t>
+          <t>discap_afiliacion AND fecha_ini_primer_empleo IS NULL</t>
         </is>
       </c>
       <c r="J381" s="2" t="inlineStr"/>
@@ -20756,7 +20756,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>C-173</t>
+          <t>C-174</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -20766,22 +20766,22 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Datos fiscales y discapacidad</t>
+          <t>Nacionalidad y geografía</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion</t>
+          <t>nacionalidad</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>nacionalidad_agrupado</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>Discapacidad en afiliación ⇒ tiene primer empleo</t>
+          <t>Nacionalidad España ⇒ agrupado 'espana'</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
@@ -20796,7 +20796,7 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion AND fecha_ini_primer_empleo IS NULL</t>
+          <t>nacionalidad LIKE 'N00%' AND nacionalidad_agrupado IS DISTINCT FROM 'espana'</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr"/>
@@ -20809,7 +20809,7 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>C-174</t>
+          <t>C-175</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -20824,17 +20824,17 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
+          <t>nacionalidad_agrupado</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
           <t>nacionalidad</t>
         </is>
       </c>
-      <c r="E383" s="2" t="inlineStr">
-        <is>
-          <t>nacionalidad_agrupado</t>
-        </is>
-      </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>Nacionalidad España ⇒ agrupado 'espana'</t>
+          <t>Agrupado 'espana' ⇒ nacionalidad España</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad LIKE 'N00%' AND nacionalidad_agrupado IS DISTINCT FROM 'espana'</t>
+          <t>nacionalidad_agrupado = 'espana' AND nacionalidad NOT LIKE 'N00%'</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr"/>
@@ -20862,7 +20862,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>C-175</t>
+          <t>C-176</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -20877,17 +20877,17 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado</t>
+          <t>pais_nacimiento</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad</t>
+          <t>pais_nacim_agrupado</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>Agrupado 'espana' ⇒ nacionalidad España</t>
+          <t>País de nacimiento España ⇒ agrupado 'espana'</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
@@ -20902,7 +20902,7 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado = 'espana' AND nacionalidad NOT LIKE 'N00%'</t>
+          <t>pais_nacimiento LIKE 'N00%' AND pais_nacim_agrupado IS DISTINCT FROM 'espana'</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr"/>
@@ -20915,7 +20915,7 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>C-176</t>
+          <t>C-177</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -20930,17 +20930,17 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
+          <t>pais_nacim_agrupado</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
           <t>pais_nacimiento</t>
         </is>
       </c>
-      <c r="E385" s="2" t="inlineStr">
-        <is>
-          <t>pais_nacim_agrupado</t>
-        </is>
-      </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>País de nacimiento España ⇒ agrupado 'espana'</t>
+          <t>Agrupado 'espana' ⇒ país de nacimiento España</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento LIKE 'N00%' AND pais_nacim_agrupado IS DISTINCT FROM 'espana'</t>
+          <t>pais_nacim_agrupado = 'espana' AND pais_nacimiento NOT LIKE 'N00%'</t>
         </is>
       </c>
       <c r="J385" s="2" t="inlineStr"/>
@@ -20968,7 +20968,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>C-177</t>
+          <t>C-178</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -20983,17 +20983,17 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado</t>
+          <t>nacionalidad</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento</t>
+          <t>nacionalidad_agrupado</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>Agrupado 'espana' ⇒ país de nacimiento España</t>
+          <t>Cada código de nacionalidad pertenece a un único grupo</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado = 'espana' AND pais_nacimiento NOT LIKE 'N00%'</t>
+          <t>nacionalidad IN (SELECT nacionalidad FROM personas GROUP BY 1 HAVING COUNT(DISTINCT nacionalidad_agrupado) &gt; 1)</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr"/>
@@ -21021,7 +21021,7 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>C-178</t>
+          <t>C-179</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -21036,17 +21036,17 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad</t>
+          <t>pais_nacimiento</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado</t>
+          <t>pais_nacim_agrupado</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>Cada código de nacionalidad pertenece a un único grupo</t>
+          <t>Cada código de país de nacimiento pertenece a un único grupo</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad IN (SELECT nacionalidad FROM personas GROUP BY 1 HAVING COUNT(DISTINCT nacionalidad_agrupado) &gt; 1)</t>
+          <t>pais_nacimiento IN (SELECT pais_nacimiento FROM personas GROUP BY 1 HAVING COUNT(DISTINCT pais_nacim_agrupado) &gt; 1)</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr"/>
@@ -21074,7 +21074,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>C-179</t>
+          <t>C-180</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -21089,17 +21089,17 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
+          <t>prov_nacimiento</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
           <t>pais_nacimiento</t>
         </is>
       </c>
-      <c r="E388" s="2" t="inlineStr">
-        <is>
-          <t>pais_nacim_agrupado</t>
-        </is>
-      </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>Cada código de país de nacimiento pertenece a un único grupo</t>
+          <t>Provincia de nacimiento española ⇒ país de nacimiento España</t>
         </is>
       </c>
       <c r="G388" s="2" t="inlineStr">
@@ -21109,15 +21109,19 @@
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento IN (SELECT pais_nacimiento FROM personas GROUP BY 1 HAVING COUNT(DISTINCT pais_nacim_agrupado) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J388" s="2" t="inlineStr"/>
+          <t>(prov_nacimiento IS NOT NULL AND prov_nacimiento NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND pais_nacimiento NOT LIKE 'N00%' AND pais_nacimiento &lt;&gt; 'NO CONSTA' AND pais_nacimiento NOT LIKE 'N99%' AND prov_nacimiento &lt;&gt; '66 EXTRANJERO'</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>Regla ajustada 2026-09-24: '66 EXTRANJERO' (nacidos en el extranjero, codificacion comun de provincias) no es una provincia española.</t>
+        </is>
+      </c>
       <c r="K388" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21127,7 +21131,7 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>C-180</t>
+          <t>C-181</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -21142,39 +21146,31 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento</t>
-        </is>
-      </c>
-      <c r="E389" s="2" t="inlineStr">
-        <is>
-          <t>pais_nacimiento</t>
-        </is>
-      </c>
+          <t>sexo</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr"/>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>Provincia de nacimiento española ⇒ país de nacimiento España</t>
+          <t>sexo ∈ {Hombre, Mujer, NO CONSTA}</t>
         </is>
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>(prov_nacimiento IS NOT NULL AND prov_nacimiento NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND pais_nacimiento NOT LIKE 'N00%' AND pais_nacimiento &lt;&gt; 'NO CONSTA' AND pais_nacimiento NOT LIKE 'N99%' AND prov_nacimiento &lt;&gt; '66 EXTRANJERO'</t>
-        </is>
-      </c>
-      <c r="J389" s="2" t="inlineStr">
-        <is>
-          <t>Regla ajustada 2026-09-24: '66 EXTRANJERO' (nacidos en el extranjero, codificacion comun de provincias) no es una provincia española.</t>
-        </is>
-      </c>
+          <t>sexo IS NOT NULL AND sexo NOT IN ('Hombre','Mujer','NO CONSTA')</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
       <c r="K389" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -21184,7 +21180,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>C-181</t>
+          <t>C-182</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -21199,13 +21195,13 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>domic_resid_habitual</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr"/>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>sexo ∈ {Hombre, Mujer, NO CONSTA}</t>
+          <t>El domicilio (INE) es NO CONSTA o 5 dígitos con provincia 01-52 (guía 1.007)</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr">
@@ -21220,7 +21216,7 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>sexo IS NOT NULL AND sexo NOT IN ('Hombre','Mujer','NO CONSTA')</t>
+          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND (NOT regexp_matches(domic_resid_habitual, '^[0-9]{5}$') OR CAST(left(domic_resid_habitual, 2) AS INTEGER) NOT BETWEEN 1 AND 52)</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr"/>
@@ -21233,7 +21229,7 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>C-182</t>
+          <t>C-183</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -21248,28 +21244,32 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual</t>
-        </is>
-      </c>
-      <c r="E391" s="2" t="inlineStr"/>
+          <t>prov_1a_afiliacion</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>fecha_ini_primer_empleo</t>
+        </is>
+      </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>El domicilio (INE) es NO CONSTA o 5 dígitos con provincia 01-52 (guía 1.007)</t>
+          <t>Con primer empleo ⇒ provincia de primera afiliación conocida</t>
         </is>
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND (NOT regexp_matches(domic_resid_habitual, '^[0-9]{5}$') OR CAST(left(domic_resid_habitual, 2) AS INTEGER) NOT BETWEEN 1 AND 52)</t>
+          <t>fecha_ini_primer_empleo IS NOT NULL AND NOT (prov_1a_afiliacion IS NOT NULL AND prov_1a_afiliacion NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta'))</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr"/>
@@ -21282,7 +21282,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>C-183</t>
+          <t>C-184</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -21292,22 +21292,22 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Nacionalidad y geografía</t>
+          <t>Coherencia código→etiqueta</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>prov_1a_afiliacion</t>
+          <t>prov_trabajo_ppal</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>prov_fiscal_actual</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>Con primer empleo ⇒ provincia de primera afiliación conocida</t>
+          <t>Cada código de provincia tiene una única etiqueta en las 5 columnas de provincia</t>
         </is>
       </c>
       <c r="G392" s="2" t="inlineStr">
@@ -21317,12 +21317,12 @@
       </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo IS NOT NULL AND NOT (prov_1a_afiliacion IS NOT NULL AND prov_1a_afiliacion NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta'))</t>
+          <t>split_part(prov_trabajo_ppal, ' ', 1) IN (SELECT c FROM (SELECT split_part(p, ' ', 1) c, p FROM (SELECT prov_trabajo_ppal p FROM personas UNION ALL SELECT prov_fiscal_actual FROM personas UNION ALL SELECT prov_nacimiento FROM personas UNION ALL SELECT prov_1a_afiliacion FROM personas UNION ALL SELECT prov_resid_habitual FROM personas) WHERE p &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT p) &gt; 1)</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr"/>
@@ -21335,7 +21335,7 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>C-184</t>
+          <t>C-185</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -21350,17 +21350,17 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal</t>
+          <t>act_econ_ppal</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual</t>
+          <t>act_econ_ult_baja</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>Cada código de provincia tiene una única etiqueta en las 5 columnas de provincia</t>
+          <t>Cada código CNAE tiene una única etiqueta en las 2 columnas de actividad</t>
         </is>
       </c>
       <c r="G393" s="2" t="inlineStr">
@@ -21375,7 +21375,7 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>split_part(prov_trabajo_ppal, ' ', 1) IN (SELECT c FROM (SELECT split_part(p, ' ', 1) c, p FROM (SELECT prov_trabajo_ppal p FROM personas UNION ALL SELECT prov_fiscal_actual FROM personas UNION ALL SELECT prov_nacimiento FROM personas UNION ALL SELECT prov_1a_afiliacion FROM personas UNION ALL SELECT prov_resid_habitual FROM personas) WHERE p &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT p) &gt; 1)</t>
+          <t>split_part(act_econ_ppal, ' ', 1) IN (SELECT c FROM (SELECT split_part(a, ' ', 1) c, a FROM (SELECT act_econ_ppal a FROM personas UNION ALL SELECT act_econ_ult_baja FROM personas) WHERE a &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT a) &gt; 1)</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr"/>
@@ -21388,7 +21388,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>C-185</t>
+          <t>C-186</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -21403,17 +21403,17 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja</t>
+          <t>causa_baja_trab_ppal</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>Cada código CNAE tiene una única etiqueta en las 2 columnas de actividad</t>
+          <t>Cada código de causa de baja tiene una única etiqueta en las 3 columnas de causa</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>split_part(act_econ_ppal, ' ', 1) IN (SELECT c FROM (SELECT split_part(a, ' ', 1) c, a FROM (SELECT act_econ_ppal a FROM personas UNION ALL SELECT act_econ_ult_baja FROM personas) WHERE a &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT a) &gt; 1)</t>
+          <t>split_part(causa_ult_baja, ' ', 1) IN (SELECT c FROM (SELECT split_part(a, ' ', 1) c, a FROM (SELECT causa_ult_baja a FROM personas UNION ALL SELECT causa_baja_trab_ppal FROM personas UNION ALL SELECT causa_baja_mas_comun FROM personas) WHERE a &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT a) &gt; 1)</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr"/>
@@ -21441,7 +21441,7 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>C-186</t>
+          <t>C-187</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -21456,17 +21456,13 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja</t>
-        </is>
-      </c>
-      <c r="E395" s="2" t="inlineStr">
-        <is>
-          <t>causa_baja_trab_ppal</t>
-        </is>
-      </c>
+          <t>grupo_cotiz_ppal</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr"/>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>Cada código de causa de baja tiene una única etiqueta en las 3 columnas de causa</t>
+          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_cotiz_ppal</t>
         </is>
       </c>
       <c r="G395" s="2" t="inlineStr">
@@ -21481,7 +21477,7 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>split_part(causa_ult_baja, ' ', 1) IN (SELECT c FROM (SELECT split_part(a, ' ', 1) c, a FROM (SELECT causa_ult_baja a FROM personas UNION ALL SELECT causa_baja_trab_ppal FROM personas UNION ALL SELECT causa_baja_mas_comun FROM personas) WHERE a &lt;&gt; 'NO CONSTA') GROUP BY c HAVING COUNT(DISTINCT a) &gt; 1)</t>
+          <t>split_part(grupo_cotiz_ppal, ' ', 1) IN (SELECT split_part(grupo_cotiz_ppal, ' ', 1) FROM personas WHERE grupo_cotiz_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_ppal) &gt; 1)</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr"/>
@@ -21494,7 +21490,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>C-187</t>
+          <t>C-188</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -21509,13 +21505,13 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr"/>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_cotiz_ppal</t>
+          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr">
@@ -21530,7 +21526,7 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_cotiz_ppal, ' ', 1) IN (SELECT split_part(grupo_cotiz_ppal, ' ', 1) FROM personas WHERE grupo_cotiz_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_ppal) &gt; 1)</t>
+          <t>split_part(grupo_ultimo_empleo, ' ', 1) IN (SELECT split_part(grupo_ultimo_empleo, ' ', 1) FROM personas WHERE grupo_ultimo_empleo &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_ultimo_empleo) &gt; 1)</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr"/>
@@ -21543,7 +21539,7 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>C-188</t>
+          <t>C-189</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -21558,13 +21554,13 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo</t>
+          <t>grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr"/>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_ultimo_empleo</t>
+          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="G397" s="2" t="inlineStr">
@@ -21579,7 +21575,7 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_ultimo_empleo, ' ', 1) IN (SELECT split_part(grupo_ultimo_empleo, ' ', 1) FROM personas WHERE grupo_ultimo_empleo &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_ultimo_empleo) &gt; 1)</t>
+          <t>split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) IN (SELECT split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) FROM personas WHERE grupo_cotiz_1er_empleo_signif &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_1er_empleo_signif) &gt; 1)</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr"/>
@@ -21592,7 +21588,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>C-189</t>
+          <t>C-190</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -21602,23 +21598,23 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Coherencia código→etiqueta</t>
+          <t>Dominio de valores (guía)</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif</t>
+          <t>grupo_cotiz_ppal</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr"/>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>Cada código de grupo de cotización tiene una única etiqueta en grupo_cotiz_1er_empleo_signif</t>
+          <t>grupo_cotiz_ppal solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -21628,7 +21624,7 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) IN (SELECT split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) FROM personas WHERE grupo_cotiz_1er_empleo_signif &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_1er_empleo_signif) &gt; 1)</t>
+          <t>grupo_cotiz_ppal IS NOT NULL AND NOT regexp_matches(grupo_cotiz_ppal, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
         </is>
       </c>
       <c r="J398" s="2" t="inlineStr"/>
@@ -21641,7 +21637,7 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>C-190</t>
+          <t>C-191</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -21656,13 +21652,13 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr"/>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
+          <t>grupo_ultimo_empleo solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr">
@@ -21677,7 +21673,7 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal IS NOT NULL AND NOT regexp_matches(grupo_cotiz_ppal, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
+          <t>grupo_ultimo_empleo IS NOT NULL AND NOT regexp_matches(grupo_ultimo_empleo, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr"/>
@@ -21690,7 +21686,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>C-191</t>
+          <t>C-192</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -21705,13 +21701,13 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo</t>
+          <t>grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr"/>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
+          <t>grupo_cotiz_1er_empleo_signif solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
@@ -21726,7 +21722,7 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo IS NOT NULL AND NOT regexp_matches(grupo_ultimo_empleo, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
+          <t>grupo_cotiz_1er_empleo_signif IS NOT NULL AND NOT regexp_matches(grupo_cotiz_1er_empleo_signif, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
         </is>
       </c>
       <c r="J400" s="2" t="inlineStr"/>
@@ -21739,7 +21735,7 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>C-192</t>
+          <t>C-193</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -21754,13 +21750,13 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif</t>
+          <t>reg_cotiz_ppal_agrupado</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr"/>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif solo toma valores de la tabla de grupos de cotización (0-12) o NO CONSTA (guía 2.003)</t>
+          <t>reg_cotiz_ppal_agrupado solo toma los regímenes 01, 0138, 05, 06, 07, 08, 09, 12</t>
         </is>
       </c>
       <c r="G401" s="2" t="inlineStr">
@@ -21775,7 +21771,7 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif IS NOT NULL AND NOT regexp_matches(grupo_cotiz_1er_empleo_signif, '^(0 NO CONSTA|NO CONSTA|([1-9]|1[0-2]) .+)$')</t>
+          <t>reg_cotiz_ppal_agrupado IS NOT NULL AND NOT regexp_matches(reg_cotiz_ppal_agrupado, '^(01|0138|05|06|07|08|09|12) .+')</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr"/>
@@ -21788,7 +21784,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>C-193</t>
+          <t>C-194</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -21803,18 +21799,18 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado</t>
+          <t>tipo_contr_ppal_agrupado</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr"/>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado solo toma los regímenes 01, 0138, 05, 06, 07, 08, 09, 12</t>
+          <t>tipo_contr_ppal_agrupado solo toma las 7 categorías de tipo de contrato</t>
         </is>
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -21824,7 +21820,7 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado IS NOT NULL AND NOT regexp_matches(reg_cotiz_ppal_agrupado, '^(01|0138|05|06|07|08|09|12) .+')</t>
+          <t>tipo_contr_ppal_agrupado IS NOT NULL AND tipo_contr_ppal_agrupado NOT IN ('Indefinido_t_completo','No consta','Temporal_t_completo','Indefinido_t_parcial','Temporal_t_parcial','Indefinido_fijo_discontinuo','Otros')</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr"/>
@@ -21837,7 +21833,7 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>C-194</t>
+          <t>C-195</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -21852,13 +21848,13 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado</t>
+          <t>tipo_contr_ult_baja</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr"/>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado solo toma las 7 categorías de tipo de contrato</t>
+          <t>tipo_contr_ult_baja solo toma las 7 categorías de tipo de contrato</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr">
@@ -21873,7 +21869,7 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado IS NOT NULL AND tipo_contr_ppal_agrupado NOT IN ('Indefinido_t_completo','No consta','Temporal_t_completo','Indefinido_t_parcial','Temporal_t_parcial','Indefinido_fijo_discontinuo','Otros')</t>
+          <t>tipo_contr_ult_baja IS NOT NULL AND tipo_contr_ult_baja NOT IN ('Indefinido_t_completo','No consta','Temporal_t_completo','Indefinido_t_parcial','Temporal_t_parcial','Indefinido_fijo_discontinuo','Otros')</t>
         </is>
       </c>
       <c r="J403" s="2" t="inlineStr"/>
@@ -21886,7 +21882,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>C-195</t>
+          <t>C-196</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -21901,18 +21897,18 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ult_baja</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr"/>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ult_baja solo toma las 7 categorías de tipo de contrato</t>
+          <t>causa_ult_baja solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
@@ -21922,7 +21918,7 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ult_baja IS NOT NULL AND tipo_contr_ult_baja NOT IN ('Indefinido_t_completo','No consta','Temporal_t_completo','Indefinido_t_parcial','Temporal_t_parcial','Indefinido_fijo_discontinuo','Otros')</t>
+          <t>causa_ult_baja IS NOT NULL AND causa_ult_baja &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_ult_baja, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr"/>
@@ -21935,7 +21931,7 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>C-196</t>
+          <t>C-197</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -21950,13 +21946,13 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja</t>
+          <t>causa_baja_trab_ppal</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr"/>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
+          <t>causa_baja_trab_ppal solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
         </is>
       </c>
       <c r="G405" s="2" t="inlineStr">
@@ -21971,7 +21967,7 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja IS NOT NULL AND causa_ult_baja &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_ult_baja, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
+          <t>causa_baja_trab_ppal IS NOT NULL AND causa_baja_trab_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_baja_trab_ppal, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
         </is>
       </c>
       <c r="J405" s="2" t="inlineStr"/>
@@ -21984,7 +21980,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>C-197</t>
+          <t>C-198</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -21999,13 +21995,13 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_trab_ppal</t>
+          <t>causa_baja_mas_comun</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr"/>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_trab_ppal solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
+          <t>causa_baja_mas_comun solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
         </is>
       </c>
       <c r="G406" s="2" t="inlineStr">
@@ -22020,7 +22016,7 @@
       </c>
       <c r="I406" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_trab_ppal IS NOT NULL AND causa_baja_trab_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_baja_trab_ppal, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
+          <t>causa_baja_mas_comun IS NOT NULL AND causa_baja_mas_comun &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_baja_mas_comun, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
         </is>
       </c>
       <c r="J406" s="2" t="inlineStr"/>
@@ -22033,7 +22029,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>C-198</t>
+          <t>C-199</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -22048,18 +22044,18 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_mas_comun</t>
+          <t>act_econ_ppal</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr"/>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_mas_comun solo toma claves de causa de baja de la guía 2.008 o NO CONSTA</t>
+          <t>act_econ_ppal = 'NNN texto' (CNAE 3 dígitos) o NO CONSTA</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -22069,7 +22065,7 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>causa_baja_mas_comun IS NOT NULL AND causa_baja_mas_comun &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(causa_baja_mas_comun, '^(00|51|52|54|55|56|58|60|65|68|69|73|74|77|85|91|92|93|94|99) .+')</t>
+          <t>act_econ_ppal IS NOT NULL AND act_econ_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(act_econ_ppal, '^[0-9]{3} .+')</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr"/>
@@ -22082,7 +22078,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>C-199</t>
+          <t>C-200</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -22097,13 +22093,13 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal</t>
+          <t>act_econ_ult_baja</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr"/>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal = 'NNN texto' (CNAE 3 dígitos) o NO CONSTA</t>
+          <t>act_econ_ult_baja = 'NNN texto' (CNAE 3 dígitos) o NO CONSTA</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
@@ -22118,7 +22114,7 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal IS NOT NULL AND act_econ_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(act_econ_ppal, '^[0-9]{3} .+')</t>
+          <t>act_econ_ult_baja IS NOT NULL AND act_econ_ult_baja &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(act_econ_ult_baja, '^[0-9]{3} .+')</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr"/>
@@ -22131,7 +22127,7 @@
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>C-200</t>
+          <t>C-201</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -22146,13 +22142,13 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja</t>
+          <t>prov_trabajo_ppal</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr"/>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja = 'NNN texto' (CNAE 3 dígitos) o NO CONSTA</t>
+          <t>prov_trabajo_ppal = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr">
@@ -22167,10 +22163,10 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja IS NOT NULL AND act_econ_ult_baja &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(act_econ_ult_baja, '^[0-9]{3} .+')</t>
-        </is>
-      </c>
-      <c r="J409" s="2" t="inlineStr"/>
+          <t>prov_trabajo_ppal IS NOT NULL AND prov_trabajo_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_trabajo_ppal, '^[0-9]{2} .+')</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="n"/>
       <c r="K409" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22180,7 +22176,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>C-201</t>
+          <t>C-202</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -22195,13 +22191,13 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal</t>
+          <t>prov_fiscal_actual</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr"/>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_fiscal_actual = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
@@ -22216,10 +22212,10 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>prov_trabajo_ppal IS NOT NULL AND prov_trabajo_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_trabajo_ppal, '^[0-9]{2} .+')</t>
-        </is>
-      </c>
-      <c r="J410" s="2" t="n"/>
+          <t>prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_fiscal_actual, '^[0-9]{2} .+')</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr"/>
       <c r="K410" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -22229,7 +22225,7 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>C-202</t>
+          <t>C-203</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -22244,13 +22240,13 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual</t>
+          <t>prov_nacimiento</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr"/>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_nacimiento = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
@@ -22265,7 +22261,7 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_fiscal_actual, '^[0-9]{2} .+')</t>
+          <t>prov_nacimiento IS NOT NULL AND prov_nacimiento &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_nacimiento, '^[0-9]{2} .+')</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr"/>
@@ -22278,7 +22274,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>C-203</t>
+          <t>C-204</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -22293,13 +22289,13 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento</t>
+          <t>prov_1a_afiliacion</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr"/>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_1a_afiliacion = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
@@ -22314,7 +22310,7 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento IS NOT NULL AND prov_nacimiento &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_nacimiento, '^[0-9]{2} .+')</t>
+          <t>prov_1a_afiliacion IS NOT NULL AND prov_1a_afiliacion &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_1a_afiliacion, '^[0-9]{2} .+')</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr"/>
@@ -22327,7 +22323,7 @@
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>C-204</t>
+          <t>C-205</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -22342,13 +22338,13 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>prov_1a_afiliacion</t>
+          <t>prov_resid_habitual</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr"/>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>prov_1a_afiliacion = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>prov_resid_habitual = 'NN NOMBRE' (provincia) o NO CONSTA</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
@@ -22363,7 +22359,7 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>prov_1a_afiliacion IS NOT NULL AND prov_1a_afiliacion &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_1a_afiliacion, '^[0-9]{2} .+')</t>
+          <t>prov_resid_habitual IS NOT NULL AND prov_resid_habitual &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_resid_habitual, '^[0-9]{2} .+')</t>
         </is>
       </c>
       <c r="J413" s="2" t="inlineStr"/>
@@ -22376,7 +22372,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>C-205</t>
+          <t>C-206</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -22391,13 +22387,13 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual</t>
+          <t>nacionalidad_agrupado</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr"/>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual = 'NN NOMBRE' (provincia) o NO CONSTA</t>
+          <t>nacionalidad_agrupado ∈ 5 grupos conocidos</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
@@ -22412,7 +22408,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual IS NOT NULL AND prov_resid_habitual &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(prov_resid_habitual, '^[0-9]{2} .+')</t>
+          <t>nacionalidad_agrupado IS NOT NULL AND nacionalidad_agrupado NOT IN ('espana','paises_UE_UK','paises_latinos','paises_africanos','paises_lejanos')</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr"/>
@@ -22425,7 +22421,7 @@
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>C-206</t>
+          <t>C-207</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -22440,13 +22436,13 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado</t>
+          <t>pais_nacim_agrupado</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr"/>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado ∈ 5 grupos conocidos</t>
+          <t>pais_nacim_agrupado ∈ 5 grupos conocidos</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
@@ -22461,7 +22457,7 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad_agrupado IS NOT NULL AND nacionalidad_agrupado NOT IN ('espana','paises_UE_UK','paises_latinos','paises_africanos','paises_lejanos')</t>
+          <t>pais_nacim_agrupado IS NOT NULL AND pais_nacim_agrupado NOT IN ('espana','paises_UE_UK','paises_latinos','paises_africanos','paises_lejanos')</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr"/>
@@ -22474,7 +22470,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>C-207</t>
+          <t>C-208</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -22489,13 +22485,13 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr"/>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado ∈ 5 grupos conocidos</t>
+          <t>cobra_pension_2024_5 ∈ {SI, NO}</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
@@ -22510,7 +22506,7 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>pais_nacim_agrupado IS NOT NULL AND pais_nacim_agrupado NOT IN ('espana','paises_UE_UK','paises_latinos','paises_africanos','paises_lejanos')</t>
+          <t>cobra_pension_2024_5 NOT IN ('SI','NO')</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr"/>
@@ -22523,7 +22519,7 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>C-208</t>
+          <t>C-209</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -22538,13 +22534,13 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>ha_fallecido</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr"/>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 ∈ {SI, NO}</t>
+          <t>ha_fallecido ∈ {SI, NO}</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
@@ -22559,7 +22555,7 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 NOT IN ('SI','NO')</t>
+          <t>ha_fallecido NOT IN ('SI','NO')</t>
         </is>
       </c>
       <c r="J417" s="2" t="inlineStr"/>
@@ -22572,7 +22568,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>C-209</t>
+          <t>C-210</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -22587,13 +22583,13 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido</t>
+          <t>situacion_actual_afiliacion</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr"/>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido ∈ {SI, NO}</t>
+          <t>situacion_actual_afiliacion ∈ 9 categorías conocidas</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr">
@@ -22608,7 +22604,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido NOT IN ('SI','NO')</t>
+          <t>situacion_actual_afiliacion NOT IN ('Alta_ocupado','Baja_de_actividad','Baja_para_pension','Baja_de_prestacion','Nunca_ha_cotizado','Baja_de_subsidio','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52','Asimilado_otros')</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr"/>
@@ -22621,7 +22617,7 @@
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>C-210</t>
+          <t>C-211</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -22636,13 +22632,13 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion</t>
+          <t>situacion_paro_ocupacion</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr"/>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion ∈ 9 categorías conocidas</t>
+          <t>situacion_paro_ocupacion ∈ 7 categorías conocidas</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
@@ -22657,7 +22653,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion NOT IN ('Alta_ocupado','Baja_de_actividad','Baja_para_pension','Baja_de_prestacion','Nunca_ha_cotizado','Baja_de_subsidio','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52','Asimilado_otros')</t>
+          <t>situacion_paro_ocupacion NOT IN ('Ocupado','Ocupado_y_pensionista','Pensionista','Parado_LD','Parado_LD_pension_no_jubilacion','Parado_NoLD','Parado_NoLD_pension_no_jubilacion')</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr"/>
@@ -22670,7 +22666,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>C-211</t>
+          <t>C-212</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -22680,18 +22676,18 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Dominio de valores (guía)</t>
+          <t>Campos obligatorios no nulos</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion</t>
+          <t>ipf</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr"/>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion ∈ 7 categorías conocidas</t>
+          <t>ipf no puede ser nulo</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
@@ -22706,7 +22702,7 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion NOT IN ('Ocupado','Ocupado_y_pensionista','Pensionista','Parado_LD','Parado_LD_pension_no_jubilacion','Parado_NoLD','Parado_NoLD_pension_no_jubilacion')</t>
+          <t>ipf IS NULL</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr"/>
@@ -22719,7 +22715,7 @@
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>C-212</t>
+          <t>C-213</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -22734,13 +22730,13 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>ipf</t>
+          <t>fecha_nacimiento</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr"/>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>ipf no puede ser nulo</t>
+          <t>fecha_nacimiento no puede ser nulo</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr">
@@ -22755,7 +22751,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>ipf IS NULL</t>
+          <t>fecha_nacimiento IS NULL</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr"/>
@@ -22768,7 +22764,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>C-213</t>
+          <t>C-214</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -22783,13 +22779,13 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>fecha_nacimiento</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr"/>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>fecha_nacimiento no puede ser nulo</t>
+          <t>sexo no puede ser nulo</t>
         </is>
       </c>
       <c r="G422" s="2" t="inlineStr">
@@ -22804,7 +22800,7 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>fecha_nacimiento IS NULL</t>
+          <t>sexo IS NULL</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr"/>
@@ -22817,7 +22813,7 @@
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>C-214</t>
+          <t>C-215</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -22832,13 +22828,13 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr"/>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>sexo no puede ser nulo</t>
+          <t>edad_actual_fecha_corte no puede ser nulo</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr">
@@ -22853,7 +22849,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>sexo IS NULL</t>
+          <t>edad_actual_fecha_corte IS NULL</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr"/>
@@ -22866,7 +22862,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>C-215</t>
+          <t>C-216</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -22881,13 +22877,13 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>situacion_actual_afiliacion</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr"/>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte no puede ser nulo</t>
+          <t>situacion_actual_afiliacion no puede ser nulo</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr">
@@ -22902,7 +22898,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte IS NULL</t>
+          <t>situacion_actual_afiliacion IS NULL</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr"/>
@@ -22915,7 +22911,7 @@
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>C-216</t>
+          <t>C-217</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -22930,13 +22926,13 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion</t>
+          <t>situacion_paro_ocupacion</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr"/>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion no puede ser nulo</t>
+          <t>situacion_paro_ocupacion no puede ser nulo</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
@@ -22951,7 +22947,7 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion IS NULL</t>
+          <t>situacion_paro_ocupacion IS NULL</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr"/>
@@ -22964,7 +22960,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>C-217</t>
+          <t>C-218</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -22979,13 +22975,13 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion</t>
+          <t>nacionalidad</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr"/>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion no puede ser nulo</t>
+          <t>nacionalidad no puede ser nulo</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
@@ -23000,7 +22996,7 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>situacion_paro_ocupacion IS NULL</t>
+          <t>nacionalidad IS NULL</t>
         </is>
       </c>
       <c r="J426" s="2" t="inlineStr"/>
@@ -23013,7 +23009,7 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>C-218</t>
+          <t>C-219</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -23028,13 +23024,13 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad</t>
+          <t>pais_nacimiento</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr"/>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad no puede ser nulo</t>
+          <t>pais_nacimiento no puede ser nulo</t>
         </is>
       </c>
       <c r="G427" s="2" t="inlineStr">
@@ -23049,7 +23045,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>nacionalidad IS NULL</t>
+          <t>pais_nacimiento IS NULL</t>
         </is>
       </c>
       <c r="J427" s="2" t="inlineStr"/>
@@ -23062,7 +23058,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>C-219</t>
+          <t>C-220</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -23077,13 +23073,13 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento</t>
+          <t>prov_nacimiento</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr"/>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento no puede ser nulo</t>
+          <t>prov_nacimiento no puede ser nulo</t>
         </is>
       </c>
       <c r="G428" s="2" t="inlineStr">
@@ -23098,7 +23094,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>pais_nacimiento IS NULL</t>
+          <t>prov_nacimiento IS NULL</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr"/>
@@ -23111,7 +23107,7 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>C-220</t>
+          <t>C-221</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -23126,13 +23122,13 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr"/>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento no puede ser nulo</t>
+          <t>cobra_pension_2024_5 no puede ser nulo</t>
         </is>
       </c>
       <c r="G429" s="2" t="inlineStr">
@@ -23147,7 +23143,7 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>prov_nacimiento IS NULL</t>
+          <t>cobra_pension_2024_5 IS NULL</t>
         </is>
       </c>
       <c r="J429" s="2" t="inlineStr"/>
@@ -23160,7 +23156,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>C-221</t>
+          <t>C-222</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
@@ -23175,13 +23171,13 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>discap_afiliacion</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr"/>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 no puede ser nulo</t>
+          <t>discap_afiliacion no puede ser nulo</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
@@ -23196,7 +23192,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 IS NULL</t>
+          <t>discap_afiliacion IS NULL</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr"/>
@@ -23209,7 +23205,7 @@
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>C-222</t>
+          <t>C-223</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -23224,13 +23220,13 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion</t>
+          <t>discap_pension</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr"/>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion no puede ser nulo</t>
+          <t>discap_pension no puede ser nulo</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
@@ -23245,7 +23241,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>discap_afiliacion IS NULL</t>
+          <t>discap_pension IS NULL</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr"/>
@@ -23258,7 +23254,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>C-223</t>
+          <t>C-224</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -23273,13 +23269,13 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>discap_pension</t>
+          <t>discap_fiscal</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr"/>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>discap_pension no puede ser nulo</t>
+          <t>discap_fiscal no puede ser nulo</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
@@ -23294,7 +23290,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>discap_pension IS NULL</t>
+          <t>discap_fiscal IS NULL</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr"/>
@@ -23307,7 +23303,7 @@
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>C-224</t>
+          <t>C-225</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -23322,13 +23318,13 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal</t>
+          <t>domic_resid_habitual</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr"/>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal no puede ser nulo</t>
+          <t>domic_resid_habitual no puede ser nulo</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
@@ -23343,7 +23339,7 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>discap_fiscal IS NULL</t>
+          <t>domic_resid_habitual IS NULL</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr"/>
@@ -23356,7 +23352,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>C-225</t>
+          <t>C-226</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -23371,13 +23367,13 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual</t>
+          <t>prov_resid_habitual</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr"/>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual no puede ser nulo</t>
+          <t>prov_resid_habitual no puede ser nulo</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
@@ -23392,7 +23388,7 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual IS NULL</t>
+          <t>prov_resid_habitual IS NULL</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr"/>
@@ -23405,7 +23401,7 @@
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>C-226</t>
+          <t>C-227</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -23420,13 +23416,13 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual</t>
+          <t>ha_fallecido</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr"/>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual no puede ser nulo</t>
+          <t>ha_fallecido no puede ser nulo</t>
         </is>
       </c>
       <c r="G435" s="2" t="inlineStr">
@@ -23441,7 +23437,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual IS NULL</t>
+          <t>ha_fallecido IS NULL</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr"/>
@@ -23454,7 +23450,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>C-227</t>
+          <t>C-228</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -23469,13 +23465,13 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido</t>
+          <t>clave_subclave_ppal</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr"/>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido no puede ser nulo</t>
+          <t>clave_subclave_ppal no puede ser nulo</t>
         </is>
       </c>
       <c r="G436" s="2" t="inlineStr">
@@ -23490,7 +23486,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido IS NULL</t>
+          <t>clave_subclave_ppal IS NULL</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr"/>
@@ -23503,7 +23499,7 @@
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>C-228</t>
+          <t>C-229</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -23518,13 +23514,13 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal</t>
+          <t>ipf</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr"/>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal no puede ser nulo</t>
+          <t>ipf es único (una fila por persona)</t>
         </is>
       </c>
       <c r="G437" s="2" t="inlineStr">
@@ -23539,7 +23535,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal IS NULL</t>
+          <t>ipf IN (SELECT ipf FROM personas GROUP BY 1 HAVING COUNT(*) &gt; 1)</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr"/>
@@ -23552,7 +23548,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>C-229</t>
+          <t>C-230</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -23562,36 +23558,44 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Campos obligatorios no nulos</t>
+          <t>Régimen de cotización</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>ipf</t>
-        </is>
-      </c>
-      <c r="E438" s="2" t="inlineStr"/>
+          <t>reg_cotiz_ppal_agrupado</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>act_econ_ppal</t>
+        </is>
+      </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>ipf es único (una fila por persona)</t>
+          <t>R.E. Agrario cuenta ajena ⇒ actividad agraria/forestal/pesquera (CNAE 01-03)</t>
         </is>
       </c>
       <c r="G438" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>ipf IN (SELECT ipf FROM personas GROUP BY 1 HAVING COUNT(*) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J438" s="2" t="inlineStr"/>
+          <t>reg_cotiz_ppal_agrupado LIKE '06 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '01%' OR act_econ_ppal LIKE '02%' OR act_econ_ppal LIKE '03%')</t>
+        </is>
+      </c>
+      <c r="J438" s="2" t="inlineStr">
+        <is>
+          <t>La actividad principal puede ser de otro periodo</t>
+        </is>
+      </c>
       <c r="K438" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23601,7 +23605,7 @@
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>C-230</t>
+          <t>C-231</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -23626,7 +23630,7 @@
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>R.E. Agrario cuenta ajena ⇒ actividad agraria/forestal/pesquera (CNAE 01-03)</t>
+          <t>R.E. Agrario cuenta propia ⇒ actividad agraria (CNAE 01-03)</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr">
@@ -23641,14 +23645,10 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '06 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '01%' OR act_econ_ppal LIKE '02%' OR act_econ_ppal LIKE '03%')</t>
-        </is>
-      </c>
-      <c r="J439" s="2" t="inlineStr">
-        <is>
-          <t>La actividad principal puede ser de otro periodo</t>
-        </is>
-      </c>
+          <t>reg_cotiz_ppal_agrupado LIKE '07 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '01%' OR act_econ_ppal LIKE '02%' OR act_econ_ppal LIKE '03%')</t>
+        </is>
+      </c>
+      <c r="J439" s="2" t="inlineStr"/>
       <c r="K439" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -23658,7 +23658,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>C-231</t>
+          <t>C-232</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
@@ -23683,7 +23683,7 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>R.E. Agrario cuenta propia ⇒ actividad agraria (CNAE 01-03)</t>
+          <t>R.E. Empleados de Hogar ⇒ CNAE 970 (hogares como empleadores)</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr">
@@ -23693,12 +23693,12 @@
       </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '07 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '01%' OR act_econ_ppal LIKE '02%' OR act_econ_ppal LIKE '03%')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '970%'</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr"/>
@@ -23711,7 +23711,7 @@
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>C-232</t>
+          <t>C-233</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
@@ -23736,7 +23736,7 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>R.E. Empleados de Hogar ⇒ CNAE 970 (hogares como empleadores)</t>
+          <t>Régimen General (S.E.C. Empleados de Hogar) ⇒ CNAE 970</t>
         </is>
       </c>
       <c r="G441" s="2" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '970%'</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '0138 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '970%'</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr"/>
@@ -23764,7 +23764,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>C-233</t>
+          <t>C-234</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>Régimen General (S.E.C. Empleados de Hogar) ⇒ CNAE 970</t>
+          <t>R.E. del Mar ⇒ pesca o transporte marítimo (CNAE 03/50)</t>
         </is>
       </c>
       <c r="G442" s="2" t="inlineStr">
@@ -23799,12 +23799,12 @@
       </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '0138 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '970%'</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '08 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '03%' OR act_econ_ppal LIKE '50%')</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr"/>
@@ -23817,7 +23817,7 @@
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>C-234</t>
+          <t>C-235</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -23842,7 +23842,7 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>R.E. del Mar ⇒ pesca o transporte marítimo (CNAE 03/50)</t>
+          <t>R.E. Minería del Carbón ⇒ CNAE 05 (extracción de carbón)</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
@@ -23852,12 +23852,12 @@
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '08 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND NOT (act_econ_ppal LIKE '03%' OR act_econ_ppal LIKE '50%')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '09 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '05%'</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr"/>
@@ -23870,7 +23870,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>C-235</t>
+          <t>C-236</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -23890,27 +23890,27 @@
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ppal</t>
+          <t>grupo_cotiz_ppal</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>R.E. Minería del Carbón ⇒ CNAE 05 (extracción de carbón)</t>
+          <t>R.E. Autónomos ⇒ sin grupo de cotización (guía 2.003)</t>
         </is>
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '09 %' AND (act_econ_ppal IS NOT NULL AND act_econ_ppal NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND act_econ_ppal NOT LIKE '05%'</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '05 %' AND grupo_cotiz_ppal NOT IN ('0 NO CONSTA','NO CONSTA')</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr"/>
@@ -23923,7 +23923,7 @@
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>C-236</t>
+          <t>C-237</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>R.E. Autónomos ⇒ sin grupo de cotización (guía 2.003)</t>
+          <t>R.E. Empleados de Hogar ⇒ sin grupo de cotización (guía 2.003)</t>
         </is>
       </c>
       <c r="G445" s="2" t="inlineStr">
@@ -23963,7 +23963,7 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '05 %' AND grupo_cotiz_ppal NOT IN ('0 NO CONSTA','NO CONSTA')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND grupo_cotiz_ppal NOT IN ('0 NO CONSTA','NO CONSTA')</t>
         </is>
       </c>
       <c r="J445" s="2" t="inlineStr"/>
@@ -23976,7 +23976,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>C-237</t>
+          <t>C-238</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -23996,27 +23996,27 @@
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal</t>
+          <t>tipo_contr_ppal_agrupado</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>R.E. Empleados de Hogar ⇒ sin grupo de cotización (guía 2.003)</t>
+          <t>R.E. Autónomos ⇒ sin tipo de contrato ('No consta')</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND grupo_cotiz_ppal NOT IN ('0 NO CONSTA','NO CONSTA')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '05 %' AND tipo_contr_ppal_agrupado NOT IN ('No consta')</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr"/>
@@ -24029,7 +24029,7 @@
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>C-238</t>
+          <t>C-239</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -24049,17 +24049,17 @@
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado</t>
+          <t>t_tot_reg_ppal</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>R.E. Autónomos ⇒ sin tipo de contrato ('No consta')</t>
+          <t>R.E. Agrario cuenta propia (extinguido en 2008) ⇒ ≤ 41,5 años en ese régimen (1967-2008)</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '05 %' AND tipo_contr_ppal_agrupado NOT IN ('No consta')</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '07 %' AND t_tot_reg_ppal &gt; 41.5</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr"/>
@@ -24082,7 +24082,7 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>C-239</t>
+          <t>C-240</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -24107,7 +24107,7 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>R.E. Agrario cuenta propia (extinguido en 2008) ⇒ ≤ 41,5 años en ese régimen (1967-2008)</t>
+          <t>R.E. Agrario cuenta ajena (integrado en 2012) ⇒ ≤ 45,5 años en ese régimen</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
@@ -24122,7 +24122,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '07 %' AND t_tot_reg_ppal &gt; 41.5</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '06 %' AND t_tot_reg_ppal &gt; 45.5</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr"/>
@@ -24135,7 +24135,7 @@
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>C-240</t>
+          <t>C-241</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>R.E. Agrario cuenta ajena (integrado en 2012) ⇒ ≤ 45,5 años en ese régimen</t>
+          <t>R.E. Empleados de Hogar (integrado en 2012) ⇒ ≤ 45,5 años</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
@@ -24175,7 +24175,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '06 %' AND t_tot_reg_ppal &gt; 45.5</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND t_tot_reg_ppal &gt; 45.5</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr"/>
@@ -24188,7 +24188,7 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>C-241</t>
+          <t>C-242</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -24213,7 +24213,7 @@
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>R.E. Empleados de Hogar (integrado en 2012) ⇒ ≤ 45,5 años</t>
+          <t>Régimen General (S.E.C. Hogar), creado en 2012 ⇒ ≤ 13,5 años</t>
         </is>
       </c>
       <c r="G450" s="2" t="inlineStr">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '12 %' AND t_tot_reg_ppal &gt; 45.5</t>
+          <t>reg_cotiz_ppal_agrupado LIKE '0138 %' AND t_tot_reg_ppal &gt; 13.5</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr"/>
@@ -24241,7 +24241,7 @@
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>C-242</t>
+          <t>C-243</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -24251,22 +24251,22 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>Régimen de cotización</t>
+          <t>Grupo de cotización × edad</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado</t>
+          <t>grupo_cotiz_ppal</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal</t>
+          <t>t_tot_grupo_ppal</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>Régimen General (S.E.C. Hogar), creado en 2012 ⇒ ≤ 13,5 años</t>
+          <t>Grupo 11 (menores de 18) ⇒ ≤ 2,1 años en ese grupo (16-18 años)</t>
         </is>
       </c>
       <c r="G451" s="2" t="inlineStr">
@@ -24281,7 +24281,7 @@
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado LIKE '0138 %' AND t_tot_reg_ppal &gt; 13.5</t>
+          <t>grupo_cotiz_ppal LIKE '11 %' AND t_tot_grupo_ppal &gt; 2.1</t>
         </is>
       </c>
       <c r="J451" s="2" t="inlineStr"/>
@@ -24294,7 +24294,7 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>C-243</t>
+          <t>C-244</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>Grupo 11 (menores de 18) ⇒ ≤ 2,1 años en ese grupo (16-18 años)</t>
+          <t>Grupo 12 (menores de 17) ⇒ ≤ 1,1 años en ese grupo</t>
         </is>
       </c>
       <c r="G452" s="2" t="inlineStr">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal LIKE '11 %' AND t_tot_grupo_ppal &gt; 2.1</t>
+          <t>grupo_cotiz_ppal LIKE '12 %' AND t_tot_grupo_ppal &gt; 1.1</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr"/>
@@ -24347,7 +24347,7 @@
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>C-244</t>
+          <t>C-245</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -24362,17 +24362,17 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal</t>
+          <t>edad_ultimo_empleo</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>Grupo 12 (menores de 17) ⇒ ≤ 1,1 años en ese grupo</t>
+          <t>Último empleo en grupo 11 ⇒ edad del último empleo &lt; 18</t>
         </is>
       </c>
       <c r="G453" s="2" t="inlineStr">
@@ -24387,7 +24387,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal LIKE '12 %' AND t_tot_grupo_ppal &gt; 1.1</t>
+          <t>grupo_ultimo_empleo LIKE '11 %' AND edad_ultimo_empleo &gt;= 18.1</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr"/>
@@ -24400,7 +24400,7 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>C-245</t>
+          <t>C-246</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -24425,7 +24425,7 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>Último empleo en grupo 11 ⇒ edad del último empleo &lt; 18</t>
+          <t>Último empleo en grupo 12 ⇒ edad del último empleo &lt; 17</t>
         </is>
       </c>
       <c r="G454" s="2" t="inlineStr">
@@ -24440,7 +24440,7 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo LIKE '11 %' AND edad_ultimo_empleo &gt;= 18.1</t>
+          <t>grupo_ultimo_empleo LIKE '12 %' AND edad_ultimo_empleo &gt;= 17.1</t>
         </is>
       </c>
       <c r="J454" s="2" t="inlineStr"/>
@@ -24453,7 +24453,7 @@
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>C-246</t>
+          <t>C-247</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -24468,17 +24468,17 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo</t>
+          <t>grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>edad_ultimo_empleo</t>
+          <t>edad_primer_empleo_signif</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>Último empleo en grupo 12 ⇒ edad del último empleo &lt; 17</t>
+          <t>Primer empleo en grupo 11 ⇒ edad &lt; 18</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
@@ -24493,7 +24493,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo LIKE '12 %' AND edad_ultimo_empleo &gt;= 17.1</t>
+          <t>grupo_cotiz_1er_empleo_signif LIKE '11 %' AND edad_primer_empleo_signif &gt;= 18.1</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr"/>
@@ -24506,7 +24506,7 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>C-247</t>
+          <t>C-248</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -24531,7 +24531,7 @@
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo en grupo 11 ⇒ edad &lt; 18</t>
+          <t>Primer empleo en grupo 12 ⇒ edad &lt; 17</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
@@ -24546,7 +24546,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif LIKE '11 %' AND edad_primer_empleo_signif &gt;= 18.1</t>
+          <t>grupo_cotiz_1er_empleo_signif LIKE '12 %' AND edad_primer_empleo_signif &gt;= 17.1</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr"/>
@@ -24559,7 +24559,7 @@
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>C-248</t>
+          <t>C-249</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -24574,17 +24574,17 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>edad_primer_empleo_signif</t>
+          <t>edad_ultimo_empleo</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo en grupo 12 ⇒ edad &lt; 17</t>
+          <t>Último empleo en grupo 10 ('mayores de 18') ⇒ edad ≥ 18</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
@@ -24594,12 +24594,12 @@
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif LIKE '12 %' AND edad_primer_empleo_signif &gt;= 17.1</t>
+          <t>grupo_ultimo_empleo LIKE '10 %' AND edad_ultimo_empleo &lt; 17.9</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr"/>
@@ -24612,7 +24612,7 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>C-249</t>
+          <t>C-250</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -24627,17 +24627,17 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo</t>
+          <t>grupo_cotiz_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>edad_ultimo_empleo</t>
+          <t>edad_primer_empleo_signif</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>Último empleo en grupo 10 ('mayores de 18') ⇒ edad ≥ 18</t>
+          <t>Primer empleo en grupo 10 ('mayores de 18') ⇒ edad ≥ 18</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>grupo_ultimo_empleo LIKE '10 %' AND edad_ultimo_empleo &lt; 17.9</t>
+          <t>grupo_cotiz_1er_empleo_signif LIKE '10 %' AND edad_primer_empleo_signif &lt; 17.9</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr"/>
@@ -24665,7 +24665,7 @@
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>C-250</t>
+          <t>C-251</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -24690,22 +24690,22 @@
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo en grupo 10 ('mayores de 18') ⇒ edad ≥ 18</t>
+          <t>Primer empleo como ingeniero/licenciado (grupo 1) ⇒ edad ≥ 18</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif LIKE '10 %' AND edad_primer_empleo_signif &lt; 17.9</t>
+          <t>grupo_cotiz_1er_empleo_signif LIKE '1 %' AND edad_primer_empleo_signif &lt; 18</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr"/>
@@ -24718,7 +24718,7 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>C-251</t>
+          <t>C-252</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
@@ -24728,22 +24728,18 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>Grupo de cotización × edad</t>
+          <t>cotizado_anual_promedio (€/año)</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif</t>
-        </is>
-      </c>
-      <c r="E460" s="2" t="inlineStr">
-        <is>
-          <t>edad_primer_empleo_signif</t>
-        </is>
-      </c>
+          <t>cotizado_anual_promedio</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr"/>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>Primer empleo como ingeniero/licenciado (grupo 1) ⇒ edad ≥ 18</t>
+          <t>Cotizado anual promedio ≤ 100.000 €/año (la base máxima ronda 57.000 €/año)</t>
         </is>
       </c>
       <c r="G460" s="2" t="inlineStr">
@@ -24758,10 +24754,14 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_1er_empleo_signif LIKE '1 %' AND edad_primer_empleo_signif &lt; 18</t>
-        </is>
-      </c>
-      <c r="J460" s="2" t="inlineStr"/>
+          <t>cotizado_anual_promedio &gt; 100000</t>
+        </is>
+      </c>
+      <c r="J460" s="2" t="inlineStr">
+        <is>
+          <t>Unidad: euros por año cotizado (confirmado por el usuario); el pluriempleo puede sumar bases</t>
+        </is>
+      </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24771,7 +24771,7 @@
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>C-252</t>
+          <t>C-253</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
@@ -24792,7 +24792,7 @@
       <c r="E461" s="2" t="inlineStr"/>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>Cotizado anual promedio ≤ 100.000 €/año (la base máxima ronda 57.000 €/año)</t>
+          <t>Si es positivo, no es inferior a 100 €/año</t>
         </is>
       </c>
       <c r="G461" s="2" t="inlineStr">
@@ -24807,12 +24807,12 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio &gt; 100000</t>
+          <t>cotizado_anual_promedio &gt; 0 AND cotizado_anual_promedio &lt; 100</t>
         </is>
       </c>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>Unidad: euros por año cotizado (confirmado por el usuario); el pluriempleo puede sumar bases</t>
+          <t>Bases muy bajas por episodios mínimos o errores de conversión (céntimos/100)</t>
         </is>
       </c>
       <c r="K461" s="2" t="inlineStr">
@@ -24824,7 +24824,7 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>C-253</t>
+          <t>C-254</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
@@ -24842,30 +24842,34 @@
           <t>cotizado_anual_promedio</t>
         </is>
       </c>
-      <c r="E462" s="2" t="inlineStr"/>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>t_total_empleo</t>
+        </is>
+      </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>Si es positivo, no es inferior a 100 €/año</t>
+          <t>Con tiempo de empleo &gt; 0 ⇒ cotizado_anual_promedio informado</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio &gt; 0 AND cotizado_anual_promedio &lt; 100</t>
+          <t>t_total_empleo &gt; 0 AND cotizado_anual_promedio IS NULL</t>
         </is>
       </c>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>Bases muy bajas por episodios mínimos o errores de conversión (céntimos/100)</t>
+          <t>Puede faltar la tabla de bases de cotización</t>
         </is>
       </c>
       <c r="K462" s="2" t="inlineStr">
@@ -24877,7 +24881,7 @@
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>C-254</t>
+          <t>C-255</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
@@ -24887,22 +24891,22 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio (€/año)</t>
+          <t>Tasas y recuentos</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>cotizado_anual_promedio</t>
+          <t>num_bajas_anual_promedio</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo</t>
+          <t>num_altas_anual_promedio</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>Con tiempo de empleo &gt; 0 ⇒ cotizado_anual_promedio informado</t>
+          <t>Nº medio de bajas ≤ nº medio de altas (cada baja cierra un alta)</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
@@ -24912,19 +24916,15 @@
       </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo &gt; 0 AND cotizado_anual_promedio IS NULL</t>
-        </is>
-      </c>
-      <c r="J463" s="2" t="inlineStr">
-        <is>
-          <t>Puede faltar la tabla de bases de cotización</t>
-        </is>
-      </c>
+          <t>num_bajas_anual_promedio &gt; num_altas_anual_promedio + 0.001</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr"/>
       <c r="K463" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -24934,7 +24934,7 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>C-255</t>
+          <t>C-256</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -24949,17 +24949,17 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio</t>
+          <t>num_altas_anual_promedio</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>num_altas_anual_promedio</t>
+          <t>tiempo_total_desde_inicio_vl</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>Nº medio de bajas ≤ nº medio de altas (cada baja cierra un alta)</t>
+          <t>Altas totales (media × años) ≥ 1 si hay historia</t>
         </is>
       </c>
       <c r="G464" s="2" t="inlineStr">
@@ -24969,12 +24969,12 @@
       </c>
       <c r="H464" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio &gt; num_altas_anual_promedio + 0.001</t>
+          <t>tiempo_total_desde_inicio_vl &gt; 0 AND num_altas_anual_promedio * tiempo_total_desde_inicio_vl &lt; 0.9</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr"/>
@@ -24987,7 +24987,7 @@
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>C-256</t>
+          <t>C-257</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>Altas totales (media × años) ≥ 1 si hay historia</t>
+          <t>Altas totales (media × años) es un entero (±0,05)</t>
         </is>
       </c>
       <c r="G465" s="2" t="inlineStr">
@@ -25022,15 +25022,19 @@
       </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND num_altas_anual_promedio * tiempo_total_desde_inicio_vl &lt; 0.9</t>
-        </is>
-      </c>
-      <c r="J465" s="2" t="inlineStr"/>
+          <t>tiempo_total_desde_inicio_vl &gt; 0 AND ABS(num_altas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365 - ROUND(num_altas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365)) &gt; 0.05</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr">
+        <is>
+          <t>El promedio anual se normaliza con 365 días y T va en años de 365,25 (regla corregida 2026-09-21)</t>
+        </is>
+      </c>
       <c r="K465" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25040,7 +25044,7 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>C-257</t>
+          <t>C-258</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
@@ -25055,7 +25059,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>num_altas_anual_promedio</t>
+          <t>num_bajas_anual_promedio</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -25065,7 +25069,7 @@
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>Altas totales (media × años) es un entero (±0,05)</t>
+          <t>Bajas totales (media × años) es un entero (±0,05)</t>
         </is>
       </c>
       <c r="G466" s="2" t="inlineStr">
@@ -25080,7 +25084,7 @@
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND ABS(num_altas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365 - ROUND(num_altas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365)) &gt; 0.05</t>
+          <t>tiempo_total_desde_inicio_vl &gt; 0 AND ABS(num_bajas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365 - ROUND(num_bajas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365)) &gt; 0.05</t>
         </is>
       </c>
       <c r="J466" s="2" t="inlineStr">
@@ -25097,7 +25101,7 @@
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>C-258</t>
+          <t>C-262</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -25112,17 +25116,17 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio</t>
+          <t>duracion_promedio_empleo</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl</t>
+          <t>t_total_empleo</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>Bajas totales (media × años) es un entero (±0,05)</t>
+          <t>Duración media de empleo ≤ tiempo total de empleo (empleo + mixto empleo/desempleo) (+0,01)</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr">
@@ -25132,17 +25136,17 @@
       </c>
       <c r="H467" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
-          <t>tiempo_total_desde_inicio_vl &gt; 0 AND ABS(num_bajas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365 - ROUND(num_bajas_anual_promedio * tiempo_total_desde_inicio_vl * 365.25/365)) &gt; 0.05</t>
+          <t>duracion_promedio_empleo &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 0.01</t>
         </is>
       </c>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>El promedio anual se normaliza con 365 días y T va en años de 365,25 (regla corregida 2026-09-21)</t>
+          <t>El tiempo 'mixto' (empleo y desempleo a la vez) también es empleo; regla corregida tras la 1ª ejecución con las tablas v2.2</t>
         </is>
       </c>
       <c r="K467" s="2" t="inlineStr">
@@ -25154,7 +25158,7 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>C-262</t>
+          <t>C-263</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -25179,7 +25183,7 @@
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>Duración media de empleo ≤ tiempo total de empleo (empleo + mixto empleo/desempleo) (+0,01)</t>
+          <t>Con tiempo de empleo &gt; 0 la duración media de empleo no puede ser 0</t>
         </is>
       </c>
       <c r="G468" s="2" t="inlineStr">
@@ -25194,14 +25198,10 @@
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
-          <t>duracion_promedio_empleo &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 0.01</t>
-        </is>
-      </c>
-      <c r="J468" s="2" t="inlineStr">
-        <is>
-          <t>El tiempo 'mixto' (empleo y desempleo a la vez) también es empleo; regla corregida tras la 1ª ejecución con las tablas v2.2</t>
-        </is>
-      </c>
+          <t>duracion_promedio_empleo = 0 AND t_total_empleo &gt; 0</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr"/>
       <c r="K468" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25211,7 +25211,7 @@
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>C-263</t>
+          <t>C-264</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -25226,7 +25226,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>duracion_promedio_empleo</t>
+          <t>t_contrato_mas_largo</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>Con tiempo de empleo &gt; 0 la duración media de empleo no puede ser 0</t>
+          <t>El contrato más largo no supera el tiempo total de empleo (+1)</t>
         </is>
       </c>
       <c r="G469" s="2" t="inlineStr">
@@ -25246,12 +25246,12 @@
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>duracion_promedio_empleo = 0 AND t_total_empleo &gt; 0</t>
+          <t>t_contrato_mas_largo &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr"/>
@@ -25264,7 +25264,7 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>C-264</t>
+          <t>C-265</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>t_contrato_mas_largo</t>
+          <t>duracion_1er_empleo_signif</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -25289,7 +25289,7 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>El contrato más largo no supera el tiempo total de empleo (+1)</t>
+          <t>La duración del primer empleo significativo no supera el tiempo total de empleo (+1)</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr">
@@ -25304,10 +25304,14 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>t_contrato_mas_largo &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1</t>
-        </is>
-      </c>
-      <c r="J470" s="2" t="inlineStr"/>
+          <t>duracion_1er_empleo_signif &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+        </is>
+      </c>
       <c r="K470" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25317,7 +25321,7 @@
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>C-265</t>
+          <t>C-266</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -25332,7 +25336,7 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>duracion_1er_empleo_signif</t>
+          <t>t_tot_reg_ppal</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
@@ -25342,7 +25346,7 @@
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>La duración del primer empleo significativo no supera el tiempo total de empleo (+1)</t>
+          <t>El régimen principal acumula al menos 1/8 del tiempo de empleo (−1)</t>
         </is>
       </c>
       <c r="G471" s="2" t="inlineStr">
@@ -25352,17 +25356,17 @@
       </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>duracion_1er_empleo_signif &gt; COALESCE(t_total_empleo,0) + COALESCE(t_total_mixto_empl_desempl,0) + 1 AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+          <t>t_tot_reg_ppal &lt; COALESCE(t_total_empleo,0) / 8 - 1</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr">
         <is>
-          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+          <t>La categoría 'principal' es la de más tiempo</t>
         </is>
       </c>
       <c r="K471" s="2" t="inlineStr">
@@ -25374,7 +25378,7 @@
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>C-266</t>
+          <t>C-267</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -25389,7 +25393,7 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal</t>
+          <t>t_tot_tipo_contrato_ppal</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -25399,7 +25403,7 @@
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>El régimen principal acumula al menos 1/8 del tiempo de empleo (−1)</t>
+          <t>El tipo de contrato principal acumula al menos 1/7 del tiempo de empleo (−1)</t>
         </is>
       </c>
       <c r="G472" s="2" t="inlineStr">
@@ -25414,7 +25418,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>t_tot_reg_ppal &lt; COALESCE(t_total_empleo,0) / 8 - 1</t>
+          <t>t_tot_tipo_contrato_ppal &lt; COALESCE(t_total_empleo,0) / 7 - 1</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr">
@@ -25431,7 +25435,7 @@
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>C-267</t>
+          <t>C-268</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
@@ -25446,7 +25450,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>t_tot_tipo_contrato_ppal</t>
+          <t>t_tot_grupo_ppal</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -25456,7 +25460,7 @@
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>El tipo de contrato principal acumula al menos 1/7 del tiempo de empleo (−1)</t>
+          <t>El grupo de cotización principal acumula al menos 1/13 del tiempo de empleo (−1)</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
@@ -25471,7 +25475,7 @@
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>t_tot_tipo_contrato_ppal &lt; COALESCE(t_total_empleo,0) / 7 - 1</t>
+          <t>t_tot_grupo_ppal &lt; COALESCE(t_total_empleo,0) / 13 - 1</t>
         </is>
       </c>
       <c r="J473" s="2" t="inlineStr">
@@ -25488,7 +25492,7 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>C-268</t>
+          <t>C-269</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
@@ -25503,7 +25507,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal</t>
+          <t>t_tot_prov_ppal</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -25513,7 +25517,7 @@
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>El grupo de cotización principal acumula al menos 1/13 del tiempo de empleo (−1)</t>
+          <t>El provincia principal acumula al menos 1/52 del tiempo de empleo (−1)</t>
         </is>
       </c>
       <c r="G474" s="2" t="inlineStr">
@@ -25528,7 +25532,7 @@
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal &lt; COALESCE(t_total_empleo,0) / 13 - 1</t>
+          <t>t_tot_prov_ppal &lt; COALESCE(t_total_empleo,0) / 52 - 1</t>
         </is>
       </c>
       <c r="J474" s="2" t="inlineStr">
@@ -25545,7 +25549,7 @@
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>C-269</t>
+          <t>C-270</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
@@ -25555,44 +25559,40 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>Tasas y recuentos</t>
+          <t>Causa de baja y último episodio</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>t_tot_prov_ppal</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>t_total_empleo</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>El provincia principal acumula al menos 1/52 del tiempo de empleo (−1)</t>
+          <t>Última baja por fallecimiento (56) ⇒ fecha_fallecimiento informada</t>
         </is>
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
-          <t>t_tot_prov_ppal &lt; COALESCE(t_total_empleo,0) / 52 - 1</t>
-        </is>
-      </c>
-      <c r="J475" s="2" t="inlineStr">
-        <is>
-          <t>La categoría 'principal' es la de más tiempo</t>
-        </is>
-      </c>
+          <t>causa_ult_baja LIKE '56 %' AND fecha_fallecimiento = 0</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr"/>
       <c r="K475" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -25602,7 +25602,7 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>C-270</t>
+          <t>C-271</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
@@ -25617,32 +25617,32 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
+          <t>fecha_ultima_baja</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
           <t>causa_ult_baja</t>
         </is>
       </c>
-      <c r="E476" s="2" t="inlineStr">
-        <is>
-          <t>fecha_fallecimiento</t>
-        </is>
-      </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>Última baja por fallecimiento (56) ⇒ fecha_fallecimiento informada</t>
+          <t>Con última baja informada ⇒ causa de última baja informada</t>
         </is>
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H476" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja LIKE '56 %' AND fecha_fallecimiento = 0</t>
+          <t>fecha_ultima_baja IS NOT NULL AND causa_ult_baja IS NULL</t>
         </is>
       </c>
       <c r="J476" s="2" t="inlineStr"/>
@@ -25655,7 +25655,7 @@
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>C-271</t>
+          <t>C-272</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
@@ -25680,12 +25680,12 @@
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>Con última baja informada ⇒ causa de última baja informada</t>
+          <t>Episodio vigente (2099) ⇒ causa 00 (guía 2.008)</t>
         </is>
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja IS NOT NULL AND causa_ult_baja IS NULL</t>
+          <t>year(fecha_ultima_baja) = 2099 AND causa_ult_baja NOT LIKE '00 %'</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr"/>
@@ -25708,7 +25708,7 @@
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>C-272</t>
+          <t>C-273</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
@@ -25728,17 +25728,17 @@
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>causa_ult_baja</t>
+          <t>tipo_contr_ult_baja</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>Episodio vigente (2099) ⇒ causa 00 (guía 2.008)</t>
+          <t>Con última baja informada ⇒ tipo de contrato del último episodio informado</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -25748,7 +25748,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>year(fecha_ultima_baja) = 2099 AND causa_ult_baja NOT LIKE '00 %'</t>
+          <t>fecha_ultima_baja IS NOT NULL AND tipo_contr_ult_baja IS NULL</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr"/>
@@ -25761,7 +25761,7 @@
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>C-273</t>
+          <t>C-274</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
@@ -25781,12 +25781,12 @@
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ult_baja</t>
+          <t>act_econ_ult_baja</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>Con última baja informada ⇒ tipo de contrato del último episodio informado</t>
+          <t>Con última baja informada ⇒ actividad económica del último episodio informada</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja IS NOT NULL AND tipo_contr_ult_baja IS NULL</t>
+          <t>fecha_ultima_baja IS NOT NULL AND act_econ_ult_baja IS NULL</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>C-274</t>
+          <t>C-275</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
@@ -25834,12 +25834,12 @@
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>act_econ_ult_baja</t>
+          <t>grupo_ultimo_empleo</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>Con última baja informada ⇒ actividad económica del último episodio informada</t>
+          <t>Con última baja informada ⇒ grupo del último empleo informado</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja IS NOT NULL AND act_econ_ult_baja IS NULL</t>
+          <t>fecha_ultima_baja IS NOT NULL AND grupo_ultimo_empleo IS NULL</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr"/>
@@ -25867,7 +25867,7 @@
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>C-275</t>
+          <t>C-276</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -25877,27 +25877,27 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>Causa de baja y último episodio</t>
+          <t>Situación de afiliación × otras columnas</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
+          <t>situacion_actual_afiliacion</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
           <t>fecha_ultima_baja</t>
         </is>
       </c>
-      <c r="E481" s="2" t="inlineStr">
-        <is>
-          <t>grupo_ultimo_empleo</t>
-        </is>
-      </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>Con última baja informada ⇒ grupo del último empleo informado</t>
+          <t>Episodio vigente (2099) ⇒ Alta_ocupado o Asimilado_*</t>
         </is>
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja IS NOT NULL AND grupo_ultimo_empleo IS NULL</t>
+          <t>year(fecha_ultima_baja) = 2099 AND situacion_actual_afiliacion NOT IN ('Alta_ocupado','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52','Asimilado_otros')</t>
         </is>
       </c>
       <c r="J481" s="2" t="inlineStr"/>
@@ -25920,7 +25920,7 @@
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>C-276</t>
+          <t>C-277</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
@@ -25945,7 +25945,7 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>Episodio vigente (2099) ⇒ Alta_ocupado o Asimilado_*</t>
+          <t>Episodio finalizado ⇒ no Alta_ocupado ni Asimilado_al_alta_*</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>year(fecha_ultima_baja) = 2099 AND situacion_actual_afiliacion NOT IN ('Alta_ocupado','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52','Asimilado_otros')</t>
+          <t>(fecha_ultima_baja IS NULL OR year(fecha_ultima_baja) &lt;&gt; 2099) AND fecha_ultima_baja IS NOT NULL AND situacion_actual_afiliacion IN ('Alta_ocupado','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52')</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr"/>
@@ -25973,7 +25973,7 @@
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>C-277</t>
+          <t>C-278</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -25988,22 +25988,22 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
+          <t>num_bajas_anual_promedio</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
           <t>situacion_actual_afiliacion</t>
         </is>
       </c>
-      <c r="E483" s="2" t="inlineStr">
-        <is>
-          <t>fecha_ultima_baja</t>
-        </is>
-      </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>Episodio finalizado ⇒ no Alta_ocupado ni Asimilado_al_alta_*</t>
+          <t>Con historia de empleo real, sin ninguna baja ⇒ su episodio sigue vigente (no está de baja)</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
@@ -26013,10 +26013,14 @@
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>(fecha_ultima_baja IS NULL OR year(fecha_ultima_baja) &lt;&gt; 2099) AND fecha_ultima_baja IS NOT NULL AND situacion_actual_afiliacion IN ('Alta_ocupado','Asimilado_al_alta_prest_subs','Asimilado_al_alta_subs52')</t>
-        </is>
-      </c>
-      <c r="J483" s="2" t="inlineStr"/>
+          <t>num_bajas_anual_promedio IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion IN ('Baja_de_actividad','Baja_para_pension','Baja_de_prestacion','Baja_de_subsidio')</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>Regla corregida 2026-09-22: num_bajas_anual_promedio solo cuenta bajas de empleo REAL (decisión 'bajas reales' del 2026-09-21); quien nunca ha trabajado (t_total_empleo=0, solo prestación/subsidio/asimilado) tiene NULL por diseño aunque esté de baja. Verificado: los 1.024 incumplimientos anteriores tenían t_total_empleo=0.</t>
+        </is>
+      </c>
       <c r="K483" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26026,7 +26030,7 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>C-278</t>
+          <t>C-279</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
@@ -26041,17 +26045,17 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
+          <t>t_total_desempleo</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
           <t>num_bajas_anual_promedio</t>
         </is>
       </c>
-      <c r="E484" s="2" t="inlineStr">
-        <is>
-          <t>situacion_actual_afiliacion</t>
-        </is>
-      </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>Con historia de empleo real, sin ninguna baja ⇒ su episodio sigue vigente (no está de baja)</t>
+          <t>Con tiempo de desempleo &gt; 0 ⇒ ha tenido bajas</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
@@ -26061,17 +26065,17 @@
       </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio IS NULL AND tiempo_total_desde_inicio_vl IS NOT NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion IN ('Baja_de_actividad','Baja_para_pension','Baja_de_prestacion','Baja_de_subsidio')</t>
+          <t>t_total_desempleo &gt; 0 AND num_bajas_anual_promedio IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones) AND situacion_actual_afiliacion &lt;&gt; 'Alta_ocupado'</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>Regla corregida 2026-09-22: num_bajas_anual_promedio solo cuenta bajas de empleo REAL (decisión 'bajas reales' del 2026-09-21); quien nunca ha trabajado (t_total_empleo=0, solo prestación/subsidio/asimilado) tiene NULL por diseño aunque esté de baja. Verificado: los 1.024 incumplimientos anteriores tenían t_total_empleo=0.</t>
+          <t>Regla ajustada 2026-09-24: excluye solo-prestaciones (G08) y empleo aún abierto (Alta_ocupado: sin bajas pero con tiempo de desempleo).</t>
         </is>
       </c>
       <c r="K484" s="2" t="inlineStr">
@@ -26083,7 +26087,7 @@
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>C-279</t>
+          <t>C-280</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -26098,17 +26102,17 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo</t>
+          <t>situacion_actual_afiliacion</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>num_bajas_anual_promedio</t>
+          <t>fecha_ini_primer_empleo</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>Con tiempo de desempleo &gt; 0 ⇒ ha tenido bajas</t>
+          <t>Sin fecha de primer empleo ⇒ Nunca_ha_cotizado</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
@@ -26118,17 +26122,17 @@
       </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo &gt; 0 AND num_bajas_anual_promedio IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones) AND situacion_actual_afiliacion &lt;&gt; 'Alta_ocupado'</t>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND fecha_ini_primer_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>Regla ajustada 2026-09-24: excluye solo-prestaciones (G08) y empleo aún abierto (Alta_ocupado: sin bajas pero con tiempo de desempleo).</t>
+          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
         </is>
       </c>
       <c r="K485" s="2" t="inlineStr">
@@ -26140,7 +26144,7 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>C-280</t>
+          <t>C-281</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
@@ -26160,12 +26164,12 @@
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>reg_cotiz_ppal_agrupado</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>Sin fecha de primer empleo ⇒ Nunca_ha_cotizado</t>
+          <t>Sin régimen de cotización, con empleo real ⇒ Nunca_ha_cotizado</t>
         </is>
       </c>
       <c r="G486" s="2" t="inlineStr">
@@ -26180,12 +26184,12 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND fecha_ini_primer_empleo IS NULL AND ipf NOT IN (SELECT ipf FROM solo_prestaciones)</t>
+          <t>reg_cotiz_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>Excluye a quien solo tiene episodios TRL 7xx/400 (G08, dato de origen).</t>
+          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene régimen principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
         </is>
       </c>
       <c r="K486" s="2" t="inlineStr">
@@ -26197,7 +26201,7 @@
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>C-281</t>
+          <t>C-282</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
@@ -26217,12 +26221,12 @@
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado</t>
+          <t>tipo_contr_ppal_agrupado</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>Sin régimen de cotización, con empleo real ⇒ Nunca_ha_cotizado</t>
+          <t>Sin tipo de contrato principal (nulo), con empleo real ⇒ Nunca_ha_cotizado</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr">
@@ -26237,12 +26241,12 @@
       </c>
       <c r="I487" s="2" t="inlineStr">
         <is>
-          <t>reg_cotiz_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
+          <t>tipo_contr_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
         </is>
       </c>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene régimen principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
+          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene tipo de contrato principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
         </is>
       </c>
       <c r="K487" s="2" t="inlineStr">
@@ -26254,7 +26258,7 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>C-282</t>
+          <t>C-283</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -26274,12 +26278,12 @@
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado</t>
+          <t>causa_ult_baja</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>Sin tipo de contrato principal (nulo), con empleo real ⇒ Nunca_ha_cotizado</t>
+          <t>Con afiliación ⇒ causa_ult_baja no es el 'NO CONSTA' sin código</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr">
@@ -26294,14 +26298,10 @@
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>tipo_contr_ppal_agrupado IS NULL AND COALESCE(t_total_empleo, 0) &gt; 0 AND situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado'</t>
-        </is>
-      </c>
-      <c r="J488" s="2" t="inlineStr">
-        <is>
-          <t>Regla corregida 2026-09-22: quien nunca tuvo empleo real (solo prestación/subsidio) no tiene tipo de contrato principal, aunque no sea Nunca_ha_cotizado (1.189 personas)</t>
-        </is>
-      </c>
+          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND causa_ult_baja = 'NO CONSTA'</t>
+        </is>
+      </c>
+      <c r="J488" s="2" t="inlineStr"/>
       <c r="K488" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26311,7 +26311,7 @@
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>C-283</t>
+          <t>C-284</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -26326,17 +26326,13 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion</t>
-        </is>
-      </c>
-      <c r="E489" s="2" t="inlineStr">
-        <is>
-          <t>causa_ult_baja</t>
-        </is>
-      </c>
+          <t>duracion_actual_sin_empleo</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr"/>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>Con afiliación ⇒ causa_ult_baja no es el 'NO CONSTA' sin código</t>
+          <t>duracion_actual_sin_empleo es un número entero de días</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr">
@@ -26346,12 +26342,12 @@
       </c>
       <c r="H489" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>situacion_actual_afiliacion &lt;&gt; 'Nunca_ha_cotizado' AND causa_ult_baja = 'NO CONSTA'</t>
+          <t>duracion_actual_sin_empleo &lt;&gt; ROUND(duracion_actual_sin_empleo)</t>
         </is>
       </c>
       <c r="J489" s="2" t="inlineStr"/>
@@ -26364,7 +26360,7 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>C-284</t>
+          <t>C-285</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -26374,18 +26370,22 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>Situación de afiliación × otras columnas</t>
+          <t>Ingresos por tipo (v2.2)</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>duracion_actual_sin_empleo</t>
-        </is>
-      </c>
-      <c r="E490" s="2" t="inlineStr"/>
+          <t>ingresos_bruto_total_2024</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_sueldo_2024</t>
+        </is>
+      </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>duracion_actual_sin_empleo es un número entero de días</t>
+          <t>ingresos_sueldo_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G490" s="2" t="inlineStr">
@@ -26395,12 +26395,12 @@
       </c>
       <c r="H490" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>duracion_actual_sin_empleo &lt;&gt; ROUND(duracion_actual_sin_empleo)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_sueldo_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr"/>
@@ -26413,7 +26413,7 @@
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>C-285</t>
+          <t>C-286</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -26433,12 +26433,12 @@
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_pension_y_bajas_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G491" s="2" t="inlineStr">
@@ -26453,7 +26453,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_sueldo_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_pension_y_bajas_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr"/>
@@ -26466,7 +26466,7 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>C-286</t>
+          <t>C-287</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -26486,12 +26486,12 @@
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_prestacion_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G492" s="2" t="inlineStr">
@@ -26506,7 +26506,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_pension_y_bajas_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_prestacion_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr"/>
@@ -26519,7 +26519,7 @@
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>C-287</t>
+          <t>C-288</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -26539,12 +26539,12 @@
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_actividad_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G493" s="2" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_prestacion_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_actividad_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr"/>
@@ -26572,7 +26572,7 @@
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>C-288</t>
+          <t>C-289</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -26592,12 +26592,12 @@
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_otras_exentas_2024</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>ingresos_otras_exentas_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G494" s="2" t="inlineStr">
@@ -26612,7 +26612,7 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_actividad_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_otras_exentas_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr"/>
@@ -26625,7 +26625,7 @@
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>C-289</t>
+          <t>C-290</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
@@ -26645,12 +26645,12 @@
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024</t>
+          <t>retenciones_irpf_2024</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>retenciones_irpf_2024 informado solo si hay datos fiscales (y al revés)</t>
         </is>
       </c>
       <c r="G495" s="2" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (ingresos_otras_exentas_2024 IS NULL)</t>
+          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (retenciones_irpf_2024 IS NULL)</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>C-290</t>
+          <t>C-291</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
@@ -26696,14 +26696,10 @@
           <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
-      <c r="E496" s="2" t="inlineStr">
-        <is>
-          <t>retenciones_irpf_2024</t>
-        </is>
-      </c>
+      <c r="E496" s="2" t="inlineStr"/>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024 informado solo si hay datos fiscales (y al revés)</t>
+          <t>Las 5 partes suman el total de ingresos (±0,01 €)</t>
         </is>
       </c>
       <c r="G496" s="2" t="inlineStr">
@@ -26718,7 +26714,7 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>(ingresos_bruto_total_2024 IS NULL) &lt;&gt; (retenciones_irpf_2024 IS NULL)</t>
+          <t>ingresos_bruto_total_2024 IS NOT NULL AND ABS(ingresos_bruto_total_2024 - (ingresos_sueldo_2024 + ingresos_pension_y_bajas_2024 + ingresos_prestacion_2024 + ingresos_actividad_2024 + ingresos_otras_exentas_2024)) &gt; 0.01</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr"/>
@@ -26731,7 +26727,7 @@
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>C-291</t>
+          <t>C-292</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
@@ -26746,13 +26742,13 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr"/>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>Las 5 partes suman el total de ingresos (±0,01 €)</t>
+          <t>ingresos_sueldo_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
@@ -26762,15 +26758,19 @@
       </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 IS NOT NULL AND ABS(ingresos_bruto_total_2024 - (ingresos_sueldo_2024 + ingresos_pension_y_bajas_2024 + ingresos_prestacion_2024 + ingresos_actividad_2024 + ingresos_otras_exentas_2024)) &gt; 0.01</t>
-        </is>
-      </c>
-      <c r="J497" s="2" t="inlineStr"/>
+          <t>ingresos_sueldo_2024 &lt; 0</t>
+        </is>
+      </c>
+      <c r="J497" s="2" t="inlineStr">
+        <is>
+          <t>Una rectificación de Hacienda podría dar importes negativos</t>
+        </is>
+      </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -26780,7 +26780,7 @@
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>C-292</t>
+          <t>C-293</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
@@ -26795,13 +26795,13 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr"/>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 ≥ 0</t>
+          <t>ingresos_pension_y_bajas_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="I498" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &lt; 0</t>
+          <t>ingresos_pension_y_bajas_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J498" s="2" t="inlineStr">
@@ -26833,7 +26833,7 @@
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>C-293</t>
+          <t>C-294</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
@@ -26848,13 +26848,13 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr"/>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024 ≥ 0</t>
+          <t>ingresos_prestacion_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G499" s="2" t="inlineStr">
@@ -26869,7 +26869,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024 &lt; 0</t>
+          <t>ingresos_prestacion_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -26886,7 +26886,7 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>C-294</t>
+          <t>C-295</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
@@ -26901,13 +26901,13 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr"/>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 ≥ 0</t>
+          <t>ingresos_actividad_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G500" s="2" t="inlineStr">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &lt; 0</t>
+          <t>ingresos_actividad_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr">
@@ -26939,7 +26939,7 @@
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>C-295</t>
+          <t>C-296</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
@@ -26954,13 +26954,13 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_otras_exentas_2024</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr"/>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 ≥ 0</t>
+          <t>ingresos_otras_exentas_2024 ≥ 0</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
@@ -26975,7 +26975,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &lt; 0</t>
+          <t>ingresos_otras_exentas_2024 &lt; 0</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr">
@@ -26992,7 +26992,7 @@
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>C-296</t>
+          <t>C-297</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
@@ -27007,13 +27007,13 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024</t>
+          <t>retenciones_irpf_2024</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr"/>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024 ≥ 0</t>
+          <t>Las retenciones de IRPF no son negativas</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
@@ -27028,14 +27028,10 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024 &lt; 0</t>
-        </is>
-      </c>
-      <c r="J502" s="2" t="inlineStr">
-        <is>
-          <t>Una rectificación de Hacienda podría dar importes negativos</t>
-        </is>
-      </c>
+          <t>retenciones_irpf_2024 &lt; 0</t>
+        </is>
+      </c>
+      <c r="J502" s="2" t="inlineStr"/>
       <c r="K502" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27045,7 +27041,7 @@
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>C-297</t>
+          <t>C-298</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
@@ -27063,10 +27059,14 @@
           <t>retenciones_irpf_2024</t>
         </is>
       </c>
-      <c r="E503" s="2" t="inlineStr"/>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_bruto_total_2024</t>
+        </is>
+      </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>Las retenciones de IRPF no son negativas</t>
+          <t>Las retenciones no superan el total de ingresos</t>
         </is>
       </c>
       <c r="G503" s="2" t="inlineStr">
@@ -27081,7 +27081,7 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024 &lt; 0</t>
+          <t>retenciones_irpf_2024 &gt; ingresos_bruto_total_2024 + 0.01</t>
         </is>
       </c>
       <c r="J503" s="2" t="inlineStr"/>
@@ -27094,7 +27094,7 @@
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>C-298</t>
+          <t>C-302</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
@@ -27109,22 +27109,22 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>Las retenciones no superan el total de ingresos</t>
+          <t>Con ingresos de sueldo ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
@@ -27134,10 +27134,14 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>retenciones_irpf_2024 &gt; ingresos_bruto_total_2024 + 0.01</t>
-        </is>
-      </c>
-      <c r="J504" s="2" t="inlineStr"/>
+          <t>ingresos_sueldo_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a los menores autorizados (art. 6.4 ET: espectáculos públicos; régimen 0112 de artistas y sectores de espectáculos, artes, publicidad y deporte). Decisión del usuario 2026-09-25.</t>
+        </is>
+      </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27147,7 +27151,7 @@
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>C-302</t>
+          <t>C-303</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -27167,34 +27171,30 @@
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de sueldo ⇒ edad ≥ 16</t>
+          <t>Con ingresos de sueldo 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
-        </is>
-      </c>
-      <c r="J505" s="2" t="inlineStr">
-        <is>
-          <t>Excluye a los menores autorizados (art. 6.4 ET: espectáculos públicos; régimen 0112 de artistas y sectores de espectáculos, artes, publicidad y deporte). Decisión del usuario 2026-09-25.</t>
-        </is>
-      </c>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="inlineStr"/>
       <c r="K505" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27204,7 +27204,7 @@
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>C-303</t>
+          <t>C-304</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -27219,32 +27219,32 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de sueldo 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con ingresos de prestación ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+          <t>ingresos_prestacion_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr"/>
@@ -27257,7 +27257,7 @@
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>C-304</t>
+          <t>C-305</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
@@ -27277,27 +27277,27 @@
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de prestación ⇒ edad ≥ 16</t>
+          <t>Con ingresos de prestación 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16</t>
+          <t>ingresos_prestacion_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J507" s="2" t="inlineStr"/>
@@ -27310,7 +27310,7 @@
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>C-305</t>
+          <t>C-306</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
@@ -27325,35 +27325,39 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>edad_actual_fecha_corte</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de prestación 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con ingresos de actividad ⇒ edad ≥ 16</t>
         </is>
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
-        </is>
-      </c>
-      <c r="J508" s="2" t="inlineStr"/>
+          <t>ingresos_actividad_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
+        </is>
+      </c>
+      <c r="J508" s="2" t="inlineStr">
+        <is>
+          <t>Excluye a los menores autorizados (art. 6.4 ET: espectáculos públicos; régimen 0112 de artistas y sectores de espectáculos, artes, publicidad y deporte). Decisión del usuario 2026-09-25.</t>
+        </is>
+      </c>
       <c r="K508" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27363,7 +27367,7 @@
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>C-306</t>
+          <t>C-307</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
@@ -27383,34 +27387,30 @@
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de actividad ⇒ edad ≥ 16</t>
+          <t>Con ingresos de actividad 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &gt; 0 AND edad_actual_fecha_corte &lt; 16 AND ipf NOT IN (SELECT ipf FROM menor_autorizado)</t>
-        </is>
-      </c>
-      <c r="J509" s="2" t="inlineStr">
-        <is>
-          <t>Excluye a los menores autorizados (art. 6.4 ET: espectáculos públicos; régimen 0112 de artistas y sectores de espectáculos, artes, publicidad y deporte). Decisión del usuario 2026-09-25.</t>
-        </is>
-      </c>
+          <t>ingresos_actividad_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+        </is>
+      </c>
+      <c r="J509" s="2" t="inlineStr"/>
       <c r="K509" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27420,7 +27420,7 @@
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>C-307</t>
+          <t>C-308</t>
         </is>
       </c>
       <c r="B510" s="2" t="inlineStr">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>Con ingresos de actividad 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con pensiones cobradas en 2024 ⇒ no fallecido antes de 2024</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
+          <t>ingresos_pension_y_bajas_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr"/>
@@ -27473,7 +27473,7 @@
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>C-308</t>
+          <t>C-309</t>
         </is>
       </c>
       <c r="B511" s="2" t="inlineStr">
@@ -27488,35 +27488,39 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>t_total_desempleo</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>Con pensiones cobradas en 2024 ⇒ no fallecido antes de 2024</t>
+          <t>Con prestación por desempleo en 2024 ⇒ ha tenido tiempo de desempleo</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024 &gt; 0 AND fecha_fallecimiento BETWEEN 1 AND 202312</t>
-        </is>
-      </c>
-      <c r="J511" s="2" t="inlineStr"/>
+          <t>ingresos_prestacion_2024 &gt; 0 AND COALESCE(t_total_desempleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0</t>
+        </is>
+      </c>
+      <c r="J511" s="2" t="inlineStr">
+        <is>
+          <t>Los subsidios pueden no figurar como desempleo en afiliación</t>
+        </is>
+      </c>
       <c r="K511" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27526,7 +27530,7 @@
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>C-309</t>
+          <t>C-310</t>
         </is>
       </c>
       <c r="B512" s="2" t="inlineStr">
@@ -27541,37 +27545,37 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_sueldo_2024</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>t_total_desempleo</t>
+          <t>fecha_ini_primer_empleo</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>Con prestación por desempleo en 2024 ⇒ ha tenido tiempo de desempleo</t>
+          <t>Con sueldo en 2024 ⇒ tiene primer empleo en afiliación</t>
         </is>
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024 &gt; 0 AND COALESCE(t_total_desempleo, 0) + COALESCE(t_total_mixto_empl_desempl, 0) = 0</t>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ini_primer_empleo IS NULL</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
         <is>
-          <t>Los subsidios pueden no figurar como desempleo en afiliación</t>
+          <t>Los funcionarios de MUFACE no cotizan en el sistema de la MCVL</t>
         </is>
       </c>
       <c r="K512" s="2" t="inlineStr">
@@ -27583,7 +27587,7 @@
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>C-310</t>
+          <t>C-311</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
@@ -27603,32 +27607,32 @@
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>fecha_ini_primer_empleo</t>
+          <t>fecha_ultima_baja</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>Con sueldo en 2024 ⇒ tiene primer empleo en afiliación</t>
+          <t>Con sueldo en 2024 ⇒ la última baja no es anterior a 2024</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ini_primer_empleo IS NULL</t>
+          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ultima_baja IS NOT NULL AND year(fecha_ultima_baja) &lt; 2024</t>
         </is>
       </c>
       <c r="J513" s="2" t="inlineStr">
         <is>
-          <t>Los funcionarios de MUFACE no cotizan en el sistema de la MCVL</t>
+          <t>Pagos atrasados o indemnizaciones podrían dar sueldo sin alta en 2024</t>
         </is>
       </c>
       <c r="K513" s="2" t="inlineStr">
@@ -27640,7 +27644,7 @@
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>C-311</t>
+          <t>C-313</t>
         </is>
       </c>
       <c r="B514" s="2" t="inlineStr">
@@ -27655,17 +27659,17 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>cobra_pension_2024_5</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>fecha_ultima_baja</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>Con sueldo en 2024 ⇒ la última baja no es anterior a 2024</t>
+          <t>Cobra pensión en la tabla de pensiones ⇒ tiene pensión en fiscal (si consta en fiscal)</t>
         </is>
       </c>
       <c r="G514" s="2" t="inlineStr">
@@ -27675,17 +27679,17 @@
       </c>
       <c r="H514" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024 &gt; 0 AND fecha_ultima_baja IS NOT NULL AND year(fecha_ultima_baja) &lt; 2024</t>
+          <t>cobra_pension_2024_5 = 'SI' AND ingresos_bruto_total_2024 IS NOT NULL AND ingresos_pension_y_bajas_2024 = 0</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>Pagos atrasados o indemnizaciones podrían dar sueldo sin alta en 2024</t>
+          <t>Puede haber empezado a cobrar en 2025</t>
         </is>
       </c>
       <c r="K514" s="2" t="inlineStr">
@@ -27697,7 +27701,7 @@
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>C-313</t>
+          <t>C-314</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
@@ -27707,42 +27711,42 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>Ingresos por tipo (v2.2)</t>
+          <t>Clave y subclave de percepción (v2.2)</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5</t>
+          <t>clave_subclave_ppal</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024</t>
+          <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>Cobra pensión en la tabla de pensiones ⇒ tiene pensión en fiscal (si consta en fiscal)</t>
+          <t>clave_subclave_ppal = NO CONSTA ⇔ ingresos fiscales nulos o 0</t>
         </is>
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>cobra_pension_2024_5 = 'SI' AND ingresos_bruto_total_2024 IS NOT NULL AND ingresos_pension_y_bajas_2024 = 0</t>
+          <t>(clave_subclave_ppal = 'NO CONSTA') &lt;&gt; (COALESCE(ingresos_bruto_total_2024, 0) = 0)</t>
         </is>
       </c>
       <c r="J515" s="2" t="inlineStr">
         <is>
-          <t>Puede haber empezado a cobrar en 2025</t>
+          <t>Regla reformulada 2026-09-24: la clave sale de la percepción con más ingresos; las 278 personas con fila fiscal a 0 en todas las partes no tienen ninguna que elegir. La versión anterior (ingresos IS NULL) las marcaba como incumplimiento.</t>
         </is>
       </c>
       <c r="K515" s="2" t="inlineStr">
@@ -27754,7 +27758,7 @@
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>C-314</t>
+          <t>C-315</t>
         </is>
       </c>
       <c r="B516" s="2" t="inlineStr">
@@ -27772,19 +27776,15 @@
           <t>clave_subclave_ppal</t>
         </is>
       </c>
-      <c r="E516" s="2" t="inlineStr">
-        <is>
-          <t>ingresos_bruto_total_2024</t>
-        </is>
-      </c>
+      <c r="E516" s="2" t="inlineStr"/>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal = NO CONSTA ⇔ ingresos fiscales nulos o 0</t>
+          <t>clave_subclave_ppal = 'letra + 2 (dígito/X)' con etiqueta, o NO CONSTA</t>
         </is>
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -27794,12 +27794,12 @@
       </c>
       <c r="I516" s="2" t="inlineStr">
         <is>
-          <t>(clave_subclave_ppal = 'NO CONSTA') &lt;&gt; (COALESCE(ingresos_bruto_total_2024, 0) = 0)</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(clave_subclave_ppal, '^[ABCFGHL][0-9X]{2}( .+)?$')</t>
         </is>
       </c>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>Regla reformulada 2026-09-24: la clave sale de la percepción con más ingresos; las 278 personas con fila fiscal a 0 en todas las partes no tienen ninguna que elegir. La versión anterior (ingresos IS NULL) las marcaba como incumplimiento.</t>
+          <t>Claves del modelo 190 presentes en la MCVL: A, B, C, F, G, H, L</t>
         </is>
       </c>
       <c r="K516" s="2" t="inlineStr">
@@ -27811,7 +27811,7 @@
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>C-315</t>
+          <t>C-316</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
@@ -27832,12 +27832,12 @@
       <c r="E517" s="2" t="inlineStr"/>
       <c r="F517" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal = 'letra + 2 (dígito/X)' con etiqueta, o NO CONSTA</t>
+          <t>Cada código de clave+subclave tiene una única etiqueta</t>
         </is>
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -27847,14 +27847,10 @@
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND NOT regexp_matches(clave_subclave_ppal, '^[ABCFGHL][0-9X]{2}( .+)?$')</t>
-        </is>
-      </c>
-      <c r="J517" s="2" t="inlineStr">
-        <is>
-          <t>Claves del modelo 190 presentes en la MCVL: A, B, C, F, G, H, L</t>
-        </is>
-      </c>
+          <t>split_part(clave_subclave_ppal, ' ', 1) IN (SELECT split_part(clave_subclave_ppal, ' ', 1) FROM personas WHERE clave_subclave_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT clave_subclave_ppal) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J517" s="2" t="inlineStr"/>
       <c r="K517" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -27864,7 +27860,7 @@
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>C-316</t>
+          <t>C-317</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
@@ -27882,10 +27878,14 @@
           <t>clave_subclave_ppal</t>
         </is>
       </c>
-      <c r="E518" s="2" t="inlineStr"/>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_sueldo_2024</t>
+        </is>
+      </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>Cada código de clave+subclave tiene una única etiqueta</t>
+          <t>Tipo principal de sueldo (A) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G518" s="2" t="inlineStr">
@@ -27900,7 +27900,7 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>split_part(clave_subclave_ppal, ' ', 1) IN (SELECT split_part(clave_subclave_ppal, ' ', 1) FROM personas WHERE clave_subclave_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT clave_subclave_ppal) &gt; 1)</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'A%' AND COALESCE(ingresos_sueldo_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr"/>
@@ -27913,7 +27913,7 @@
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>C-317</t>
+          <t>C-318</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
@@ -27933,12 +27933,12 @@
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_pension_y_bajas_2024</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de sueldo (A) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de pensión (B, L06, L07, L08) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G519" s="2" t="inlineStr">
@@ -27953,7 +27953,7 @@
       </c>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'A%' AND COALESCE(ingresos_sueldo_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'B%' OR split_part(clave_subclave_ppal, ' ', 1) IN ('L06','L07','L08')) AND COALESCE(ingresos_pension_y_bajas_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J519" s="2" t="inlineStr"/>
@@ -27966,7 +27966,7 @@
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>C-318</t>
+          <t>C-319</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
@@ -27986,12 +27986,12 @@
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>ingresos_pension_y_bajas_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de pensión (B, L06, L07, L08) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de prestación (C) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G520" s="2" t="inlineStr">
@@ -28006,7 +28006,7 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'B%' OR split_part(clave_subclave_ppal, ' ', 1) IN ('L06','L07','L08')) AND COALESCE(ingresos_pension_y_bajas_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'C%' AND COALESCE(ingresos_prestacion_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr"/>
@@ -28019,7 +28019,7 @@
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>C-319</t>
+          <t>C-320</t>
         </is>
       </c>
       <c r="B521" s="2" t="inlineStr">
@@ -28039,12 +28039,12 @@
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>ingresos_actividad_2024</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de prestación (C) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de actividad (F, G, H) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND split_part(clave_subclave_ppal, ' ', 1) LIKE 'C%' AND COALESCE(ingresos_prestacion_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'F%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'G%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'H%') AND COALESCE(ingresos_actividad_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J521" s="2" t="inlineStr"/>
@@ -28072,7 +28072,7 @@
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>C-320</t>
+          <t>C-321</t>
         </is>
       </c>
       <c r="B522" s="2" t="inlineStr">
@@ -28092,12 +28092,12 @@
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>ingresos_actividad_2024</t>
+          <t>ingresos_otras_exentas_2024</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de actividad (F, G, H) ⇒ ese importe es positivo</t>
+          <t>Tipo principal de otras exentas (resto de L) ⇒ ese importe es positivo</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'F%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'G%' OR split_part(clave_subclave_ppal, ' ', 1) LIKE 'H%') AND COALESCE(ingresos_actividad_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'L%' AND split_part(clave_subclave_ppal, ' ', 1) NOT IN ('L06','L07','L08')) AND COALESCE(ingresos_otras_exentas_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr"/>
@@ -28125,7 +28125,7 @@
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>C-321</t>
+          <t>C-322</t>
         </is>
       </c>
       <c r="B523" s="2" t="inlineStr">
@@ -28140,17 +28140,17 @@
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal</t>
+          <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>ingresos_otras_exentas_2024</t>
+          <t>ingresos_bruto_total_2024</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
-          <t>Tipo principal de otras exentas (resto de L) ⇒ ese importe es positivo</t>
+          <t>Con lista de tipos cobrados ⇒ total de ingresos &gt; 0</t>
         </is>
       </c>
       <c r="G523" s="2" t="inlineStr">
@@ -28165,7 +28165,7 @@
       </c>
       <c r="I523" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_ppal &lt;&gt; 'NO CONSTA' AND (split_part(clave_subclave_ppal, ' ', 1) LIKE 'L%' AND split_part(clave_subclave_ppal, ' ', 1) NOT IN ('L06','L07','L08')) AND COALESCE(ingresos_otras_exentas_2024, 0) &lt;= 0</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND COALESCE(ingresos_bruto_total_2024, 0) &lt;= 0</t>
         </is>
       </c>
       <c r="J523" s="2" t="inlineStr"/>
@@ -28178,7 +28178,7 @@
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>C-322</t>
+          <t>C-323</t>
         </is>
       </c>
       <c r="B524" s="2" t="inlineStr">
@@ -28203,7 +28203,7 @@
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>Con lista de tipos cobrados ⇒ total de ingresos &gt; 0</t>
+          <t>Total de ingresos &gt; 0 ⇒ hay lista de tipos cobrados</t>
         </is>
       </c>
       <c r="G524" s="2" t="inlineStr">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND COALESCE(ingresos_bruto_total_2024, 0) &lt;= 0</t>
+          <t>ingresos_bruto_total_2024 &gt; 0 AND clave_subclave_todas_cobradas IS NULL</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr"/>
@@ -28231,7 +28231,7 @@
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>C-323</t>
+          <t>C-324</t>
         </is>
       </c>
       <c r="B525" s="2" t="inlineStr">
@@ -28251,12 +28251,12 @@
       </c>
       <c r="E525" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024</t>
+          <t>clave_subclave_ppal</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>Total de ingresos &gt; 0 ⇒ hay lista de tipos cobrados</t>
+          <t>El primer tipo cobrado es el tipo principal</t>
         </is>
       </c>
       <c r="G525" s="2" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="I525" s="2" t="inlineStr">
         <is>
-          <t>ingresos_bruto_total_2024 &gt; 0 AND clave_subclave_todas_cobradas IS NULL</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND clave_subclave_todas_cobradas[1] &lt;&gt; split_part(clave_subclave_ppal, ' ', 1)</t>
         </is>
       </c>
       <c r="J525" s="2" t="inlineStr"/>
@@ -28284,7 +28284,7 @@
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>C-324</t>
+          <t>C-325</t>
         </is>
       </c>
       <c r="B526" s="2" t="inlineStr">
@@ -28302,14 +28302,10 @@
           <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
-      <c r="E526" s="2" t="inlineStr">
-        <is>
-          <t>clave_subclave_ppal</t>
-        </is>
-      </c>
+      <c r="E526" s="2" t="inlineStr"/>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>El primer tipo cobrado es el tipo principal</t>
+          <t>La lista de tipos cobrados no repite códigos</t>
         </is>
       </c>
       <c r="G526" s="2" t="inlineStr">
@@ -28324,7 +28320,7 @@
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND clave_subclave_todas_cobradas[1] &lt;&gt; split_part(clave_subclave_ppal, ' ', 1)</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) &lt;&gt; len(list_distinct(clave_subclave_todas_cobradas))</t>
         </is>
       </c>
       <c r="J526" s="2" t="inlineStr"/>
@@ -28337,7 +28333,7 @@
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>C-325</t>
+          <t>C-326</t>
         </is>
       </c>
       <c r="B527" s="2" t="inlineStr">
@@ -28358,12 +28354,12 @@
       <c r="E527" s="2" t="inlineStr"/>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>La lista de tipos cobrados no repite códigos</t>
+          <t>Los códigos de la lista tienen formato letra + 2 (dígito/X)</t>
         </is>
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H527" s="2" t="inlineStr">
@@ -28373,7 +28369,7 @@
       </c>
       <c r="I527" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) &lt;&gt; len(list_distinct(clave_subclave_todas_cobradas))</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(list_filter(clave_subclave_todas_cobradas, x -&gt; NOT regexp_matches(x, '^[ABCFGHL][0-9X]{2}$'))) &gt; 0</t>
         </is>
       </c>
       <c r="J527" s="2" t="inlineStr"/>
@@ -28386,7 +28382,7 @@
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>C-326</t>
+          <t>C-327</t>
         </is>
       </c>
       <c r="B528" s="2" t="inlineStr">
@@ -28407,22 +28403,22 @@
       <c r="E528" s="2" t="inlineStr"/>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>Los códigos de la lista tienen formato letra + 2 (dígito/X)</t>
+          <t>Sin tipos cobrados ⇒ NULL, no lista vacía</t>
         </is>
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H528" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(list_filter(clave_subclave_todas_cobradas, x -&gt; NOT regexp_matches(x, '^[ABCFGHL][0-9X]{2}$'))) &gt; 0</t>
+          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) = 0</t>
         </is>
       </c>
       <c r="J528" s="2" t="inlineStr"/>
@@ -28435,7 +28431,7 @@
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>C-327</t>
+          <t>C-328</t>
         </is>
       </c>
       <c r="B529" s="2" t="inlineStr">
@@ -28453,10 +28449,14 @@
           <t>clave_subclave_todas_cobradas</t>
         </is>
       </c>
-      <c r="E529" s="2" t="inlineStr"/>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>ingresos_sueldo_2024</t>
+        </is>
+      </c>
       <c r="F529" s="2" t="inlineStr">
         <is>
-          <t>Sin tipos cobrados ⇒ NULL, no lista vacía</t>
+          <t>A00 en la lista ⇔ sueldo positivo</t>
         </is>
       </c>
       <c r="G529" s="2" t="inlineStr">
@@ -28466,12 +28466,12 @@
       </c>
       <c r="H529" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I529" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas IS NOT NULL AND len(clave_subclave_todas_cobradas) = 0</t>
+          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'A00'), false) &lt;&gt; (COALESCE(ingresos_sueldo_2024, 0) &gt; 0)</t>
         </is>
       </c>
       <c r="J529" s="2" t="inlineStr"/>
@@ -28484,7 +28484,7 @@
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>C-328</t>
+          <t>C-329</t>
         </is>
       </c>
       <c r="B530" s="2" t="inlineStr">
@@ -28504,12 +28504,12 @@
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>ingresos_sueldo_2024</t>
+          <t>ingresos_prestacion_2024</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>A00 en la lista ⇔ sueldo positivo</t>
+          <t>C00 en la lista ⇔ prestación positiva</t>
         </is>
       </c>
       <c r="G530" s="2" t="inlineStr">
@@ -28524,7 +28524,7 @@
       </c>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'A00'), false) &lt;&gt; (COALESCE(ingresos_sueldo_2024, 0) &gt; 0)</t>
+          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'C00'), false) &lt;&gt; (COALESCE(ingresos_prestacion_2024, 0) &gt; 0)</t>
         </is>
       </c>
       <c r="J530" s="2" t="inlineStr"/>
@@ -28537,7 +28537,7 @@
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>C-329</t>
+          <t>C-330</t>
         </is>
       </c>
       <c r="B531" s="2" t="inlineStr">
@@ -28547,27 +28547,27 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>Clave y subclave de percepción (v2.2)</t>
+          <t>Fallecimiento (v2.2)</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>clave_subclave_todas_cobradas</t>
+          <t>ha_fallecido</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>ingresos_prestacion_2024</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>C00 en la lista ⇔ prestación positiva</t>
+          <t>ha_fallecido = SI ⇔ fecha_fallecimiento informada</t>
         </is>
       </c>
       <c r="G531" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Guía MCVL</t>
         </is>
       </c>
       <c r="H531" s="2" t="inlineStr">
@@ -28577,7 +28577,7 @@
       </c>
       <c r="I531" s="2" t="inlineStr">
         <is>
-          <t>COALESCE(list_contains(clave_subclave_todas_cobradas, 'C00'), false) &lt;&gt; (COALESCE(ingresos_prestacion_2024, 0) &gt; 0)</t>
+          <t>(ha_fallecido = 'SI') &lt;&gt; (COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0)</t>
         </is>
       </c>
       <c r="J531" s="2" t="inlineStr"/>
@@ -28590,7 +28590,7 @@
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>C-330</t>
+          <t>C-331</t>
         </is>
       </c>
       <c r="B532" s="2" t="inlineStr">
@@ -28610,17 +28610,17 @@
       </c>
       <c r="E532" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>edad_fallecimiento</t>
         </is>
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = SI ⇔ fecha_fallecimiento informada</t>
+          <t>ha_fallecido = SI ⇔ edad_fallecimiento informada</t>
         </is>
       </c>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>Guía MCVL</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H532" s="2" t="inlineStr">
@@ -28630,7 +28630,7 @@
       </c>
       <c r="I532" s="2" t="inlineStr">
         <is>
-          <t>(ha_fallecido = 'SI') &lt;&gt; (COALESCE(fecha_fallecimiento, 0) &lt;&gt; 0)</t>
+          <t>(ha_fallecido = 'SI') &lt;&gt; (edad_fallecimiento IS NOT NULL)</t>
         </is>
       </c>
       <c r="J532" s="2" t="inlineStr"/>
@@ -28643,7 +28643,7 @@
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>C-331</t>
+          <t>C-332</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
@@ -28658,17 +28658,13 @@
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido</t>
-        </is>
-      </c>
-      <c r="E533" s="2" t="inlineStr">
-        <is>
           <t>edad_fallecimiento</t>
         </is>
       </c>
+      <c r="E533" s="2" t="inlineStr"/>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = SI ⇔ edad_fallecimiento informada</t>
+          <t>edad_fallecimiento ≥ 0 (no se muere antes de nacer)</t>
         </is>
       </c>
       <c r="G533" s="2" t="inlineStr">
@@ -28683,7 +28679,7 @@
       </c>
       <c r="I533" s="2" t="inlineStr">
         <is>
-          <t>(ha_fallecido = 'SI') &lt;&gt; (edad_fallecimiento IS NOT NULL)</t>
+          <t>edad_fallecimiento &lt; 0</t>
         </is>
       </c>
       <c r="J533" s="2" t="inlineStr"/>
@@ -28696,7 +28692,7 @@
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>C-332</t>
+          <t>C-333</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
@@ -28717,22 +28713,22 @@
       <c r="E534" s="2" t="inlineStr"/>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento ≥ 0 (no se muere antes de nacer)</t>
+          <t>edad_fallecimiento ≤ 115</t>
         </is>
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento &lt; 0</t>
+          <t>edad_fallecimiento &gt; 115</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr"/>
@@ -28745,7 +28741,7 @@
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>C-333</t>
+          <t>C-334</t>
         </is>
       </c>
       <c r="B535" s="2" t="inlineStr">
@@ -28763,28 +28759,36 @@
           <t>edad_fallecimiento</t>
         </is>
       </c>
-      <c r="E535" s="2" t="inlineStr"/>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>edad_actual_fecha_corte</t>
+        </is>
+      </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento ≤ 115</t>
+          <t>Fallecidos: edad_actual_fecha_corte = edad_fallecimiento (la edad se calcula a la fecha de fallecimiento)</t>
         </is>
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>Dominio (Seg. Social / lógica)</t>
+          <t>Significado del nombre</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="I535" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento &gt; 115</t>
-        </is>
-      </c>
-      <c r="J535" s="2" t="inlineStr"/>
+          <t>ha_fallecido = 'SI' AND ABS(edad_actual_fecha_corte - edad_fallecimiento) &gt; 0.01</t>
+        </is>
+      </c>
+      <c r="J535" s="2" t="inlineStr">
+        <is>
+          <t>Comprobación pedida por el usuario 2026-09-21 | Reformulada 2026-09-25 (decisión del usuario): Edad_Actual_Fecha_Corte de los fallecidos se calcula a su fecha de fallecimiento. Con el Parquet anterior a esa regeneración da 18.801 incumplimientos; debe dar 0 tras regenerar.</t>
+        </is>
+      </c>
       <c r="K535" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28794,7 +28798,7 @@
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>C-334</t>
+          <t>C-335</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
@@ -28814,12 +28818,12 @@
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>edad_actual_fecha_corte</t>
+          <t>fecha_fallecimiento</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>Fallecidos: edad_actual_fecha_corte = edad_fallecimiento (la edad se calcula a la fecha de fallecimiento)</t>
+          <t>edad_fallecimiento = meses entre nacimiento y fallecimiento / 12 (±0,001)</t>
         </is>
       </c>
       <c r="G536" s="2" t="inlineStr">
@@ -28834,14 +28838,10 @@
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = 'SI' AND ABS(edad_actual_fecha_corte - edad_fallecimiento) &gt; 0.01</t>
-        </is>
-      </c>
-      <c r="J536" s="2" t="inlineStr">
-        <is>
-          <t>Comprobación pedida por el usuario 2026-09-21 | Reformulada 2026-09-25 (decisión del usuario): Edad_Actual_Fecha_Corte de los fallecidos se calcula a su fecha de fallecimiento. Con el Parquet anterior a esa regeneración da 18.801 incumplimientos; debe dar 0 tras regenerar.</t>
-        </is>
-      </c>
+          <t>ha_fallecido = 'SI' AND ABS(edad_fallecimiento - (((fecha_fallecimiento // 100 - year(fecha_nacimiento)) * 12 + (fecha_fallecimiento % 100 - month(fecha_nacimiento))) / 12.0)) &gt; 0.001</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr"/>
       <c r="K536" s="2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -28851,7 +28851,7 @@
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>C-335</t>
+          <t>C-336</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
@@ -28861,22 +28861,22 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>Fallecimiento (v2.2)</t>
+          <t>Residencia (v2.2)</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento</t>
+          <t>domic_resid_habitual</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
         <is>
-          <t>fecha_fallecimiento</t>
+          <t>prov_resid_habitual</t>
         </is>
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>edad_fallecimiento = meses entre nacimiento y fallecimiento / 12 (±0,001)</t>
+          <t>domicilio NO CONSTA ⇔ provincia de residencia NO CONSTA</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
@@ -28891,7 +28891,7 @@
       </c>
       <c r="I537" s="2" t="inlineStr">
         <is>
-          <t>ha_fallecido = 'SI' AND ABS(edad_fallecimiento - (((fecha_fallecimiento // 100 - year(fecha_nacimiento)) * 12 + (fecha_fallecimiento % 100 - month(fecha_nacimiento))) / 12.0)) &gt; 0.001</t>
+          <t>(domic_resid_habitual = 'NO CONSTA') &lt;&gt; (prov_resid_habitual = 'NO CONSTA')</t>
         </is>
       </c>
       <c r="J537" s="2" t="inlineStr"/>
@@ -28904,7 +28904,7 @@
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>C-336</t>
+          <t>C-337</t>
         </is>
       </c>
       <c r="B538" s="2" t="inlineStr">
@@ -28929,7 +28929,7 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>domicilio NO CONSTA ⇔ provincia de residencia NO CONSTA</t>
+          <t>El código de provincia del domicilio coincide con prov_resid_habitual</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
@@ -28944,7 +28944,7 @@
       </c>
       <c r="I538" s="2" t="inlineStr">
         <is>
-          <t>(domic_resid_habitual = 'NO CONSTA') &lt;&gt; (prov_resid_habitual = 'NO CONSTA')</t>
+          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND split_part(prov_resid_habitual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
         </is>
       </c>
       <c r="J538" s="2" t="inlineStr"/>
@@ -28957,7 +28957,7 @@
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>C-337</t>
+          <t>C-338</t>
         </is>
       </c>
       <c r="B539" s="2" t="inlineStr">
@@ -28977,88 +28977,35 @@
       </c>
       <c r="E539" s="2" t="inlineStr">
         <is>
-          <t>prov_resid_habitual</t>
+          <t>prov_fiscal_actual</t>
         </is>
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>El código de provincia del domicilio coincide con prov_resid_habitual</t>
+          <t>La provincia de residencia coincide con la provincia fiscal</t>
         </is>
       </c>
       <c r="G539" s="2" t="inlineStr">
         <is>
-          <t>Significado del nombre</t>
+          <t>Dominio (Seg. Social / lógica)</t>
         </is>
       </c>
       <c r="H539" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (heurística, puede haber excepciones legítimas)</t>
         </is>
       </c>
       <c r="I539" s="2" t="inlineStr">
         <is>
-          <t>domic_resid_habitual &lt;&gt; 'NO CONSTA' AND split_part(prov_resid_habitual, ' ', 1) &lt;&gt; left(domic_resid_habitual, 2)</t>
-        </is>
-      </c>
-      <c r="J539" s="2" t="inlineStr"/>
+          <t>(domic_resid_habitual IS NOT NULL AND domic_resid_habitual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND CASE WHEN split_part(prov_fiscal_actual, ' ', 1) = '53' THEN '38' ELSE split_part(prov_fiscal_actual, ' ', 1) END &lt;&gt; left(domic_resid_habitual, 2) AND split_part(prov_fiscal_actual, ' ', 1) &lt;&gt; '98'</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="inlineStr">
+        <is>
+          <t>El domicilio fiscal es el del 31-12-2024; puede haber mudanzas | Regla ajustada 2026-09-24: el 53 fiscal (Isla de La Palma) es provincia 38 (Santa Cruz de Tenerife) en el INE, y el 98 (residencia fiscal en el extranjero) no es comparable.</t>
+        </is>
+      </c>
       <c r="K539" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" s="2" t="inlineStr">
-        <is>
-          <t>C-338</t>
-        </is>
-      </c>
-      <c r="B540" s="2" t="inlineStr">
-        <is>
-          <t>C · otras columnas</t>
-        </is>
-      </c>
-      <c r="C540" s="2" t="inlineStr">
-        <is>
-          <t>Residencia (v2.2)</t>
-        </is>
-      </c>
-      <c r="D540" s="2" t="inlineStr">
-        <is>
-          <t>domic_resid_habitual</t>
-        </is>
-      </c>
-      <c r="E540" s="2" t="inlineStr">
-        <is>
-          <t>prov_fiscal_actual</t>
-        </is>
-      </c>
-      <c r="F540" s="2" t="inlineStr">
-        <is>
-          <t>La provincia de residencia coincide con la provincia fiscal</t>
-        </is>
-      </c>
-      <c r="G540" s="2" t="inlineStr">
-        <is>
-          <t>Dominio (Seg. Social / lógica)</t>
-        </is>
-      </c>
-      <c r="H540" s="2" t="inlineStr">
-        <is>
-          <t>Baja (heurística, puede haber excepciones legítimas)</t>
-        </is>
-      </c>
-      <c r="I540" s="2" t="inlineStr">
-        <is>
-          <t>(domic_resid_habitual IS NOT NULL AND domic_resid_habitual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND (prov_fiscal_actual IS NOT NULL AND prov_fiscal_actual NOT IN ('NO CONSTA','No consta','0 NO CONSTA','00 No consta')) AND CASE WHEN split_part(prov_fiscal_actual, ' ', 1) = '53' THEN '38' ELSE split_part(prov_fiscal_actual, ' ', 1) END &lt;&gt; left(domic_resid_habitual, 2) AND split_part(prov_fiscal_actual, ' ', 1) &lt;&gt; '98'</t>
-        </is>
-      </c>
-      <c r="J540" s="2" t="inlineStr">
-        <is>
-          <t>El domicilio fiscal es el del 31-12-2024; puede haber mudanzas | Regla ajustada 2026-09-24: el 53 fiscal (Isla de La Palma) es provincia 38 (Santa Cruz de Tenerife) en el INE, y el 98 (residencia fiscal en el extranjero) no es comparable.</t>
-        </is>
-      </c>
-      <c r="K540" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -29122,7 +29069,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5">
@@ -29132,9 +29079,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>539</v>
-      </c>
-    </row>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -29175,6 +29123,7 @@
         <v>120</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -29282,6 +29231,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>

--- a/tests/reglas_consistencia_v4.xlsx
+++ b/tests/reglas_consistencia_v4.xlsx
@@ -18126,7 +18126,7 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal IS NULL AND NOT (grupo_cotiz_ppal = 'NO CONSTA')</t>
+          <t>t_tot_grupo_ppal IS NULL AND NOT (grupo_cotiz_ppal = '0 NO CONSTA')</t>
         </is>
       </c>
       <c r="J332" s="2" t="inlineStr"/>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>grupo_cotiz_ppal sin valor ⇒ t_tot_grupo_ppal vacío</t>
+          <t>Sin primer empleo ⇒ t_tot_grupo_ppal vacío</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
@@ -18179,7 +18179,7 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>t_tot_grupo_ppal IS NOT NULL AND (grupo_cotiz_ppal = 'NO CONSTA') AND t_tot_grupo_ppal &gt; 0</t>
+          <t>fecha_ini_primer_empleo IS NULL AND t_tot_grupo_ppal IS NOT NULL</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr"/>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_cotiz_ppal, ' ', 1) IN (SELECT split_part(grupo_cotiz_ppal, ' ', 1) FROM personas WHERE grupo_cotiz_ppal &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_ppal) &gt; 1)</t>
+          <t>split_part(grupo_cotiz_ppal, ' ', 1) IN (SELECT split_part(grupo_cotiz_ppal, ' ', 1) FROM personas WHERE grupo_cotiz_ppal &lt;&gt; '0 NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_ppal) &gt; 1)</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr"/>
@@ -21526,7 +21526,7 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_ultimo_empleo, ' ', 1) IN (SELECT split_part(grupo_ultimo_empleo, ' ', 1) FROM personas WHERE grupo_ultimo_empleo &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_ultimo_empleo) &gt; 1)</t>
+          <t>split_part(grupo_ultimo_empleo, ' ', 1) IN (SELECT split_part(grupo_ultimo_empleo, ' ', 1) FROM personas WHERE grupo_ultimo_empleo &lt;&gt; '0 NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_ultimo_empleo) &gt; 1)</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr"/>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) IN (SELECT split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) FROM personas WHERE grupo_cotiz_1er_empleo_signif &lt;&gt; 'NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_1er_empleo_signif) &gt; 1)</t>
+          <t>split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) IN (SELECT split_part(grupo_cotiz_1er_empleo_signif, ' ', 1) FROM personas WHERE grupo_cotiz_1er_empleo_signif &lt;&gt; '0 NO CONSTA' GROUP BY 1 HAVING COUNT(DISTINCT grupo_cotiz_1er_empleo_signif) &gt; 1)</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr"/>
@@ -29082,7 +29082,6 @@
         <v>538</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -29123,7 +29122,6 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -29231,7 +29229,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
